--- a/Swans/R_calc_swans/Data/swans.xlsx
+++ b/Swans/R_calc_swans/Data/swans.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9264"/>
+    <workbookView windowWidth="22188" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="All_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Ice_period" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$B$1:$J$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">All_data!$B$1:$J$666</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ice_period!$A$1:$K$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -127,6 +129,15 @@
   <si>
     <t>Восточный берег кургальского полуострова у Липово</t>
   </si>
+  <si>
+    <t>Feeding_place</t>
+  </si>
+  <si>
+    <t>remote deep-water areas near the ice edge</t>
+  </si>
+  <si>
+    <t>coastal shallow ice floes</t>
+  </si>
 </sst>
 </file>
 
@@ -139,7 +150,7 @@
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="[$-419]d\ mmm;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +161,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="204"/>
       <scheme val="minor"/>
@@ -312,12 +337,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -632,148 +663,155 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1361,7 +1399,7 @@
       <c r="E2" s="1">
         <v>2006</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <v>38815</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1393,7 +1431,7 @@
       <c r="E3" s="1">
         <v>2006</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <v>38815</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1425,7 +1463,7 @@
       <c r="E4" s="1">
         <v>2006</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <v>38820</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1457,7 +1495,7 @@
       <c r="E5" s="1">
         <v>2006</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <v>38820</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1489,7 +1527,7 @@
       <c r="E6" s="1">
         <v>2006</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <v>38820</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1521,7 +1559,7 @@
       <c r="E7" s="1">
         <v>2006</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <v>38820</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1553,7 +1591,7 @@
       <c r="E8" s="1">
         <v>2006</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <v>38820</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1585,7 +1623,7 @@
       <c r="E9" s="1">
         <v>2006</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <v>38820</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1617,7 +1655,7 @@
       <c r="E10" s="1">
         <v>2006</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <v>38820</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1649,7 +1687,7 @@
       <c r="E11" s="1">
         <v>2006</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <v>38827</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1681,7 +1719,7 @@
       <c r="E12" s="1">
         <v>2006</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <v>38827</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1713,7 +1751,7 @@
       <c r="E13" s="1">
         <v>2006</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <v>38827</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1745,7 +1783,7 @@
       <c r="E14" s="1">
         <v>2006</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <v>38827</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1777,7 +1815,7 @@
       <c r="E15" s="1">
         <v>2006</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <v>38827</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1809,7 +1847,7 @@
       <c r="E16" s="1">
         <v>2006</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <v>38827</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1841,7 +1879,7 @@
       <c r="E17" s="1">
         <v>2006</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <v>38827</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1873,7 +1911,7 @@
       <c r="E18" s="1">
         <v>2006</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <v>38827</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1905,7 +1943,7 @@
       <c r="E19" s="1">
         <v>2006</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <v>38827</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1937,7 +1975,7 @@
       <c r="E20" s="1">
         <v>2006</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="7">
         <v>38827</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1969,7 +2007,7 @@
       <c r="E21" s="1">
         <v>2006</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="7">
         <v>38827</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2001,7 +2039,7 @@
       <c r="E22" s="1">
         <v>2006</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="7">
         <v>38827</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2033,7 +2071,7 @@
       <c r="E23" s="1">
         <v>2006</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="7">
         <v>38827</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2065,7 +2103,7 @@
       <c r="E24" s="1">
         <v>2006</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="7">
         <v>38827</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2097,7 +2135,7 @@
       <c r="E25" s="1">
         <v>2006</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="7">
         <v>38827</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2129,7 +2167,7 @@
       <c r="E26" s="1">
         <v>2006</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="7">
         <v>38827</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2161,7 +2199,7 @@
       <c r="E27" s="1">
         <v>2006</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="7">
         <v>38827</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2193,7 +2231,7 @@
       <c r="E28" s="1">
         <v>2006</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="7">
         <v>38827</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2225,7 +2263,7 @@
       <c r="E29" s="1">
         <v>2006</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="7">
         <v>38827</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2257,7 +2295,7 @@
       <c r="E30" s="1">
         <v>2006</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="7">
         <v>38827</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2289,7 +2327,7 @@
       <c r="E31" s="1">
         <v>2006</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="7">
         <v>38827</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2321,7 +2359,7 @@
       <c r="E32" s="1">
         <v>2006</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="7">
         <v>38827</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2353,7 +2391,7 @@
       <c r="E33" s="1">
         <v>2007</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="7">
         <v>38789</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2385,7 +2423,7 @@
       <c r="E34" s="1">
         <v>2007</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="7">
         <v>38789</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2417,7 +2455,7 @@
       <c r="E35" s="1">
         <v>2007</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="7">
         <v>38789</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -2449,7 +2487,7 @@
       <c r="E36" s="1">
         <v>2007</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="7">
         <v>38789</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2481,7 +2519,7 @@
       <c r="E37" s="1">
         <v>2007</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="7">
         <v>38789</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2513,7 +2551,7 @@
       <c r="E38" s="1">
         <v>2007</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="7">
         <v>38789</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2545,7 +2583,7 @@
       <c r="E39" s="1">
         <v>2007</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="7">
         <v>38789</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -2577,7 +2615,7 @@
       <c r="E40" s="1">
         <v>2007</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="7">
         <v>38789</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -2609,7 +2647,7 @@
       <c r="E41" s="1">
         <v>2007</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="7">
         <v>38789</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -2641,7 +2679,7 @@
       <c r="E42" s="1">
         <v>2007</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="7">
         <v>38810</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -2673,7 +2711,7 @@
       <c r="E43" s="1">
         <v>2007</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="7">
         <v>38810</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -2705,7 +2743,7 @@
       <c r="E44" s="1">
         <v>2007</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="7">
         <v>38810</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -2737,7 +2775,7 @@
       <c r="E45" s="1">
         <v>2007</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="7">
         <v>38810</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -2769,7 +2807,7 @@
       <c r="E46" s="1">
         <v>2007</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="7">
         <v>38810</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2801,7 +2839,7 @@
       <c r="E47" s="1">
         <v>2007</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="7">
         <v>38810</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -2833,7 +2871,7 @@
       <c r="E48" s="1">
         <v>2007</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="7">
         <v>38810</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -2865,7 +2903,7 @@
       <c r="E49" s="1">
         <v>2007</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="7">
         <v>38810</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2897,7 +2935,7 @@
       <c r="E50" s="1">
         <v>2007</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="7">
         <v>38810</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -2929,7 +2967,7 @@
       <c r="E51" s="1">
         <v>2007</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="7">
         <v>38810</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -2961,7 +2999,7 @@
       <c r="E52" s="1">
         <v>2007</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="7">
         <v>38810</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -2993,7 +3031,7 @@
       <c r="E53" s="1">
         <v>2007</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="7">
         <v>38810</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -3025,7 +3063,7 @@
       <c r="E54" s="1">
         <v>2007</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="7">
         <v>38810</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -3057,7 +3095,7 @@
       <c r="E55" s="1">
         <v>2007</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="7">
         <v>38810</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3089,7 +3127,7 @@
       <c r="E56" s="1">
         <v>2007</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="7">
         <v>38810</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -3121,7 +3159,7 @@
       <c r="E57" s="1">
         <v>2007</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="7">
         <v>38810</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -3153,7 +3191,7 @@
       <c r="E58" s="1">
         <v>2007</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="7">
         <v>38810</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -3185,7 +3223,7 @@
       <c r="E59" s="1">
         <v>2007</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="7">
         <v>38810</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -3217,7 +3255,7 @@
       <c r="E60" s="1">
         <v>2007</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="7">
         <v>38810</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -3249,7 +3287,7 @@
       <c r="E61" s="1">
         <v>2007</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="7">
         <v>38810</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -3281,7 +3319,7 @@
       <c r="E62" s="1">
         <v>2007</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="7">
         <v>38810</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -3313,7 +3351,7 @@
       <c r="E63" s="1">
         <v>2007</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="7">
         <v>38810</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -3345,7 +3383,7 @@
       <c r="E64" s="1">
         <v>2007</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="7">
         <v>38810</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -3377,7 +3415,7 @@
       <c r="E65" s="1">
         <v>2007</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="7">
         <v>38824</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -3409,7 +3447,7 @@
       <c r="E66" s="1">
         <v>2007</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="7">
         <v>38824</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -3441,7 +3479,7 @@
       <c r="E67" s="1">
         <v>2007</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="7">
         <v>38824</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -3473,7 +3511,7 @@
       <c r="E68" s="1">
         <v>2007</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="7">
         <v>38824</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -3505,7 +3543,7 @@
       <c r="E69" s="1">
         <v>2007</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="7">
         <v>38824</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -3537,7 +3575,7 @@
       <c r="E70" s="1">
         <v>2007</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="7">
         <v>38824</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -3569,7 +3607,7 @@
       <c r="E71" s="1">
         <v>2007</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="7">
         <v>38824</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -3601,7 +3639,7 @@
       <c r="E72" s="1">
         <v>2007</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="7">
         <v>38824</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -3633,7 +3671,7 @@
       <c r="E73" s="1">
         <v>2007</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="7">
         <v>38824</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -3665,7 +3703,7 @@
       <c r="E74" s="1">
         <v>2007</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="7">
         <v>38824</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -3697,7 +3735,7 @@
       <c r="E75" s="1">
         <v>2007</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="7">
         <v>38824</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -3729,7 +3767,7 @@
       <c r="E76" s="1">
         <v>2007</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="7">
         <v>38824</v>
       </c>
       <c r="G76" s="1" t="s">
@@ -3761,7 +3799,7 @@
       <c r="E77" s="1">
         <v>2007</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="7">
         <v>38824</v>
       </c>
       <c r="G77" s="1" t="s">
@@ -3793,7 +3831,7 @@
       <c r="E78" s="1">
         <v>2007</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="7">
         <v>38824</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -3825,7 +3863,7 @@
       <c r="E79" s="1">
         <v>2007</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="7">
         <v>38824</v>
       </c>
       <c r="G79" s="1" t="s">
@@ -3857,7 +3895,7 @@
       <c r="E80" s="1">
         <v>2007</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="7">
         <v>38824</v>
       </c>
       <c r="G80" s="1" t="s">
@@ -3889,7 +3927,7 @@
       <c r="E81" s="1">
         <v>2007</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="7">
         <v>38824</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -3921,7 +3959,7 @@
       <c r="E82" s="1">
         <v>2007</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="7">
         <v>38824</v>
       </c>
       <c r="G82" s="1" t="s">
@@ -3953,7 +3991,7 @@
       <c r="E83" s="1">
         <v>2007</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="7">
         <v>38824</v>
       </c>
       <c r="G83" s="1" t="s">
@@ -3985,7 +4023,7 @@
       <c r="E84" s="1">
         <v>2007</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="7">
         <v>38824</v>
       </c>
       <c r="G84" s="1" t="s">
@@ -4017,7 +4055,7 @@
       <c r="E85" s="1">
         <v>2007</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="7">
         <v>38824</v>
       </c>
       <c r="G85" s="1" t="s">
@@ -4049,7 +4087,7 @@
       <c r="E86" s="1">
         <v>2007</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="7">
         <v>38824</v>
       </c>
       <c r="G86" s="1" t="s">
@@ -4081,7 +4119,7 @@
       <c r="E87" s="1">
         <v>2007</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="7">
         <v>38824</v>
       </c>
       <c r="G87" s="1" t="s">
@@ -4113,7 +4151,7 @@
       <c r="E88" s="1">
         <v>2007</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="7">
         <v>38824</v>
       </c>
       <c r="G88" s="1" t="s">
@@ -4145,7 +4183,7 @@
       <c r="E89" s="1">
         <v>2007</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="7">
         <v>38824</v>
       </c>
       <c r="G89" s="1" t="s">
@@ -4177,7 +4215,7 @@
       <c r="E90" s="1">
         <v>2007</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="7">
         <v>38824</v>
       </c>
       <c r="G90" s="1" t="s">
@@ -4209,7 +4247,7 @@
       <c r="E91" s="1">
         <v>2007</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="7">
         <v>38824</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -4241,7 +4279,7 @@
       <c r="E92" s="1">
         <v>2007</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="7">
         <v>38824</v>
       </c>
       <c r="G92" s="1" t="s">
@@ -4273,7 +4311,7 @@
       <c r="E93" s="1">
         <v>2007</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="7">
         <v>38824</v>
       </c>
       <c r="G93" s="1" t="s">
@@ -4305,7 +4343,7 @@
       <c r="E94" s="1">
         <v>2007</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="7">
         <v>38824</v>
       </c>
       <c r="G94" s="1" t="s">
@@ -4337,7 +4375,7 @@
       <c r="E95" s="1">
         <v>2007</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="7">
         <v>38824</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -4369,7 +4407,7 @@
       <c r="E96" s="1">
         <v>2007</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="7">
         <v>38824</v>
       </c>
       <c r="G96" s="1" t="s">
@@ -4401,7 +4439,7 @@
       <c r="E97" s="1">
         <v>2008</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="7">
         <v>38776</v>
       </c>
       <c r="G97" s="1" t="s">
@@ -4433,7 +4471,7 @@
       <c r="E98" s="1">
         <v>2008</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="7">
         <v>38776</v>
       </c>
       <c r="G98" s="1" t="s">
@@ -4465,7 +4503,7 @@
       <c r="E99" s="1">
         <v>2008</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="7">
         <v>38776</v>
       </c>
       <c r="G99" s="1" t="s">
@@ -4497,7 +4535,7 @@
       <c r="E100" s="1">
         <v>2008</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="7">
         <v>38776</v>
       </c>
       <c r="G100" s="1" t="s">
@@ -4529,7 +4567,7 @@
       <c r="E101" s="1">
         <v>2008</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="7">
         <v>38776</v>
       </c>
       <c r="G101" s="1" t="s">
@@ -4561,7 +4599,7 @@
       <c r="E102" s="1">
         <v>2008</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="7">
         <v>38776</v>
       </c>
       <c r="G102" s="1" t="s">
@@ -4593,7 +4631,7 @@
       <c r="E103" s="1">
         <v>2008</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="7">
         <v>38776</v>
       </c>
       <c r="G103" s="1" t="s">
@@ -4625,7 +4663,7 @@
       <c r="E104" s="1">
         <v>2008</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="7">
         <v>38776</v>
       </c>
       <c r="G104" s="1" t="s">
@@ -4657,7 +4695,7 @@
       <c r="E105" s="1">
         <v>2008</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="7">
         <v>38776</v>
       </c>
       <c r="G105" s="1" t="s">
@@ -4689,7 +4727,7 @@
       <c r="E106" s="1">
         <v>2008</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="7">
         <v>38776</v>
       </c>
       <c r="G106" s="1" t="s">
@@ -4721,7 +4759,7 @@
       <c r="E107" s="1">
         <v>2008</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="7">
         <v>38776</v>
       </c>
       <c r="G107" s="1" t="s">
@@ -4753,7 +4791,7 @@
       <c r="E108" s="1">
         <v>2008</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="7">
         <v>38776</v>
       </c>
       <c r="G108" s="1" t="s">
@@ -4785,7 +4823,7 @@
       <c r="E109" s="1">
         <v>2008</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="7">
         <v>38776</v>
       </c>
       <c r="G109" s="1" t="s">
@@ -4817,7 +4855,7 @@
       <c r="E110" s="1">
         <v>2008</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="7">
         <v>38776</v>
       </c>
       <c r="G110" s="1" t="s">
@@ -4849,7 +4887,7 @@
       <c r="E111" s="1">
         <v>2008</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="7">
         <v>38804</v>
       </c>
       <c r="G111" s="1" t="s">
@@ -4881,7 +4919,7 @@
       <c r="E112" s="1">
         <v>2008</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="7">
         <v>38804</v>
       </c>
       <c r="G112" s="1" t="s">
@@ -4913,7 +4951,7 @@
       <c r="E113" s="1">
         <v>2008</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="7">
         <v>38804</v>
       </c>
       <c r="G113" s="1" t="s">
@@ -4945,7 +4983,7 @@
       <c r="E114" s="1">
         <v>2008</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="7">
         <v>38804</v>
       </c>
       <c r="G114" s="1" t="s">
@@ -4977,7 +5015,7 @@
       <c r="E115" s="1">
         <v>2008</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="7">
         <v>38804</v>
       </c>
       <c r="G115" s="1" t="s">
@@ -5009,7 +5047,7 @@
       <c r="E116" s="1">
         <v>2008</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="7">
         <v>38804</v>
       </c>
       <c r="G116" s="1" t="s">
@@ -5041,7 +5079,7 @@
       <c r="E117" s="1">
         <v>2008</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="7">
         <v>38804</v>
       </c>
       <c r="G117" s="1" t="s">
@@ -5073,7 +5111,7 @@
       <c r="E118" s="1">
         <v>2008</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="7">
         <v>38804</v>
       </c>
       <c r="G118" s="1" t="s">
@@ -5105,7 +5143,7 @@
       <c r="E119" s="1">
         <v>2008</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="7">
         <v>38804</v>
       </c>
       <c r="G119" s="1" t="s">
@@ -5137,7 +5175,7 @@
       <c r="E120" s="1">
         <v>2008</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="7">
         <v>38804</v>
       </c>
       <c r="G120" s="1" t="s">
@@ -5169,7 +5207,7 @@
       <c r="E121" s="1">
         <v>2008</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="7">
         <v>38804</v>
       </c>
       <c r="G121" s="1" t="s">
@@ -5201,7 +5239,7 @@
       <c r="E122" s="1">
         <v>2008</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="7">
         <v>38804</v>
       </c>
       <c r="G122" s="1" t="s">
@@ -5233,7 +5271,7 @@
       <c r="E123" s="1">
         <v>2008</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="7">
         <v>38804</v>
       </c>
       <c r="G123" s="1" t="s">
@@ -5265,7 +5303,7 @@
       <c r="E124" s="1">
         <v>2008</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="7">
         <v>38804</v>
       </c>
       <c r="G124" s="1" t="s">
@@ -5297,7 +5335,7 @@
       <c r="E125" s="1">
         <v>2008</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="7">
         <v>38804</v>
       </c>
       <c r="G125" s="1" t="s">
@@ -5329,7 +5367,7 @@
       <c r="E126" s="1">
         <v>2008</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="7">
         <v>38804</v>
       </c>
       <c r="G126" s="1" t="s">
@@ -5361,7 +5399,7 @@
       <c r="E127" s="1">
         <v>2008</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="7">
         <v>38804</v>
       </c>
       <c r="G127" s="1" t="s">
@@ -5393,7 +5431,7 @@
       <c r="E128" s="1">
         <v>2008</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="7">
         <v>38804</v>
       </c>
       <c r="G128" s="1" t="s">
@@ -5425,7 +5463,7 @@
       <c r="E129" s="1">
         <v>2008</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="7">
         <v>38804</v>
       </c>
       <c r="G129" s="1" t="s">
@@ -5457,7 +5495,7 @@
       <c r="E130" s="1">
         <v>2008</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="7">
         <v>38804</v>
       </c>
       <c r="G130" s="1" t="s">
@@ -5489,7 +5527,7 @@
       <c r="E131" s="1">
         <v>2008</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="7">
         <v>38804</v>
       </c>
       <c r="G131" s="1" t="s">
@@ -5521,7 +5559,7 @@
       <c r="E132" s="1">
         <v>2008</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="7">
         <v>38804</v>
       </c>
       <c r="G132" s="1" t="s">
@@ -5553,7 +5591,7 @@
       <c r="E133" s="1">
         <v>2008</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="7">
         <v>38804</v>
       </c>
       <c r="G133" s="1" t="s">
@@ -5585,7 +5623,7 @@
       <c r="E134" s="1">
         <v>2008</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="7">
         <v>38825</v>
       </c>
       <c r="G134" s="1" t="s">
@@ -5617,7 +5655,7 @@
       <c r="E135" s="1">
         <v>2008</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="7">
         <v>38825</v>
       </c>
       <c r="G135" s="1" t="s">
@@ -5649,7 +5687,7 @@
       <c r="E136" s="1">
         <v>2008</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="7">
         <v>38825</v>
       </c>
       <c r="G136" s="1" t="s">
@@ -5681,7 +5719,7 @@
       <c r="E137" s="1">
         <v>2008</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="7">
         <v>38825</v>
       </c>
       <c r="G137" s="1" t="s">
@@ -5713,7 +5751,7 @@
       <c r="E138" s="1">
         <v>2008</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="7">
         <v>38825</v>
       </c>
       <c r="G138" s="1" t="s">
@@ -5745,7 +5783,7 @@
       <c r="E139" s="1">
         <v>2008</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="7">
         <v>38825</v>
       </c>
       <c r="G139" s="1" t="s">
@@ -5777,7 +5815,7 @@
       <c r="E140" s="1">
         <v>2008</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="7">
         <v>38825</v>
       </c>
       <c r="G140" s="1" t="s">
@@ -5809,7 +5847,7 @@
       <c r="E141" s="1">
         <v>2008</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="7">
         <v>38825</v>
       </c>
       <c r="G141" s="1" t="s">
@@ -5841,7 +5879,7 @@
       <c r="E142" s="1">
         <v>2008</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="7">
         <v>38825</v>
       </c>
       <c r="G142" s="1" t="s">
@@ -5873,7 +5911,7 @@
       <c r="E143" s="1">
         <v>2008</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="7">
         <v>38825</v>
       </c>
       <c r="G143" s="1" t="s">
@@ -5905,7 +5943,7 @@
       <c r="E144" s="1">
         <v>2008</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="7">
         <v>38825</v>
       </c>
       <c r="G144" s="1" t="s">
@@ -5937,7 +5975,7 @@
       <c r="E145" s="1">
         <v>2008</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="7">
         <v>38825</v>
       </c>
       <c r="G145" s="1" t="s">
@@ -5969,7 +6007,7 @@
       <c r="E146" s="1">
         <v>2008</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="7">
         <v>38825</v>
       </c>
       <c r="G146" s="1" t="s">
@@ -6001,7 +6039,7 @@
       <c r="E147" s="1">
         <v>2008</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="7">
         <v>38825</v>
       </c>
       <c r="G147" s="1" t="s">
@@ -6033,7 +6071,7 @@
       <c r="E148" s="1">
         <v>2008</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="7">
         <v>38825</v>
       </c>
       <c r="G148" s="1" t="s">
@@ -6065,7 +6103,7 @@
       <c r="E149" s="1">
         <v>2008</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="7">
         <v>38825</v>
       </c>
       <c r="G149" s="1" t="s">
@@ -6097,7 +6135,7 @@
       <c r="E150" s="1">
         <v>2008</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="7">
         <v>38825</v>
       </c>
       <c r="G150" s="1" t="s">
@@ -6129,7 +6167,7 @@
       <c r="E151" s="1">
         <v>2008</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="7">
         <v>38825</v>
       </c>
       <c r="G151" s="1" t="s">
@@ -6161,7 +6199,7 @@
       <c r="E152" s="1">
         <v>2008</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="7">
         <v>38825</v>
       </c>
       <c r="G152" s="1" t="s">
@@ -6193,7 +6231,7 @@
       <c r="E153" s="1">
         <v>2008</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="7">
         <v>38825</v>
       </c>
       <c r="G153" s="1" t="s">
@@ -6225,7 +6263,7 @@
       <c r="E154" s="1">
         <v>2008</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="7">
         <v>38825</v>
       </c>
       <c r="G154" s="1" t="s">
@@ -6257,7 +6295,7 @@
       <c r="E155" s="1">
         <v>2008</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="7">
         <v>38825</v>
       </c>
       <c r="G155" s="1" t="s">
@@ -6289,7 +6327,7 @@
       <c r="E156" s="1">
         <v>2008</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="7">
         <v>38825</v>
       </c>
       <c r="G156" s="1" t="s">
@@ -6321,7 +6359,7 @@
       <c r="E157" s="1">
         <v>2008</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="7">
         <v>38825</v>
       </c>
       <c r="G157" s="1" t="s">
@@ -6353,7 +6391,7 @@
       <c r="E158" s="1">
         <v>2008</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="7">
         <v>38825</v>
       </c>
       <c r="G158" s="1" t="s">
@@ -6385,7 +6423,7 @@
       <c r="E159" s="1">
         <v>2008</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="7">
         <v>38825</v>
       </c>
       <c r="G159" s="1" t="s">
@@ -6417,7 +6455,7 @@
       <c r="E160" s="1">
         <v>2009</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="7">
         <v>38804</v>
       </c>
       <c r="G160" s="1" t="s">
@@ -6449,7 +6487,7 @@
       <c r="E161" s="1">
         <v>2009</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="7">
         <v>38804</v>
       </c>
       <c r="G161" s="1" t="s">
@@ -6481,7 +6519,7 @@
       <c r="E162" s="1">
         <v>2009</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="7">
         <v>38804</v>
       </c>
       <c r="G162" s="1" t="s">
@@ -6513,7 +6551,7 @@
       <c r="E163" s="1">
         <v>2009</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="7">
         <v>38804</v>
       </c>
       <c r="G163" s="1" t="s">
@@ -6545,7 +6583,7 @@
       <c r="E164" s="1">
         <v>2009</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="7">
         <v>38804</v>
       </c>
       <c r="G164" s="1" t="s">
@@ -6577,7 +6615,7 @@
       <c r="E165" s="1">
         <v>2009</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="7">
         <v>38804</v>
       </c>
       <c r="G165" s="1" t="s">
@@ -6609,7 +6647,7 @@
       <c r="E166" s="1">
         <v>2009</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="7">
         <v>38804</v>
       </c>
       <c r="G166" s="1" t="s">
@@ -6641,7 +6679,7 @@
       <c r="E167" s="1">
         <v>2009</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="7">
         <v>38804</v>
       </c>
       <c r="G167" s="1" t="s">
@@ -6673,7 +6711,7 @@
       <c r="E168" s="1">
         <v>2009</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="7">
         <v>38804</v>
       </c>
       <c r="G168" s="1" t="s">
@@ -6705,7 +6743,7 @@
       <c r="E169" s="1">
         <v>2009</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="7">
         <v>38804</v>
       </c>
       <c r="G169" s="1" t="s">
@@ -6737,7 +6775,7 @@
       <c r="E170" s="1">
         <v>2009</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="7">
         <v>38804</v>
       </c>
       <c r="G170" s="1" t="s">
@@ -6769,7 +6807,7 @@
       <c r="E171" s="1">
         <v>2009</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="7">
         <v>38804</v>
       </c>
       <c r="G171" s="1" t="s">
@@ -6801,7 +6839,7 @@
       <c r="E172" s="1">
         <v>2009</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="7">
         <v>38804</v>
       </c>
       <c r="G172" s="1" t="s">
@@ -6833,7 +6871,7 @@
       <c r="E173" s="1">
         <v>2009</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="7">
         <v>38813</v>
       </c>
       <c r="G173" s="1" t="s">
@@ -6865,7 +6903,7 @@
       <c r="E174" s="1">
         <v>2009</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="7">
         <v>38813</v>
       </c>
       <c r="G174" s="1" t="s">
@@ -6897,7 +6935,7 @@
       <c r="E175" s="1">
         <v>2009</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="7">
         <v>38813</v>
       </c>
       <c r="G175" s="1" t="s">
@@ -6929,7 +6967,7 @@
       <c r="E176" s="1">
         <v>2009</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="7">
         <v>38813</v>
       </c>
       <c r="G176" s="1" t="s">
@@ -6961,7 +6999,7 @@
       <c r="E177" s="1">
         <v>2009</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="7">
         <v>38813</v>
       </c>
       <c r="G177" s="1" t="s">
@@ -6993,7 +7031,7 @@
       <c r="E178" s="1">
         <v>2009</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="7">
         <v>38813</v>
       </c>
       <c r="G178" s="1" t="s">
@@ -7025,7 +7063,7 @@
       <c r="E179" s="1">
         <v>2009</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="7">
         <v>38813</v>
       </c>
       <c r="G179" s="1" t="s">
@@ -7057,7 +7095,7 @@
       <c r="E180" s="1">
         <v>2009</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="7">
         <v>38813</v>
       </c>
       <c r="G180" s="1" t="s">
@@ -7089,7 +7127,7 @@
       <c r="E181" s="1">
         <v>2009</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="7">
         <v>38813</v>
       </c>
       <c r="G181" s="1" t="s">
@@ -7121,7 +7159,7 @@
       <c r="E182" s="1">
         <v>2009</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="7">
         <v>38813</v>
       </c>
       <c r="G182" s="1" t="s">
@@ -7153,7 +7191,7 @@
       <c r="E183" s="1">
         <v>2009</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="7">
         <v>38813</v>
       </c>
       <c r="G183" s="1" t="s">
@@ -7185,7 +7223,7 @@
       <c r="E184" s="1">
         <v>2009</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="7">
         <v>38813</v>
       </c>
       <c r="G184" s="1" t="s">
@@ -7217,7 +7255,7 @@
       <c r="E185" s="1">
         <v>2009</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="7">
         <v>38813</v>
       </c>
       <c r="G185" s="1" t="s">
@@ -7249,7 +7287,7 @@
       <c r="E186" s="1">
         <v>2009</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="7">
         <v>38813</v>
       </c>
       <c r="G186" s="1" t="s">
@@ -7281,7 +7319,7 @@
       <c r="E187" s="1">
         <v>2009</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="7">
         <v>38813</v>
       </c>
       <c r="G187" s="1" t="s">
@@ -7313,7 +7351,7 @@
       <c r="E188" s="1">
         <v>2009</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="7">
         <v>38813</v>
       </c>
       <c r="G188" s="1" t="s">
@@ -7345,7 +7383,7 @@
       <c r="E189" s="1">
         <v>2009</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="7">
         <v>38813</v>
       </c>
       <c r="G189" s="1" t="s">
@@ -7377,7 +7415,7 @@
       <c r="E190" s="1">
         <v>2009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="7">
         <v>38813</v>
       </c>
       <c r="G190" s="1" t="s">
@@ -7409,7 +7447,7 @@
       <c r="E191" s="1">
         <v>2009</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="7">
         <v>38813</v>
       </c>
       <c r="G191" s="1" t="s">
@@ -7441,7 +7479,7 @@
       <c r="E192" s="1">
         <v>2009</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="7">
         <v>38813</v>
       </c>
       <c r="G192" s="1" t="s">
@@ -7473,7 +7511,7 @@
       <c r="E193" s="1">
         <v>2009</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="7">
         <v>38813</v>
       </c>
       <c r="G193" s="1" t="s">
@@ -7505,7 +7543,7 @@
       <c r="E194" s="1">
         <v>2009</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="7">
         <v>38813</v>
       </c>
       <c r="G194" s="1" t="s">
@@ -7537,7 +7575,7 @@
       <c r="E195" s="1">
         <v>2009</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="7">
         <v>38813</v>
       </c>
       <c r="G195" s="1" t="s">
@@ -7569,7 +7607,7 @@
       <c r="E196" s="1">
         <v>2009</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="7">
         <v>38813</v>
       </c>
       <c r="G196" s="1" t="s">
@@ -7601,7 +7639,7 @@
       <c r="E197" s="1">
         <v>2009</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="7">
         <v>38825</v>
       </c>
       <c r="G197" s="1" t="s">
@@ -7633,7 +7671,7 @@
       <c r="E198" s="1">
         <v>2009</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="7">
         <v>38825</v>
       </c>
       <c r="G198" s="1" t="s">
@@ -7665,7 +7703,7 @@
       <c r="E199" s="1">
         <v>2009</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="7">
         <v>38825</v>
       </c>
       <c r="G199" s="1" t="s">
@@ -7697,7 +7735,7 @@
       <c r="E200" s="1">
         <v>2009</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="7">
         <v>38825</v>
       </c>
       <c r="G200" s="1" t="s">
@@ -7729,7 +7767,7 @@
       <c r="E201" s="1">
         <v>2009</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="7">
         <v>38825</v>
       </c>
       <c r="G201" s="1" t="s">
@@ -7761,7 +7799,7 @@
       <c r="E202" s="1">
         <v>2009</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="7">
         <v>38825</v>
       </c>
       <c r="G202" s="1" t="s">
@@ -7793,7 +7831,7 @@
       <c r="E203" s="1">
         <v>2009</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="7">
         <v>38825</v>
       </c>
       <c r="G203" s="1" t="s">
@@ -7825,7 +7863,7 @@
       <c r="E204" s="1">
         <v>2009</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="7">
         <v>38825</v>
       </c>
       <c r="G204" s="1" t="s">
@@ -7857,7 +7895,7 @@
       <c r="E205" s="1">
         <v>2009</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="7">
         <v>38825</v>
       </c>
       <c r="G205" s="1" t="s">
@@ -7889,7 +7927,7 @@
       <c r="E206" s="1">
         <v>2009</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="7">
         <v>38825</v>
       </c>
       <c r="G206" s="1" t="s">
@@ -7921,7 +7959,7 @@
       <c r="E207" s="1">
         <v>2009</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="7">
         <v>38825</v>
       </c>
       <c r="G207" s="1" t="s">
@@ -7953,7 +7991,7 @@
       <c r="E208" s="1">
         <v>2009</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="7">
         <v>38825</v>
       </c>
       <c r="G208" s="1" t="s">
@@ -7985,7 +8023,7 @@
       <c r="E209" s="1">
         <v>2009</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="7">
         <v>38825</v>
       </c>
       <c r="G209" s="1" t="s">
@@ -8017,7 +8055,7 @@
       <c r="E210" s="1">
         <v>2009</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="7">
         <v>38825</v>
       </c>
       <c r="G210" s="1" t="s">
@@ -8049,7 +8087,7 @@
       <c r="E211" s="1">
         <v>2009</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="7">
         <v>38825</v>
       </c>
       <c r="G211" s="1" t="s">
@@ -8081,7 +8119,7 @@
       <c r="E212" s="1">
         <v>2009</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="7">
         <v>38825</v>
       </c>
       <c r="G212" s="1" t="s">
@@ -8113,7 +8151,7 @@
       <c r="E213" s="1">
         <v>2009</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="7">
         <v>38825</v>
       </c>
       <c r="G213" s="1" t="s">
@@ -8145,7 +8183,7 @@
       <c r="E214" s="1">
         <v>2009</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="7">
         <v>38825</v>
       </c>
       <c r="G214" s="1" t="s">
@@ -8177,7 +8215,7 @@
       <c r="E215" s="1">
         <v>2009</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="7">
         <v>38825</v>
       </c>
       <c r="G215" s="1" t="s">
@@ -8209,7 +8247,7 @@
       <c r="E216" s="1">
         <v>2009</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="7">
         <v>38825</v>
       </c>
       <c r="G216" s="1" t="s">
@@ -8241,7 +8279,7 @@
       <c r="E217" s="1">
         <v>2009</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="7">
         <v>38825</v>
       </c>
       <c r="G217" s="1" t="s">
@@ -8273,7 +8311,7 @@
       <c r="E218" s="1">
         <v>2009</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="7">
         <v>38825</v>
       </c>
       <c r="G218" s="1" t="s">
@@ -8305,7 +8343,7 @@
       <c r="E219" s="1">
         <v>2009</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="7">
         <v>38825</v>
       </c>
       <c r="G219" s="1" t="s">
@@ -8337,7 +8375,7 @@
       <c r="E220" s="1">
         <v>2009</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="7">
         <v>38825</v>
       </c>
       <c r="G220" s="1" t="s">
@@ -8369,7 +8407,7 @@
       <c r="E221" s="1">
         <v>2009</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="7">
         <v>38825</v>
       </c>
       <c r="G221" s="1" t="s">
@@ -8401,7 +8439,7 @@
       <c r="E222" s="1">
         <v>2009</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="7">
         <v>38825</v>
       </c>
       <c r="G222" s="1" t="s">
@@ -8433,7 +8471,7 @@
       <c r="E223" s="1">
         <v>2009</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="7">
         <v>38825</v>
       </c>
       <c r="G223" s="1" t="s">
@@ -8465,7 +8503,7 @@
       <c r="E224" s="1">
         <v>2009</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="7">
         <v>38825</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -8497,7 +8535,7 @@
       <c r="E225" s="1">
         <v>2010</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="7">
         <v>38813</v>
       </c>
       <c r="G225" s="1" t="s">
@@ -8529,7 +8567,7 @@
       <c r="E226" s="1">
         <v>2010</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="7">
         <v>38813</v>
       </c>
       <c r="G226" s="1" t="s">
@@ -8561,7 +8599,7 @@
       <c r="E227" s="1">
         <v>2010</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="7">
         <v>38813</v>
       </c>
       <c r="G227" s="1" t="s">
@@ -8593,7 +8631,7 @@
       <c r="E228" s="1">
         <v>2010</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="7">
         <v>38813</v>
       </c>
       <c r="G228" s="1" t="s">
@@ -8616,14 +8654,13 @@
       <c r="B229" s="1">
         <v>1</v>
       </c>
-      <c r="C229" s="1"/>
       <c r="D229" s="1">
         <v>1</v>
       </c>
       <c r="E229" s="1">
         <v>2010</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="7">
         <v>38813</v>
       </c>
       <c r="G229" s="1" t="s">
@@ -8655,7 +8692,7 @@
       <c r="E230" s="1">
         <v>2010</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="7">
         <v>38813</v>
       </c>
       <c r="G230" s="1" t="s">
@@ -8687,7 +8724,7 @@
       <c r="E231" s="1">
         <v>2010</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="7">
         <v>38813</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -8719,7 +8756,7 @@
       <c r="E232" s="1">
         <v>2010</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="7">
         <v>38813</v>
       </c>
       <c r="G232" s="1" t="s">
@@ -8751,7 +8788,7 @@
       <c r="E233" s="1">
         <v>2010</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="7">
         <v>38813</v>
       </c>
       <c r="G233" s="1" t="s">
@@ -8783,7 +8820,7 @@
       <c r="E234" s="1">
         <v>2010</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="7">
         <v>38813</v>
       </c>
       <c r="G234" s="1" t="s">
@@ -8815,7 +8852,7 @@
       <c r="E235" s="1">
         <v>2010</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="7">
         <v>38813</v>
       </c>
       <c r="G235" s="1" t="s">
@@ -8847,7 +8884,7 @@
       <c r="E236" s="1">
         <v>2010</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="7">
         <v>38813</v>
       </c>
       <c r="G236" s="1" t="s">
@@ -8879,7 +8916,7 @@
       <c r="E237" s="1">
         <v>2010</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="7">
         <v>38813</v>
       </c>
       <c r="G237" s="1" t="s">
@@ -8911,7 +8948,7 @@
       <c r="E238" s="1">
         <v>2010</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="7">
         <v>38813</v>
       </c>
       <c r="G238" s="1" t="s">
@@ -8943,7 +8980,7 @@
       <c r="E239" s="1">
         <v>2010</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="7">
         <v>38819</v>
       </c>
       <c r="G239" s="1" t="s">
@@ -8975,7 +9012,7 @@
       <c r="E240" s="1">
         <v>2010</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="7">
         <v>38819</v>
       </c>
       <c r="G240" s="1" t="s">
@@ -9007,7 +9044,7 @@
       <c r="E241" s="1">
         <v>2010</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="7">
         <v>38819</v>
       </c>
       <c r="G241" s="1" t="s">
@@ -9039,7 +9076,7 @@
       <c r="E242" s="1">
         <v>2010</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="7">
         <v>38819</v>
       </c>
       <c r="G242" s="1" t="s">
@@ -9071,7 +9108,7 @@
       <c r="E243" s="1">
         <v>2010</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="7">
         <v>38819</v>
       </c>
       <c r="G243" s="1" t="s">
@@ -9103,7 +9140,7 @@
       <c r="E244" s="1">
         <v>2010</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="7">
         <v>38819</v>
       </c>
       <c r="G244" s="1" t="s">
@@ -9135,7 +9172,7 @@
       <c r="E245" s="1">
         <v>2010</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="7">
         <v>38819</v>
       </c>
       <c r="G245" s="1" t="s">
@@ -9167,7 +9204,7 @@
       <c r="E246" s="1">
         <v>2010</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="7">
         <v>38819</v>
       </c>
       <c r="G246" s="1" t="s">
@@ -9199,7 +9236,7 @@
       <c r="E247" s="1">
         <v>2010</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="7">
         <v>38819</v>
       </c>
       <c r="G247" s="1" t="s">
@@ -9231,7 +9268,7 @@
       <c r="E248" s="1">
         <v>2010</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="7">
         <v>38819</v>
       </c>
       <c r="G248" s="1" t="s">
@@ -9263,7 +9300,7 @@
       <c r="E249" s="1">
         <v>2010</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="7">
         <v>38819</v>
       </c>
       <c r="G249" s="1" t="s">
@@ -9295,7 +9332,7 @@
       <c r="E250" s="1">
         <v>2010</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="7">
         <v>38819</v>
       </c>
       <c r="G250" s="1" t="s">
@@ -9327,7 +9364,7 @@
       <c r="E251" s="1">
         <v>2010</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="7">
         <v>38819</v>
       </c>
       <c r="G251" s="1" t="s">
@@ -9359,7 +9396,7 @@
       <c r="E252" s="1">
         <v>2010</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="7">
         <v>38819</v>
       </c>
       <c r="G252" s="1" t="s">
@@ -9391,7 +9428,7 @@
       <c r="E253" s="1">
         <v>2010</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="7">
         <v>38819</v>
       </c>
       <c r="G253" s="1" t="s">
@@ -9423,7 +9460,7 @@
       <c r="E254" s="1">
         <v>2010</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="7">
         <v>38819</v>
       </c>
       <c r="G254" s="1" t="s">
@@ -9455,7 +9492,7 @@
       <c r="E255" s="1">
         <v>2010</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="7">
         <v>38830</v>
       </c>
       <c r="G255" s="1" t="s">
@@ -9487,7 +9524,7 @@
       <c r="E256" s="1">
         <v>2010</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="7">
         <v>38830</v>
       </c>
       <c r="G256" s="1" t="s">
@@ -9519,7 +9556,7 @@
       <c r="E257" s="1">
         <v>2010</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="7">
         <v>38830</v>
       </c>
       <c r="G257" s="1" t="s">
@@ -9551,7 +9588,7 @@
       <c r="E258" s="1">
         <v>2010</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="7">
         <v>38830</v>
       </c>
       <c r="G258" s="1" t="s">
@@ -9583,7 +9620,7 @@
       <c r="E259" s="1">
         <v>2010</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="7">
         <v>38830</v>
       </c>
       <c r="G259" s="1" t="s">
@@ -9615,7 +9652,7 @@
       <c r="E260" s="1">
         <v>2010</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="7">
         <v>38830</v>
       </c>
       <c r="G260" s="1" t="s">
@@ -9647,7 +9684,7 @@
       <c r="E261" s="1">
         <v>2010</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="7">
         <v>38830</v>
       </c>
       <c r="G261" s="1" t="s">
@@ -9679,7 +9716,7 @@
       <c r="E262" s="1">
         <v>2010</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="7">
         <v>38830</v>
       </c>
       <c r="G262" s="1" t="s">
@@ -9711,7 +9748,7 @@
       <c r="E263" s="1">
         <v>2010</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="7">
         <v>38830</v>
       </c>
       <c r="G263" s="1" t="s">
@@ -9743,7 +9780,7 @@
       <c r="E264" s="1">
         <v>2010</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="7">
         <v>38830</v>
       </c>
       <c r="G264" s="1" t="s">
@@ -9775,7 +9812,7 @@
       <c r="E265" s="1">
         <v>2010</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="7">
         <v>38830</v>
       </c>
       <c r="G265" s="1" t="s">
@@ -9807,7 +9844,7 @@
       <c r="E266" s="1">
         <v>2010</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="7">
         <v>38830</v>
       </c>
       <c r="G266" s="1" t="s">
@@ -9839,7 +9876,7 @@
       <c r="E267" s="1">
         <v>2010</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="7">
         <v>38830</v>
       </c>
       <c r="G267" s="1" t="s">
@@ -9871,7 +9908,7 @@
       <c r="E268" s="1">
         <v>2010</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="7">
         <v>38830</v>
       </c>
       <c r="G268" s="1" t="s">
@@ -9903,7 +9940,7 @@
       <c r="E269" s="1">
         <v>2010</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="7">
         <v>38830</v>
       </c>
       <c r="G269" s="1" t="s">
@@ -9935,7 +9972,7 @@
       <c r="E270" s="1">
         <v>2010</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="7">
         <v>38830</v>
       </c>
       <c r="G270" s="1" t="s">
@@ -9967,7 +10004,7 @@
       <c r="E271" s="1">
         <v>2010</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="7">
         <v>38830</v>
       </c>
       <c r="G271" s="1" t="s">
@@ -9999,7 +10036,7 @@
       <c r="E272" s="1">
         <v>2010</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="7">
         <v>38830</v>
       </c>
       <c r="G272" s="1" t="s">
@@ -10031,7 +10068,7 @@
       <c r="E273" s="1">
         <v>2010</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="7">
         <v>38830</v>
       </c>
       <c r="G273" s="1" t="s">
@@ -10063,7 +10100,7 @@
       <c r="E274" s="1">
         <v>2010</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="7">
         <v>38830</v>
       </c>
       <c r="G274" s="1" t="s">
@@ -10095,7 +10132,7 @@
       <c r="E275" s="1">
         <v>2010</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="7">
         <v>38830</v>
       </c>
       <c r="G275" s="1" t="s">
@@ -10127,7 +10164,7 @@
       <c r="E276" s="1">
         <v>2010</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="7">
         <v>38830</v>
       </c>
       <c r="G276" s="1" t="s">
@@ -10159,7 +10196,7 @@
       <c r="E277" s="1">
         <v>2010</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="7">
         <v>38830</v>
       </c>
       <c r="G277" s="1" t="s">
@@ -10191,7 +10228,7 @@
       <c r="E278" s="1">
         <v>2010</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="7">
         <v>38830</v>
       </c>
       <c r="G278" s="1" t="s">
@@ -10223,7 +10260,7 @@
       <c r="E279" s="1">
         <v>2010</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="7">
         <v>38830</v>
       </c>
       <c r="G279" s="1" t="s">
@@ -10255,7 +10292,7 @@
       <c r="E280" s="1">
         <v>2010</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="7">
         <v>38830</v>
       </c>
       <c r="G280" s="1" t="s">
@@ -10287,7 +10324,7 @@
       <c r="E281" s="1">
         <v>2011</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="7">
         <v>38821</v>
       </c>
       <c r="G281" s="1" t="s">
@@ -10319,7 +10356,7 @@
       <c r="E282" s="1">
         <v>2011</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="7">
         <v>38821</v>
       </c>
       <c r="G282" s="1" t="s">
@@ -10351,7 +10388,7 @@
       <c r="E283" s="1">
         <v>2011</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="7">
         <v>38821</v>
       </c>
       <c r="G283" s="1" t="s">
@@ -10383,7 +10420,7 @@
       <c r="E284" s="1">
         <v>2011</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="7">
         <v>38821</v>
       </c>
       <c r="G284" s="1" t="s">
@@ -10415,7 +10452,7 @@
       <c r="E285" s="1">
         <v>2011</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="7">
         <v>38821</v>
       </c>
       <c r="G285" s="1" t="s">
@@ -10447,7 +10484,7 @@
       <c r="E286" s="1">
         <v>2011</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="7">
         <v>38821</v>
       </c>
       <c r="G286" s="1" t="s">
@@ -10479,7 +10516,7 @@
       <c r="E287" s="1">
         <v>2011</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="7">
         <v>38821</v>
       </c>
       <c r="G287" s="1" t="s">
@@ -10511,7 +10548,7 @@
       <c r="E288" s="1">
         <v>2011</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="7">
         <v>38821</v>
       </c>
       <c r="G288" s="1" t="s">
@@ -10543,7 +10580,7 @@
       <c r="E289" s="1">
         <v>2011</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="7">
         <v>38821</v>
       </c>
       <c r="G289" s="1" t="s">
@@ -10575,7 +10612,7 @@
       <c r="E290" s="1">
         <v>2011</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="7">
         <v>38821</v>
       </c>
       <c r="G290" s="1" t="s">
@@ -10607,7 +10644,7 @@
       <c r="E291" s="1">
         <v>2011</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="7">
         <v>38832</v>
       </c>
       <c r="G291" s="1" t="s">
@@ -10639,7 +10676,7 @@
       <c r="E292" s="1">
         <v>2011</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="7">
         <v>38832</v>
       </c>
       <c r="G292" s="1" t="s">
@@ -10671,7 +10708,7 @@
       <c r="E293" s="1">
         <v>2011</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="7">
         <v>38832</v>
       </c>
       <c r="G293" s="1" t="s">
@@ -10703,7 +10740,7 @@
       <c r="E294" s="1">
         <v>2011</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="7">
         <v>38832</v>
       </c>
       <c r="G294" s="1" t="s">
@@ -10735,7 +10772,7 @@
       <c r="E295" s="1">
         <v>2011</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="7">
         <v>38832</v>
       </c>
       <c r="G295" s="1" t="s">
@@ -10767,7 +10804,7 @@
       <c r="E296" s="1">
         <v>2011</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="7">
         <v>38832</v>
       </c>
       <c r="G296" s="1" t="s">
@@ -10799,7 +10836,7 @@
       <c r="E297" s="1">
         <v>2011</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="7">
         <v>38832</v>
       </c>
       <c r="G297" s="1" t="s">
@@ -10831,7 +10868,7 @@
       <c r="E298" s="1">
         <v>2011</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="7">
         <v>38832</v>
       </c>
       <c r="G298" s="1" t="s">
@@ -10863,7 +10900,7 @@
       <c r="E299" s="1">
         <v>2011</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="7">
         <v>38832</v>
       </c>
       <c r="G299" s="1" t="s">
@@ -10895,7 +10932,7 @@
       <c r="E300" s="1">
         <v>2011</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="7">
         <v>38832</v>
       </c>
       <c r="G300" s="1" t="s">
@@ -10927,7 +10964,7 @@
       <c r="E301" s="1">
         <v>2011</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="7">
         <v>38832</v>
       </c>
       <c r="G301" s="1" t="s">
@@ -10959,7 +10996,7 @@
       <c r="E302" s="1">
         <v>2011</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="7">
         <v>38832</v>
       </c>
       <c r="G302" s="1" t="s">
@@ -10991,7 +11028,7 @@
       <c r="E303" s="1">
         <v>2011</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="7">
         <v>38832</v>
       </c>
       <c r="G303" s="1" t="s">
@@ -11023,7 +11060,7 @@
       <c r="E304" s="1">
         <v>2011</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="7">
         <v>38832</v>
       </c>
       <c r="G304" s="1" t="s">
@@ -11055,7 +11092,7 @@
       <c r="E305" s="1">
         <v>2011</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="7">
         <v>38832</v>
       </c>
       <c r="G305" s="1" t="s">
@@ -11087,7 +11124,7 @@
       <c r="E306" s="1">
         <v>2011</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="7">
         <v>38832</v>
       </c>
       <c r="G306" s="1" t="s">
@@ -11119,7 +11156,7 @@
       <c r="E307" s="1">
         <v>2011</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="7">
         <v>38832</v>
       </c>
       <c r="G307" s="1" t="s">
@@ -11151,7 +11188,7 @@
       <c r="E308" s="1">
         <v>2011</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="7">
         <v>38832</v>
       </c>
       <c r="G308" s="1" t="s">
@@ -11183,7 +11220,7 @@
       <c r="E309" s="1">
         <v>2011</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="7">
         <v>38832</v>
       </c>
       <c r="G309" s="1" t="s">
@@ -11215,7 +11252,7 @@
       <c r="E310" s="1">
         <v>2011</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="7">
         <v>38832</v>
       </c>
       <c r="G310" s="1" t="s">
@@ -11247,7 +11284,7 @@
       <c r="E311" s="1">
         <v>2011</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="7">
         <v>38832</v>
       </c>
       <c r="G311" s="1" t="s">
@@ -11279,7 +11316,7 @@
       <c r="E312" s="1">
         <v>2011</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="7">
         <v>38839</v>
       </c>
       <c r="G312" s="1" t="s">
@@ -11311,7 +11348,7 @@
       <c r="E313" s="1">
         <v>2011</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="7">
         <v>38839</v>
       </c>
       <c r="G313" s="1" t="s">
@@ -11343,7 +11380,7 @@
       <c r="E314" s="1">
         <v>2011</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="7">
         <v>38839</v>
       </c>
       <c r="G314" s="1" t="s">
@@ -11375,7 +11412,7 @@
       <c r="E315" s="1">
         <v>2011</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="7">
         <v>38839</v>
       </c>
       <c r="G315" s="1" t="s">
@@ -11407,7 +11444,7 @@
       <c r="E316" s="1">
         <v>2011</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="7">
         <v>38839</v>
       </c>
       <c r="G316" s="1" t="s">
@@ -11439,7 +11476,7 @@
       <c r="E317" s="1">
         <v>2011</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="7">
         <v>38839</v>
       </c>
       <c r="G317" s="1" t="s">
@@ -11471,7 +11508,7 @@
       <c r="E318" s="1">
         <v>2011</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="7">
         <v>38839</v>
       </c>
       <c r="G318" s="1" t="s">
@@ -11503,7 +11540,7 @@
       <c r="E319" s="1">
         <v>2011</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="7">
         <v>38839</v>
       </c>
       <c r="G319" s="1" t="s">
@@ -11535,7 +11572,7 @@
       <c r="E320" s="1">
         <v>2011</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="7">
         <v>38839</v>
       </c>
       <c r="G320" s="1" t="s">
@@ -11567,7 +11604,7 @@
       <c r="E321" s="1">
         <v>2011</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="7">
         <v>38839</v>
       </c>
       <c r="G321" s="1" t="s">
@@ -11599,7 +11636,7 @@
       <c r="E322" s="1">
         <v>2011</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="7">
         <v>38839</v>
       </c>
       <c r="G322" s="1" t="s">
@@ -11631,7 +11668,7 @@
       <c r="E323" s="1">
         <v>2011</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="7">
         <v>38839</v>
       </c>
       <c r="G323" s="1" t="s">
@@ -11663,7 +11700,7 @@
       <c r="E324" s="1">
         <v>2011</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="7">
         <v>38839</v>
       </c>
       <c r="G324" s="1" t="s">
@@ -11695,7 +11732,7 @@
       <c r="E325" s="1">
         <v>2011</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="7">
         <v>38839</v>
       </c>
       <c r="G325" s="1" t="s">
@@ -11727,7 +11764,7 @@
       <c r="E326" s="1">
         <v>2011</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="7">
         <v>38839</v>
       </c>
       <c r="G326" s="1" t="s">
@@ -11759,7 +11796,7 @@
       <c r="E327" s="1">
         <v>2011</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="7">
         <v>38839</v>
       </c>
       <c r="G327" s="1" t="s">
@@ -11791,7 +11828,7 @@
       <c r="E328" s="1">
         <v>2011</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="7">
         <v>38839</v>
       </c>
       <c r="G328" s="1" t="s">
@@ -11823,7 +11860,7 @@
       <c r="E329" s="1">
         <v>2011</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="7">
         <v>38839</v>
       </c>
       <c r="G329" s="1" t="s">
@@ -11855,7 +11892,7 @@
       <c r="E330" s="1">
         <v>2011</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="7">
         <v>38839</v>
       </c>
       <c r="G330" s="1" t="s">
@@ -11887,7 +11924,7 @@
       <c r="E331" s="1">
         <v>2011</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="7">
         <v>38839</v>
       </c>
       <c r="G331" s="1" t="s">
@@ -11919,7 +11956,7 @@
       <c r="E332" s="1">
         <v>2011</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="7">
         <v>38839</v>
       </c>
       <c r="G332" s="1" t="s">
@@ -11951,7 +11988,7 @@
       <c r="E333" s="1">
         <v>2011</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="7">
         <v>38839</v>
       </c>
       <c r="G333" s="1" t="s">
@@ -11983,7 +12020,7 @@
       <c r="E334" s="1">
         <v>2011</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="7">
         <v>38839</v>
       </c>
       <c r="G334" s="1" t="s">
@@ -12015,7 +12052,7 @@
       <c r="E335" s="1">
         <v>2012</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="7">
         <v>38821</v>
       </c>
       <c r="G335" s="1" t="s">
@@ -12047,7 +12084,7 @@
       <c r="E336" s="1">
         <v>2012</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="7">
         <v>38821</v>
       </c>
       <c r="G336" s="1" t="s">
@@ -12079,7 +12116,7 @@
       <c r="E337" s="1">
         <v>2012</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="7">
         <v>38821</v>
       </c>
       <c r="G337" s="1" t="s">
@@ -12111,7 +12148,7 @@
       <c r="E338" s="1">
         <v>2012</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="7">
         <v>38821</v>
       </c>
       <c r="G338" s="1" t="s">
@@ -12143,7 +12180,7 @@
       <c r="E339" s="1">
         <v>2012</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="7">
         <v>38821</v>
       </c>
       <c r="G339" s="1" t="s">
@@ -12175,7 +12212,7 @@
       <c r="E340" s="1">
         <v>2012</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="7">
         <v>38821</v>
       </c>
       <c r="G340" s="1" t="s">
@@ -12207,7 +12244,7 @@
       <c r="E341" s="1">
         <v>2012</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="7">
         <v>38821</v>
       </c>
       <c r="G341" s="1" t="s">
@@ -12239,7 +12276,7 @@
       <c r="E342" s="1">
         <v>2012</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="7">
         <v>38821</v>
       </c>
       <c r="G342" s="1" t="s">
@@ -12271,7 +12308,7 @@
       <c r="E343" s="1">
         <v>2012</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="7">
         <v>38821</v>
       </c>
       <c r="G343" s="1" t="s">
@@ -12303,7 +12340,7 @@
       <c r="E344" s="1">
         <v>2012</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="7">
         <v>38821</v>
       </c>
       <c r="G344" s="1" t="s">
@@ -12335,7 +12372,7 @@
       <c r="E345" s="1">
         <v>2012</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="7">
         <v>38821</v>
       </c>
       <c r="G345" s="1" t="s">
@@ -12367,7 +12404,7 @@
       <c r="E346" s="1">
         <v>2012</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="7">
         <v>38821</v>
       </c>
       <c r="G346" s="1" t="s">
@@ -12399,7 +12436,7 @@
       <c r="E347" s="1">
         <v>2012</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="7">
         <v>38829</v>
       </c>
       <c r="G347" s="1" t="s">
@@ -12431,7 +12468,7 @@
       <c r="E348" s="1">
         <v>2012</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="7">
         <v>38829</v>
       </c>
       <c r="G348" s="1" t="s">
@@ -12463,7 +12500,7 @@
       <c r="E349" s="1">
         <v>2012</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="7">
         <v>38829</v>
       </c>
       <c r="G349" s="1" t="s">
@@ -12495,7 +12532,7 @@
       <c r="E350" s="1">
         <v>2012</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="7">
         <v>38829</v>
       </c>
       <c r="G350" s="1" t="s">
@@ -12527,7 +12564,7 @@
       <c r="E351" s="1">
         <v>2012</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="7">
         <v>38829</v>
       </c>
       <c r="G351" s="1" t="s">
@@ -12559,7 +12596,7 @@
       <c r="E352" s="1">
         <v>2012</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="7">
         <v>38829</v>
       </c>
       <c r="G352" s="1" t="s">
@@ -12591,7 +12628,7 @@
       <c r="E353" s="1">
         <v>2012</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="7">
         <v>38829</v>
       </c>
       <c r="G353" s="1" t="s">
@@ -12623,7 +12660,7 @@
       <c r="E354" s="1">
         <v>2012</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="7">
         <v>38829</v>
       </c>
       <c r="G354" s="1" t="s">
@@ -12655,7 +12692,7 @@
       <c r="E355" s="1">
         <v>2012</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="7">
         <v>38829</v>
       </c>
       <c r="G355" s="1" t="s">
@@ -12687,7 +12724,7 @@
       <c r="E356" s="1">
         <v>2012</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="7">
         <v>38829</v>
       </c>
       <c r="G356" s="1" t="s">
@@ -12719,7 +12756,7 @@
       <c r="E357" s="1">
         <v>2012</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="7">
         <v>38829</v>
       </c>
       <c r="G357" s="1" t="s">
@@ -12751,7 +12788,7 @@
       <c r="E358" s="1">
         <v>2012</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="7">
         <v>38829</v>
       </c>
       <c r="G358" s="1" t="s">
@@ -12783,7 +12820,7 @@
       <c r="E359" s="1">
         <v>2012</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="7">
         <v>38829</v>
       </c>
       <c r="G359" s="1" t="s">
@@ -12815,7 +12852,7 @@
       <c r="E360" s="1">
         <v>2012</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="7">
         <v>38829</v>
       </c>
       <c r="G360" s="1" t="s">
@@ -12847,7 +12884,7 @@
       <c r="E361" s="1">
         <v>2012</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="7">
         <v>38829</v>
       </c>
       <c r="G361" s="1" t="s">
@@ -12879,7 +12916,7 @@
       <c r="E362" s="1">
         <v>2012</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="7">
         <v>38829</v>
       </c>
       <c r="G362" s="1" t="s">
@@ -12911,7 +12948,7 @@
       <c r="E363" s="1">
         <v>2012</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="7">
         <v>38829</v>
       </c>
       <c r="G363" s="1" t="s">
@@ -12943,7 +12980,7 @@
       <c r="E364" s="1">
         <v>2012</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="7">
         <v>38829</v>
       </c>
       <c r="G364" s="1" t="s">
@@ -12975,7 +13012,7 @@
       <c r="E365" s="1">
         <v>2012</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="7">
         <v>38829</v>
       </c>
       <c r="G365" s="1" t="s">
@@ -13007,7 +13044,7 @@
       <c r="E366" s="1">
         <v>2012</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="7">
         <v>38829</v>
       </c>
       <c r="G366" s="1" t="s">
@@ -13039,7 +13076,7 @@
       <c r="E367" s="1">
         <v>2012</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="7">
         <v>38829</v>
       </c>
       <c r="G367" s="1" t="s">
@@ -13071,7 +13108,7 @@
       <c r="E368" s="1">
         <v>2012</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="7">
         <v>38829</v>
       </c>
       <c r="G368" s="1" t="s">
@@ -13103,7 +13140,7 @@
       <c r="E369" s="1">
         <v>2012</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="7">
         <v>38829</v>
       </c>
       <c r="G369" s="1" t="s">
@@ -13135,7 +13172,7 @@
       <c r="E370" s="1">
         <v>2012</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="7">
         <v>38829</v>
       </c>
       <c r="G370" s="1" t="s">
@@ -13167,7 +13204,7 @@
       <c r="E371" s="1">
         <v>2012</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="7">
         <v>38829</v>
       </c>
       <c r="G371" s="1" t="s">
@@ -13199,7 +13236,7 @@
       <c r="E372" s="1">
         <v>2012</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="7">
         <v>38829</v>
       </c>
       <c r="G372" s="1" t="s">
@@ -13231,7 +13268,7 @@
       <c r="E373" s="1">
         <v>2012</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="7">
         <v>38829</v>
       </c>
       <c r="G373" s="1" t="s">
@@ -13263,7 +13300,7 @@
       <c r="E374" s="1">
         <v>2012</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="7">
         <v>38829</v>
       </c>
       <c r="G374" s="1" t="s">
@@ -13295,7 +13332,7 @@
       <c r="E375" s="1">
         <v>2012</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="7">
         <v>38829</v>
       </c>
       <c r="G375" s="1" t="s">
@@ -13327,7 +13364,7 @@
       <c r="E376" s="1">
         <v>2012</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="7">
         <v>38829</v>
       </c>
       <c r="G376" s="1" t="s">
@@ -13359,7 +13396,7 @@
       <c r="E377" s="1">
         <v>2012</v>
       </c>
-      <c r="F377" s="2" t="s">
+      <c r="F377" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G377" s="1" t="s">
@@ -13391,7 +13428,7 @@
       <c r="E378" s="1">
         <v>2012</v>
       </c>
-      <c r="F378" s="2" t="s">
+      <c r="F378" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G378" s="1" t="s">
@@ -13423,7 +13460,7 @@
       <c r="E379" s="1">
         <v>2012</v>
       </c>
-      <c r="F379" s="2" t="s">
+      <c r="F379" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G379" s="1" t="s">
@@ -13455,7 +13492,7 @@
       <c r="E380" s="1">
         <v>2012</v>
       </c>
-      <c r="F380" s="2" t="s">
+      <c r="F380" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G380" s="1" t="s">
@@ -13487,7 +13524,7 @@
       <c r="E381" s="1">
         <v>2012</v>
       </c>
-      <c r="F381" s="2" t="s">
+      <c r="F381" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G381" s="1" t="s">
@@ -13519,7 +13556,7 @@
       <c r="E382" s="1">
         <v>2012</v>
       </c>
-      <c r="F382" s="2" t="s">
+      <c r="F382" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G382" s="1" t="s">
@@ -13551,7 +13588,7 @@
       <c r="E383" s="1">
         <v>2012</v>
       </c>
-      <c r="F383" s="2" t="s">
+      <c r="F383" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G383" s="1" t="s">
@@ -13583,7 +13620,7 @@
       <c r="E384" s="1">
         <v>2012</v>
       </c>
-      <c r="F384" s="2" t="s">
+      <c r="F384" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G384" s="1" t="s">
@@ -13615,7 +13652,7 @@
       <c r="E385" s="1">
         <v>2012</v>
       </c>
-      <c r="F385" s="2" t="s">
+      <c r="F385" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G385" s="1" t="s">
@@ -13647,7 +13684,7 @@
       <c r="E386" s="1">
         <v>2012</v>
       </c>
-      <c r="F386" s="2" t="s">
+      <c r="F386" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G386" s="1" t="s">
@@ -13679,7 +13716,7 @@
       <c r="E387" s="1">
         <v>2012</v>
       </c>
-      <c r="F387" s="2" t="s">
+      <c r="F387" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G387" s="1" t="s">
@@ -13711,7 +13748,7 @@
       <c r="E388" s="1">
         <v>2012</v>
       </c>
-      <c r="F388" s="2" t="s">
+      <c r="F388" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G388" s="1" t="s">
@@ -13743,7 +13780,7 @@
       <c r="E389" s="1">
         <v>2012</v>
       </c>
-      <c r="F389" s="2" t="s">
+      <c r="F389" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G389" s="1" t="s">
@@ -13775,7 +13812,7 @@
       <c r="E390" s="1">
         <v>2012</v>
       </c>
-      <c r="F390" s="2" t="s">
+      <c r="F390" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G390" s="1" t="s">
@@ -13807,7 +13844,7 @@
       <c r="E391" s="1">
         <v>2012</v>
       </c>
-      <c r="F391" s="2" t="s">
+      <c r="F391" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G391" s="1" t="s">
@@ -13839,7 +13876,7 @@
       <c r="E392" s="1">
         <v>2012</v>
       </c>
-      <c r="F392" s="2" t="s">
+      <c r="F392" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G392" s="1" t="s">
@@ -13871,7 +13908,7 @@
       <c r="E393" s="1">
         <v>2012</v>
       </c>
-      <c r="F393" s="2" t="s">
+      <c r="F393" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G393" s="1" t="s">
@@ -13903,7 +13940,7 @@
       <c r="E394" s="1">
         <v>2012</v>
       </c>
-      <c r="F394" s="2" t="s">
+      <c r="F394" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G394" s="1" t="s">
@@ -13935,7 +13972,7 @@
       <c r="E395" s="1">
         <v>2012</v>
       </c>
-      <c r="F395" s="2" t="s">
+      <c r="F395" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G395" s="1" t="s">
@@ -13967,7 +14004,7 @@
       <c r="E396" s="1">
         <v>2012</v>
       </c>
-      <c r="F396" s="2" t="s">
+      <c r="F396" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G396" s="1" t="s">
@@ -13999,7 +14036,7 @@
       <c r="E397" s="1">
         <v>2012</v>
       </c>
-      <c r="F397" s="2" t="s">
+      <c r="F397" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G397" s="1" t="s">
@@ -14031,7 +14068,7 @@
       <c r="E398" s="1">
         <v>2012</v>
       </c>
-      <c r="F398" s="2" t="s">
+      <c r="F398" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G398" s="1" t="s">
@@ -14063,7 +14100,7 @@
       <c r="E399" s="1">
         <v>2012</v>
       </c>
-      <c r="F399" s="2" t="s">
+      <c r="F399" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G399" s="1" t="s">
@@ -14095,7 +14132,7 @@
       <c r="E400" s="1">
         <v>2012</v>
       </c>
-      <c r="F400" s="2" t="s">
+      <c r="F400" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G400" s="1" t="s">
@@ -14127,7 +14164,7 @@
       <c r="E401" s="1">
         <v>2012</v>
       </c>
-      <c r="F401" s="2" t="s">
+      <c r="F401" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G401" s="1" t="s">
@@ -14159,7 +14196,7 @@
       <c r="E402" s="1">
         <v>2012</v>
       </c>
-      <c r="F402" s="2" t="s">
+      <c r="F402" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G402" s="1" t="s">
@@ -14191,7 +14228,7 @@
       <c r="E403" s="1">
         <v>2012</v>
       </c>
-      <c r="F403" s="2" t="s">
+      <c r="F403" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G403" s="1" t="s">
@@ -14223,7 +14260,7 @@
       <c r="E404" s="1">
         <v>2012</v>
       </c>
-      <c r="F404" s="2" t="s">
+      <c r="F404" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G404" s="1" t="s">
@@ -14255,7 +14292,7 @@
       <c r="E405" s="1">
         <v>2013</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="7">
         <v>38814</v>
       </c>
       <c r="G405" s="1" t="s">
@@ -14287,7 +14324,7 @@
       <c r="E406" s="1">
         <v>2013</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="7">
         <v>38814</v>
       </c>
       <c r="G406" s="1" t="s">
@@ -14319,7 +14356,7 @@
       <c r="E407" s="1">
         <v>2013</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="7">
         <v>38814</v>
       </c>
       <c r="G407" s="1" t="s">
@@ -14351,7 +14388,7 @@
       <c r="E408" s="1">
         <v>2013</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="7">
         <v>38814</v>
       </c>
       <c r="G408" s="1" t="s">
@@ -14383,7 +14420,7 @@
       <c r="E409" s="1">
         <v>2013</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="7">
         <v>38814</v>
       </c>
       <c r="G409" s="1" t="s">
@@ -14415,7 +14452,7 @@
       <c r="E410" s="1">
         <v>2013</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="7">
         <v>38814</v>
       </c>
       <c r="G410" s="1" t="s">
@@ -14447,7 +14484,7 @@
       <c r="E411" s="1">
         <v>2013</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="7">
         <v>38814</v>
       </c>
       <c r="G411" s="1" t="s">
@@ -14479,7 +14516,7 @@
       <c r="E412" s="1">
         <v>2013</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="7">
         <v>38814</v>
       </c>
       <c r="G412" s="1" t="s">
@@ -14511,7 +14548,7 @@
       <c r="E413" s="1">
         <v>2013</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="7">
         <v>38814</v>
       </c>
       <c r="G413" s="1" t="s">
@@ -14543,7 +14580,7 @@
       <c r="E414" s="1">
         <v>2013</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="7">
         <v>38814</v>
       </c>
       <c r="G414" s="1" t="s">
@@ -14575,7 +14612,7 @@
       <c r="E415" s="1">
         <v>2013</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="7">
         <v>38814</v>
       </c>
       <c r="G415" s="1" t="s">
@@ -14607,7 +14644,7 @@
       <c r="E416" s="1">
         <v>2013</v>
       </c>
-      <c r="F416" s="3">
+      <c r="F416" s="8">
         <v>38828</v>
       </c>
       <c r="G416" s="1" t="s">
@@ -14639,7 +14676,7 @@
       <c r="E417" s="1">
         <v>2013</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="7">
         <v>38828</v>
       </c>
       <c r="G417" s="1" t="s">
@@ -14671,7 +14708,7 @@
       <c r="E418" s="1">
         <v>2013</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="7">
         <v>38828</v>
       </c>
       <c r="G418" s="1" t="s">
@@ -14703,7 +14740,7 @@
       <c r="E419" s="1">
         <v>2013</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="7">
         <v>38828</v>
       </c>
       <c r="G419" s="1" t="s">
@@ -14735,7 +14772,7 @@
       <c r="E420" s="1">
         <v>2013</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="7">
         <v>38828</v>
       </c>
       <c r="G420" s="1" t="s">
@@ -14767,7 +14804,7 @@
       <c r="E421" s="1">
         <v>2013</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="7">
         <v>38828</v>
       </c>
       <c r="G421" s="1" t="s">
@@ -14799,7 +14836,7 @@
       <c r="E422" s="1">
         <v>2013</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="7">
         <v>38828</v>
       </c>
       <c r="G422" s="1" t="s">
@@ -14831,7 +14868,7 @@
       <c r="E423" s="1">
         <v>2013</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="7">
         <v>38828</v>
       </c>
       <c r="G423" s="1" t="s">
@@ -14863,7 +14900,7 @@
       <c r="E424" s="1">
         <v>2013</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="7">
         <v>38828</v>
       </c>
       <c r="G424" s="1" t="s">
@@ -14895,7 +14932,7 @@
       <c r="E425" s="1">
         <v>2013</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="7">
         <v>38828</v>
       </c>
       <c r="G425" s="1" t="s">
@@ -14927,7 +14964,7 @@
       <c r="E426" s="1">
         <v>2013</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="7">
         <v>38828</v>
       </c>
       <c r="G426" s="1" t="s">
@@ -14959,7 +14996,7 @@
       <c r="E427" s="1">
         <v>2013</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="7">
         <v>38828</v>
       </c>
       <c r="G427" s="1" t="s">
@@ -14991,7 +15028,7 @@
       <c r="E428" s="1">
         <v>2013</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="7">
         <v>38828</v>
       </c>
       <c r="G428" s="1" t="s">
@@ -15023,7 +15060,7 @@
       <c r="E429" s="1">
         <v>2013</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="7">
         <v>38828</v>
       </c>
       <c r="G429" s="1" t="s">
@@ -15055,7 +15092,7 @@
       <c r="E430" s="1">
         <v>2013</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="7">
         <v>38828</v>
       </c>
       <c r="G430" s="1" t="s">
@@ -15087,7 +15124,7 @@
       <c r="E431" s="1">
         <v>2013</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="7">
         <v>38828</v>
       </c>
       <c r="G431" s="1" t="s">
@@ -15119,7 +15156,7 @@
       <c r="E432" s="1">
         <v>2013</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="7">
         <v>38828</v>
       </c>
       <c r="G432" s="1" t="s">
@@ -15151,7 +15188,7 @@
       <c r="E433" s="1">
         <v>2013</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="7">
         <v>38828</v>
       </c>
       <c r="G433" s="1" t="s">
@@ -15183,7 +15220,7 @@
       <c r="E434" s="1">
         <v>2013</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="7">
         <v>38828</v>
       </c>
       <c r="G434" s="1" t="s">
@@ -15215,7 +15252,7 @@
       <c r="E435" s="1">
         <v>2013</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="7">
         <v>38828</v>
       </c>
       <c r="G435" s="1" t="s">
@@ -15247,7 +15284,7 @@
       <c r="E436" s="1">
         <v>2013</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="7">
         <v>38828</v>
       </c>
       <c r="G436" s="1" t="s">
@@ -15279,7 +15316,7 @@
       <c r="E437" s="1">
         <v>2013</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="7">
         <v>38828</v>
       </c>
       <c r="G437" s="1" t="s">
@@ -15311,7 +15348,7 @@
       <c r="E438" s="1">
         <v>2013</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="7">
         <v>38828</v>
       </c>
       <c r="G438" s="1" t="s">
@@ -15343,7 +15380,7 @@
       <c r="E439" s="1">
         <v>2013</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="7">
         <v>38828</v>
       </c>
       <c r="G439" s="1" t="s">
@@ -15375,7 +15412,7 @@
       <c r="E440" s="1">
         <v>2013</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="7">
         <v>38828</v>
       </c>
       <c r="G440" s="1" t="s">
@@ -15407,7 +15444,7 @@
       <c r="E441" s="1">
         <v>2013</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="7">
         <v>38828</v>
       </c>
       <c r="G441" s="1" t="s">
@@ -15439,7 +15476,7 @@
       <c r="E442" s="1">
         <v>2013</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="7">
         <v>38837</v>
       </c>
       <c r="G442" s="1" t="s">
@@ -15471,7 +15508,7 @@
       <c r="E443" s="1">
         <v>2013</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="7">
         <v>38837</v>
       </c>
       <c r="G443" s="1" t="s">
@@ -15503,7 +15540,7 @@
       <c r="E444" s="1">
         <v>2013</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="7">
         <v>38837</v>
       </c>
       <c r="G444" s="1" t="s">
@@ -15535,7 +15572,7 @@
       <c r="E445" s="1">
         <v>2013</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="7">
         <v>38837</v>
       </c>
       <c r="G445" s="1" t="s">
@@ -15567,7 +15604,7 @@
       <c r="E446" s="1">
         <v>2013</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="7">
         <v>38837</v>
       </c>
       <c r="G446" s="1" t="s">
@@ -15599,7 +15636,7 @@
       <c r="E447" s="1">
         <v>2013</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="7">
         <v>38837</v>
       </c>
       <c r="G447" s="1" t="s">
@@ -15631,7 +15668,7 @@
       <c r="E448" s="1">
         <v>2013</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="7">
         <v>38837</v>
       </c>
       <c r="G448" s="1" t="s">
@@ -15663,7 +15700,7 @@
       <c r="E449" s="1">
         <v>2013</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="7">
         <v>38837</v>
       </c>
       <c r="G449" s="1" t="s">
@@ -15695,7 +15732,7 @@
       <c r="E450" s="1">
         <v>2013</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="7">
         <v>38837</v>
       </c>
       <c r="G450" s="1" t="s">
@@ -15727,7 +15764,7 @@
       <c r="E451" s="1">
         <v>2013</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="7">
         <v>38837</v>
       </c>
       <c r="G451" s="1" t="s">
@@ -15759,7 +15796,7 @@
       <c r="E452" s="1">
         <v>2013</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="7">
         <v>38837</v>
       </c>
       <c r="G452" s="1" t="s">
@@ -15791,7 +15828,7 @@
       <c r="E453" s="1">
         <v>2013</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="7">
         <v>38837</v>
       </c>
       <c r="G453" s="1" t="s">
@@ -15823,7 +15860,7 @@
       <c r="E454" s="1">
         <v>2013</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="7">
         <v>38837</v>
       </c>
       <c r="G454" s="1" t="s">
@@ -15855,7 +15892,7 @@
       <c r="E455" s="1">
         <v>2013</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="7">
         <v>38837</v>
       </c>
       <c r="G455" s="1" t="s">
@@ -15887,7 +15924,7 @@
       <c r="E456" s="1">
         <v>2013</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="7">
         <v>38837</v>
       </c>
       <c r="G456" s="1" t="s">
@@ -15919,7 +15956,7 @@
       <c r="E457" s="1">
         <v>2013</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="7">
         <v>38837</v>
       </c>
       <c r="G457" s="1" t="s">
@@ -15951,7 +15988,7 @@
       <c r="E458" s="1">
         <v>2013</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="7">
         <v>38837</v>
       </c>
       <c r="G458" s="1" t="s">
@@ -15983,7 +16020,7 @@
       <c r="E459" s="1">
         <v>2013</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="7">
         <v>38837</v>
       </c>
       <c r="G459" s="1" t="s">
@@ -16015,7 +16052,7 @@
       <c r="E460" s="1">
         <v>2013</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="7">
         <v>38837</v>
       </c>
       <c r="G460" s="1" t="s">
@@ -16047,7 +16084,7 @@
       <c r="E461" s="1">
         <v>2013</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="7">
         <v>38837</v>
       </c>
       <c r="G461" s="1" t="s">
@@ -16079,7 +16116,7 @@
       <c r="E462" s="1">
         <v>2013</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="7">
         <v>38837</v>
       </c>
       <c r="G462" s="1" t="s">
@@ -16111,7 +16148,7 @@
       <c r="E463" s="1">
         <v>2013</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="7">
         <v>38837</v>
       </c>
       <c r="G463" s="1" t="s">
@@ -16143,7 +16180,7 @@
       <c r="E464" s="1">
         <v>2013</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="7">
         <v>38837</v>
       </c>
       <c r="G464" s="1" t="s">
@@ -16175,7 +16212,7 @@
       <c r="E465" s="1">
         <v>2013</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="7">
         <v>38837</v>
       </c>
       <c r="G465" s="1" t="s">
@@ -16207,7 +16244,7 @@
       <c r="E466" s="1">
         <v>2013</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="7">
         <v>38837</v>
       </c>
       <c r="G466" s="1" t="s">
@@ -16239,7 +16276,7 @@
       <c r="E467" s="1">
         <v>2013</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="7">
         <v>38837</v>
       </c>
       <c r="G467" s="1" t="s">
@@ -16271,7 +16308,7 @@
       <c r="E468" s="1">
         <v>2013</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="7">
         <v>38837</v>
       </c>
       <c r="G468" s="1" t="s">
@@ -16303,7 +16340,7 @@
       <c r="E469" s="1">
         <v>2013</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="7">
         <v>38837</v>
       </c>
       <c r="G469" s="1" t="s">
@@ -16335,7 +16372,7 @@
       <c r="E470" s="1">
         <v>2013</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="7">
         <v>38837</v>
       </c>
       <c r="G470" s="1" t="s">
@@ -16367,7 +16404,7 @@
       <c r="E471" s="1">
         <v>2014</v>
       </c>
-      <c r="F471" s="3">
+      <c r="F471" s="8">
         <v>38779</v>
       </c>
       <c r="G471" s="1" t="s">
@@ -16399,7 +16436,7 @@
       <c r="E472" s="1">
         <v>2014</v>
       </c>
-      <c r="F472" s="3">
+      <c r="F472" s="8">
         <v>38779</v>
       </c>
       <c r="G472" s="1" t="s">
@@ -16431,7 +16468,7 @@
       <c r="E473" s="1">
         <v>2014</v>
       </c>
-      <c r="F473" s="3">
+      <c r="F473" s="8">
         <v>38779</v>
       </c>
       <c r="G473" s="1" t="s">
@@ -16463,7 +16500,7 @@
       <c r="E474" s="1">
         <v>2014</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="7">
         <v>38779</v>
       </c>
       <c r="G474" s="1" t="s">
@@ -16495,7 +16532,7 @@
       <c r="E475" s="1">
         <v>2014</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="7">
         <v>38779</v>
       </c>
       <c r="G475" s="1" t="s">
@@ -16527,7 +16564,7 @@
       <c r="E476" s="1">
         <v>2014</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="7">
         <v>38779</v>
       </c>
       <c r="G476" s="1" t="s">
@@ -16559,7 +16596,7 @@
       <c r="E477" s="1">
         <v>2014</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="7">
         <v>38779</v>
       </c>
       <c r="G477" s="1" t="s">
@@ -16591,7 +16628,7 @@
       <c r="E478" s="1">
         <v>2014</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="7">
         <v>38779</v>
       </c>
       <c r="G478" s="1" t="s">
@@ -16623,7 +16660,7 @@
       <c r="E479" s="1">
         <v>2014</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="7">
         <v>38779</v>
       </c>
       <c r="G479" s="1" t="s">
@@ -16655,7 +16692,7 @@
       <c r="E480" s="1">
         <v>2014</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="7">
         <v>38779</v>
       </c>
       <c r="G480" s="1" t="s">
@@ -16687,7 +16724,7 @@
       <c r="E481" s="1">
         <v>2014</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="7">
         <v>38779</v>
       </c>
       <c r="G481" s="1" t="s">
@@ -16719,7 +16756,7 @@
       <c r="E482" s="1">
         <v>2014</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="7">
         <v>38779</v>
       </c>
       <c r="G482" s="1" t="s">
@@ -16751,7 +16788,7 @@
       <c r="E483" s="1">
         <v>2014</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="7">
         <v>38779</v>
       </c>
       <c r="G483" s="1" t="s">
@@ -16783,7 +16820,7 @@
       <c r="E484" s="1">
         <v>2014</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="7">
         <v>38779</v>
       </c>
       <c r="G484" s="1" t="s">
@@ -16815,7 +16852,7 @@
       <c r="E485" s="1">
         <v>2014</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="7">
         <v>38779</v>
       </c>
       <c r="G485" s="1" t="s">
@@ -16847,7 +16884,7 @@
       <c r="E486" s="1">
         <v>2014</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="7">
         <v>38779</v>
       </c>
       <c r="G486" s="1" t="s">
@@ -16879,7 +16916,7 @@
       <c r="E487" s="1">
         <v>2014</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="7">
         <v>38779</v>
       </c>
       <c r="G487" s="1" t="s">
@@ -16911,7 +16948,7 @@
       <c r="E488" s="1">
         <v>2014</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="7">
         <v>38779</v>
       </c>
       <c r="G488" s="1" t="s">
@@ -16943,7 +16980,7 @@
       <c r="E489" s="1">
         <v>2014</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="7">
         <v>38779</v>
       </c>
       <c r="G489" s="1" t="s">
@@ -16975,7 +17012,7 @@
       <c r="E490" s="1">
         <v>2014</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="7">
         <v>38779</v>
       </c>
       <c r="G490" s="1" t="s">
@@ -17007,7 +17044,7 @@
       <c r="E491" s="1">
         <v>2014</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="7">
         <v>38779</v>
       </c>
       <c r="G491" s="1" t="s">
@@ -17039,7 +17076,7 @@
       <c r="E492" s="1">
         <v>2014</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="7">
         <v>38779</v>
       </c>
       <c r="G492" s="1" t="s">
@@ -17071,7 +17108,7 @@
       <c r="E493" s="1">
         <v>2014</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="7">
         <v>38779</v>
       </c>
       <c r="G493" s="1" t="s">
@@ -17103,7 +17140,7 @@
       <c r="E494" s="1">
         <v>2014</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="7">
         <v>38779</v>
       </c>
       <c r="G494" s="1" t="s">
@@ -17135,7 +17172,7 @@
       <c r="E495" s="1">
         <v>2014</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="7">
         <v>38779</v>
       </c>
       <c r="G495" s="1" t="s">
@@ -17167,7 +17204,7 @@
       <c r="E496" s="1">
         <v>2014</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="7">
         <v>38779</v>
       </c>
       <c r="G496" s="1" t="s">
@@ -17199,7 +17236,7 @@
       <c r="E497" s="1">
         <v>2014</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="7">
         <v>38779</v>
       </c>
       <c r="G497" s="1" t="s">
@@ -17231,7 +17268,7 @@
       <c r="E498" s="1">
         <v>2014</v>
       </c>
-      <c r="F498" s="3">
+      <c r="F498" s="8">
         <v>38798</v>
       </c>
       <c r="G498" s="1" t="s">
@@ -17263,7 +17300,7 @@
       <c r="E499" s="1">
         <v>2014</v>
       </c>
-      <c r="F499" s="3">
+      <c r="F499" s="8">
         <v>38798</v>
       </c>
       <c r="G499" s="1" t="s">
@@ -17295,7 +17332,7 @@
       <c r="E500" s="1">
         <v>2014</v>
       </c>
-      <c r="F500" s="3">
+      <c r="F500" s="8">
         <v>38798</v>
       </c>
       <c r="G500" s="1" t="s">
@@ -17327,7 +17364,7 @@
       <c r="E501" s="1">
         <v>2014</v>
       </c>
-      <c r="F501" s="3">
+      <c r="F501" s="8">
         <v>38798</v>
       </c>
       <c r="G501" s="1" t="s">
@@ -17359,7 +17396,7 @@
       <c r="E502" s="1">
         <v>2014</v>
       </c>
-      <c r="F502" s="3">
+      <c r="F502" s="8">
         <v>38798</v>
       </c>
       <c r="G502" s="1" t="s">
@@ -17391,7 +17428,7 @@
       <c r="E503" s="1">
         <v>2014</v>
       </c>
-      <c r="F503" s="3">
+      <c r="F503" s="8">
         <v>38798</v>
       </c>
       <c r="G503" s="1" t="s">
@@ -17423,7 +17460,7 @@
       <c r="E504" s="1">
         <v>2014</v>
       </c>
-      <c r="F504" s="3">
+      <c r="F504" s="8">
         <v>38798</v>
       </c>
       <c r="G504" s="1" t="s">
@@ -17455,7 +17492,7 @@
       <c r="E505" s="1">
         <v>2014</v>
       </c>
-      <c r="F505" s="3">
+      <c r="F505" s="8">
         <v>38798</v>
       </c>
       <c r="G505" s="1" t="s">
@@ -17487,7 +17524,7 @@
       <c r="E506" s="1">
         <v>2014</v>
       </c>
-      <c r="F506" s="3">
+      <c r="F506" s="8">
         <v>38798</v>
       </c>
       <c r="G506" s="1" t="s">
@@ -17519,7 +17556,7 @@
       <c r="E507" s="1">
         <v>2014</v>
       </c>
-      <c r="F507" s="3">
+      <c r="F507" s="8">
         <v>38798</v>
       </c>
       <c r="G507" s="1" t="s">
@@ -17551,7 +17588,7 @@
       <c r="E508" s="1">
         <v>2014</v>
       </c>
-      <c r="F508" s="3">
+      <c r="F508" s="8">
         <v>38798</v>
       </c>
       <c r="G508" s="1" t="s">
@@ -17583,7 +17620,7 @@
       <c r="E509" s="1">
         <v>2014</v>
       </c>
-      <c r="F509" s="3">
+      <c r="F509" s="8">
         <v>38798</v>
       </c>
       <c r="G509" s="1" t="s">
@@ -17615,7 +17652,7 @@
       <c r="E510" s="1">
         <v>2014</v>
       </c>
-      <c r="F510" s="3">
+      <c r="F510" s="8">
         <v>38798</v>
       </c>
       <c r="G510" s="1" t="s">
@@ -17647,7 +17684,7 @@
       <c r="E511" s="1">
         <v>2014</v>
       </c>
-      <c r="F511" s="3">
+      <c r="F511" s="8">
         <v>38798</v>
       </c>
       <c r="G511" s="1" t="s">
@@ -17679,7 +17716,7 @@
       <c r="E512" s="1">
         <v>2014</v>
       </c>
-      <c r="F512" s="3">
+      <c r="F512" s="8">
         <v>38798</v>
       </c>
       <c r="G512" s="1" t="s">
@@ -17711,7 +17748,7 @@
       <c r="E513" s="1">
         <v>2014</v>
       </c>
-      <c r="F513" s="3">
+      <c r="F513" s="8">
         <v>38798</v>
       </c>
       <c r="G513" s="1" t="s">
@@ -17743,7 +17780,7 @@
       <c r="E514" s="1">
         <v>2014</v>
       </c>
-      <c r="F514" s="3">
+      <c r="F514" s="8">
         <v>38798</v>
       </c>
       <c r="G514" s="1" t="s">
@@ -17775,7 +17812,7 @@
       <c r="E515" s="1">
         <v>2014</v>
       </c>
-      <c r="F515" s="3">
+      <c r="F515" s="8">
         <v>38798</v>
       </c>
       <c r="G515" s="1" t="s">
@@ -17807,7 +17844,7 @@
       <c r="E516" s="1">
         <v>2014</v>
       </c>
-      <c r="F516" s="3">
+      <c r="F516" s="8">
         <v>38798</v>
       </c>
       <c r="G516" s="1" t="s">
@@ -17839,7 +17876,7 @@
       <c r="E517" s="1">
         <v>2014</v>
       </c>
-      <c r="F517" s="3">
+      <c r="F517" s="8">
         <v>38798</v>
       </c>
       <c r="G517" s="1" t="s">
@@ -17871,7 +17908,7 @@
       <c r="E518" s="1">
         <v>2014</v>
       </c>
-      <c r="F518" s="3">
+      <c r="F518" s="8">
         <v>38798</v>
       </c>
       <c r="G518" s="1" t="s">
@@ -17903,7 +17940,7 @@
       <c r="E519" s="1">
         <v>2014</v>
       </c>
-      <c r="F519" s="3">
+      <c r="F519" s="8">
         <v>38798</v>
       </c>
       <c r="G519" s="1" t="s">
@@ -17935,7 +17972,7 @@
       <c r="E520" s="1">
         <v>2014</v>
       </c>
-      <c r="F520" s="3">
+      <c r="F520" s="8">
         <v>38798</v>
       </c>
       <c r="G520" s="1" t="s">
@@ -17967,7 +18004,7 @@
       <c r="E521" s="1">
         <v>2014</v>
       </c>
-      <c r="F521" s="3">
+      <c r="F521" s="8">
         <v>38798</v>
       </c>
       <c r="G521" s="1" t="s">
@@ -17999,7 +18036,7 @@
       <c r="E522" s="1">
         <v>2014</v>
       </c>
-      <c r="F522" s="3">
+      <c r="F522" s="8">
         <v>38798</v>
       </c>
       <c r="G522" s="1" t="s">
@@ -18031,7 +18068,7 @@
       <c r="E523" s="1">
         <v>2014</v>
       </c>
-      <c r="F523" s="3">
+      <c r="F523" s="8">
         <v>38798</v>
       </c>
       <c r="G523" s="1" t="s">
@@ -18063,7 +18100,7 @@
       <c r="E524" s="1">
         <v>2014</v>
       </c>
-      <c r="F524" s="3">
+      <c r="F524" s="8">
         <v>38798</v>
       </c>
       <c r="G524" s="1" t="s">
@@ -18095,7 +18132,7 @@
       <c r="E525" s="1">
         <v>2014</v>
       </c>
-      <c r="F525" s="3">
+      <c r="F525" s="8">
         <v>38798</v>
       </c>
       <c r="G525" s="1" t="s">
@@ -18127,7 +18164,7 @@
       <c r="E526" s="1">
         <v>2014</v>
       </c>
-      <c r="F526" s="3">
+      <c r="F526" s="8">
         <v>38798</v>
       </c>
       <c r="G526" s="1" t="s">
@@ -18159,7 +18196,7 @@
       <c r="E527" s="1">
         <v>2014</v>
       </c>
-      <c r="F527" s="3">
+      <c r="F527" s="8">
         <v>38798</v>
       </c>
       <c r="G527" s="1" t="s">
@@ -18191,7 +18228,7 @@
       <c r="E528" s="1">
         <v>2014</v>
       </c>
-      <c r="F528" s="3">
+      <c r="F528" s="8">
         <v>38798</v>
       </c>
       <c r="G528" s="1" t="s">
@@ -18223,7 +18260,7 @@
       <c r="E529" s="1">
         <v>2014</v>
       </c>
-      <c r="F529" s="3">
+      <c r="F529" s="8">
         <v>38798</v>
       </c>
       <c r="G529" s="1" t="s">
@@ -18255,7 +18292,7 @@
       <c r="E530" s="1">
         <v>2014</v>
       </c>
-      <c r="F530" s="3">
+      <c r="F530" s="8">
         <v>38798</v>
       </c>
       <c r="G530" s="1" t="s">
@@ -18287,7 +18324,7 @@
       <c r="E531" s="1">
         <v>2014</v>
       </c>
-      <c r="F531" s="2">
+      <c r="F531" s="7">
         <v>38821</v>
       </c>
       <c r="G531" s="1" t="s">
@@ -18319,7 +18356,7 @@
       <c r="E532" s="1">
         <v>2014</v>
       </c>
-      <c r="F532" s="2">
+      <c r="F532" s="7">
         <v>38821</v>
       </c>
       <c r="G532" s="1" t="s">
@@ -18351,7 +18388,7 @@
       <c r="E533" s="1">
         <v>2014</v>
       </c>
-      <c r="F533" s="2">
+      <c r="F533" s="7">
         <v>38821</v>
       </c>
       <c r="G533" s="1" t="s">
@@ -18383,7 +18420,7 @@
       <c r="E534" s="1">
         <v>2014</v>
       </c>
-      <c r="F534" s="2">
+      <c r="F534" s="7">
         <v>38821</v>
       </c>
       <c r="G534" s="1" t="s">
@@ -18415,7 +18452,7 @@
       <c r="E535" s="1">
         <v>2014</v>
       </c>
-      <c r="F535" s="2">
+      <c r="F535" s="7">
         <v>38821</v>
       </c>
       <c r="G535" s="1" t="s">
@@ -18447,7 +18484,7 @@
       <c r="E536" s="1">
         <v>2014</v>
       </c>
-      <c r="F536" s="2">
+      <c r="F536" s="7">
         <v>38821</v>
       </c>
       <c r="G536" s="1" t="s">
@@ -18479,7 +18516,7 @@
       <c r="E537" s="1">
         <v>2014</v>
       </c>
-      <c r="F537" s="2">
+      <c r="F537" s="7">
         <v>38821</v>
       </c>
       <c r="G537" s="1" t="s">
@@ -18511,7 +18548,7 @@
       <c r="E538" s="1">
         <v>2014</v>
       </c>
-      <c r="F538" s="2">
+      <c r="F538" s="7">
         <v>38821</v>
       </c>
       <c r="G538" s="1" t="s">
@@ -18543,7 +18580,7 @@
       <c r="E539" s="1">
         <v>2014</v>
       </c>
-      <c r="F539" s="2">
+      <c r="F539" s="7">
         <v>38821</v>
       </c>
       <c r="G539" s="1" t="s">
@@ -18575,7 +18612,7 @@
       <c r="E540" s="1">
         <v>2014</v>
       </c>
-      <c r="F540" s="2">
+      <c r="F540" s="7">
         <v>38821</v>
       </c>
       <c r="G540" s="1" t="s">
@@ -18607,7 +18644,7 @@
       <c r="E541" s="1">
         <v>2014</v>
       </c>
-      <c r="F541" s="2">
+      <c r="F541" s="7">
         <v>38821</v>
       </c>
       <c r="G541" s="1" t="s">
@@ -18639,7 +18676,7 @@
       <c r="E542" s="1">
         <v>2014</v>
       </c>
-      <c r="F542" s="2">
+      <c r="F542" s="7">
         <v>38821</v>
       </c>
       <c r="G542" s="1" t="s">
@@ -18671,7 +18708,7 @@
       <c r="E543" s="1">
         <v>2014</v>
       </c>
-      <c r="F543" s="2">
+      <c r="F543" s="7">
         <v>38821</v>
       </c>
       <c r="G543" s="1" t="s">
@@ -18703,7 +18740,7 @@
       <c r="E544" s="1">
         <v>2014</v>
       </c>
-      <c r="F544" s="2">
+      <c r="F544" s="7">
         <v>38821</v>
       </c>
       <c r="G544" s="1" t="s">
@@ -18735,7 +18772,7 @@
       <c r="E545" s="1">
         <v>2014</v>
       </c>
-      <c r="F545" s="2">
+      <c r="F545" s="7">
         <v>38821</v>
       </c>
       <c r="G545" s="1" t="s">
@@ -18767,7 +18804,7 @@
       <c r="E546" s="1">
         <v>2014</v>
       </c>
-      <c r="F546" s="2">
+      <c r="F546" s="7">
         <v>38821</v>
       </c>
       <c r="G546" s="1" t="s">
@@ -18799,7 +18836,7 @@
       <c r="E547" s="1">
         <v>2014</v>
       </c>
-      <c r="F547" s="2">
+      <c r="F547" s="7">
         <v>38821</v>
       </c>
       <c r="G547" s="1" t="s">
@@ -18831,7 +18868,7 @@
       <c r="E548" s="1">
         <v>2014</v>
       </c>
-      <c r="F548" s="2">
+      <c r="F548" s="7">
         <v>38821</v>
       </c>
       <c r="G548" s="1" t="s">
@@ -18863,7 +18900,7 @@
       <c r="E549" s="1">
         <v>2014</v>
       </c>
-      <c r="F549" s="2">
+      <c r="F549" s="7">
         <v>38821</v>
       </c>
       <c r="G549" s="1" t="s">
@@ -18895,7 +18932,7 @@
       <c r="E550" s="1">
         <v>2014</v>
       </c>
-      <c r="F550" s="2">
+      <c r="F550" s="7">
         <v>38821</v>
       </c>
       <c r="G550" s="1" t="s">
@@ -18927,7 +18964,7 @@
       <c r="E551" s="1">
         <v>2014</v>
       </c>
-      <c r="F551" s="2">
+      <c r="F551" s="7">
         <v>38821</v>
       </c>
       <c r="G551" s="1" t="s">
@@ -18959,7 +18996,7 @@
       <c r="E552" s="1">
         <v>2014</v>
       </c>
-      <c r="F552" s="2">
+      <c r="F552" s="7">
         <v>38821</v>
       </c>
       <c r="G552" s="1" t="s">
@@ -18991,7 +19028,7 @@
       <c r="E553" s="1">
         <v>2014</v>
       </c>
-      <c r="F553" s="2">
+      <c r="F553" s="7">
         <v>38821</v>
       </c>
       <c r="G553" s="1" t="s">
@@ -19023,7 +19060,7 @@
       <c r="E554" s="1">
         <v>2014</v>
       </c>
-      <c r="F554" s="2">
+      <c r="F554" s="7">
         <v>38821</v>
       </c>
       <c r="G554" s="1" t="s">
@@ -19055,7 +19092,7 @@
       <c r="E555" s="1">
         <v>2014</v>
       </c>
-      <c r="F555" s="2">
+      <c r="F555" s="7">
         <v>38821</v>
       </c>
       <c r="G555" s="1" t="s">
@@ -19087,7 +19124,7 @@
       <c r="E556" s="1">
         <v>2014</v>
       </c>
-      <c r="F556" s="2">
+      <c r="F556" s="7">
         <v>38821</v>
       </c>
       <c r="G556" s="1" t="s">
@@ -19119,7 +19156,7 @@
       <c r="E557" s="1">
         <v>2014</v>
       </c>
-      <c r="F557" s="2">
+      <c r="F557" s="7">
         <v>38821</v>
       </c>
       <c r="G557" s="1" t="s">
@@ -19151,7 +19188,7 @@
       <c r="E558" s="1">
         <v>2014</v>
       </c>
-      <c r="F558" s="2">
+      <c r="F558" s="7">
         <v>38821</v>
       </c>
       <c r="G558" s="1" t="s">
@@ -19183,7 +19220,7 @@
       <c r="E559" s="1">
         <v>2014</v>
       </c>
-      <c r="F559" s="2">
+      <c r="F559" s="7">
         <v>38821</v>
       </c>
       <c r="G559" s="1" t="s">
@@ -19212,10 +19249,10 @@
       <c r="D560" s="1">
         <v>3</v>
       </c>
-      <c r="E560" s="4">
+      <c r="E560" s="9">
         <v>2015</v>
       </c>
-      <c r="F560" s="3">
+      <c r="F560" s="8">
         <v>38771</v>
       </c>
       <c r="G560" s="1" t="s">
@@ -19244,10 +19281,10 @@
       <c r="D561" s="1">
         <v>4</v>
       </c>
-      <c r="E561" s="4">
+      <c r="E561" s="9">
         <v>2015</v>
       </c>
-      <c r="F561" s="3">
+      <c r="F561" s="8">
         <v>38771</v>
       </c>
       <c r="G561" s="1" t="s">
@@ -19276,10 +19313,10 @@
       <c r="D562" s="1">
         <v>3</v>
       </c>
-      <c r="E562" s="4">
+      <c r="E562" s="9">
         <v>2015</v>
       </c>
-      <c r="F562" s="3">
+      <c r="F562" s="8">
         <v>38771</v>
       </c>
       <c r="G562" s="1" t="s">
@@ -19308,10 +19345,10 @@
       <c r="D563" s="1">
         <v>2</v>
       </c>
-      <c r="E563" s="4">
+      <c r="E563" s="9">
         <v>2015</v>
       </c>
-      <c r="F563" s="3">
+      <c r="F563" s="8">
         <v>38771</v>
       </c>
       <c r="G563" s="1" t="s">
@@ -19340,10 +19377,10 @@
       <c r="D564" s="1">
         <v>3</v>
       </c>
-      <c r="E564" s="4">
+      <c r="E564" s="9">
         <v>2015</v>
       </c>
-      <c r="F564" s="3">
+      <c r="F564" s="8">
         <v>38771</v>
       </c>
       <c r="G564" s="1" t="s">
@@ -19372,10 +19409,10 @@
       <c r="D565" s="1">
         <v>4</v>
       </c>
-      <c r="E565" s="4">
+      <c r="E565" s="9">
         <v>2015</v>
       </c>
-      <c r="F565" s="3">
+      <c r="F565" s="8">
         <v>38771</v>
       </c>
       <c r="G565" s="1" t="s">
@@ -19404,10 +19441,10 @@
       <c r="D566" s="1">
         <v>6</v>
       </c>
-      <c r="E566" s="4">
+      <c r="E566" s="9">
         <v>2015</v>
       </c>
-      <c r="F566" s="3">
+      <c r="F566" s="8">
         <v>38771</v>
       </c>
       <c r="G566" s="1" t="s">
@@ -19436,10 +19473,10 @@
       <c r="D567" s="1">
         <v>2</v>
       </c>
-      <c r="E567" s="4">
+      <c r="E567" s="9">
         <v>2015</v>
       </c>
-      <c r="F567" s="3">
+      <c r="F567" s="8">
         <v>38771</v>
       </c>
       <c r="G567" s="1" t="s">
@@ -19468,10 +19505,10 @@
       <c r="D568" s="1">
         <v>5</v>
       </c>
-      <c r="E568" s="4">
+      <c r="E568" s="9">
         <v>2015</v>
       </c>
-      <c r="F568" s="3">
+      <c r="F568" s="8">
         <v>38771</v>
       </c>
       <c r="G568" s="1" t="s">
@@ -19500,10 +19537,10 @@
       <c r="D569" s="1">
         <v>2</v>
       </c>
-      <c r="E569" s="4">
+      <c r="E569" s="9">
         <v>2015</v>
       </c>
-      <c r="F569" s="3">
+      <c r="F569" s="8">
         <v>38771</v>
       </c>
       <c r="G569" s="1" t="s">
@@ -19532,10 +19569,10 @@
       <c r="D570" s="1">
         <v>3</v>
       </c>
-      <c r="E570" s="4">
+      <c r="E570" s="9">
         <v>2015</v>
       </c>
-      <c r="F570" s="3">
+      <c r="F570" s="8">
         <v>38771</v>
       </c>
       <c r="G570" s="1" t="s">
@@ -19564,10 +19601,10 @@
       <c r="D571" s="1">
         <v>2</v>
       </c>
-      <c r="E571" s="4">
+      <c r="E571" s="9">
         <v>2015</v>
       </c>
-      <c r="F571" s="3">
+      <c r="F571" s="8">
         <v>38771</v>
       </c>
       <c r="G571" s="1" t="s">
@@ -19596,10 +19633,10 @@
       <c r="D572" s="1">
         <v>1</v>
       </c>
-      <c r="E572" s="4">
+      <c r="E572" s="9">
         <v>2015</v>
       </c>
-      <c r="F572" s="3">
+      <c r="F572" s="8">
         <v>38771</v>
       </c>
       <c r="G572" s="1" t="s">
@@ -19628,10 +19665,10 @@
       <c r="D573" s="1">
         <v>2</v>
       </c>
-      <c r="E573" s="4">
+      <c r="E573" s="9">
         <v>2015</v>
       </c>
-      <c r="F573" s="3">
+      <c r="F573" s="8">
         <v>38771</v>
       </c>
       <c r="G573" s="1" t="s">
@@ -19660,10 +19697,10 @@
       <c r="D574" s="1">
         <v>3</v>
       </c>
-      <c r="E574" s="4">
+      <c r="E574" s="9">
         <v>2015</v>
       </c>
-      <c r="F574" s="3">
+      <c r="F574" s="8">
         <v>38771</v>
       </c>
       <c r="G574" s="1" t="s">
@@ -19692,10 +19729,10 @@
       <c r="D575" s="1">
         <v>6</v>
       </c>
-      <c r="E575" s="4">
+      <c r="E575" s="9">
         <v>2015</v>
       </c>
-      <c r="F575" s="3">
+      <c r="F575" s="8">
         <v>38771</v>
       </c>
       <c r="G575" s="1" t="s">
@@ -19724,10 +19761,10 @@
       <c r="D576" s="1">
         <v>2</v>
       </c>
-      <c r="E576" s="4">
+      <c r="E576" s="9">
         <v>2015</v>
       </c>
-      <c r="F576" s="3">
+      <c r="F576" s="8">
         <v>38771</v>
       </c>
       <c r="G576" s="1" t="s">
@@ -19756,10 +19793,10 @@
       <c r="D577" s="1">
         <v>3</v>
       </c>
-      <c r="E577" s="4">
+      <c r="E577" s="9">
         <v>2015</v>
       </c>
-      <c r="F577" s="3">
+      <c r="F577" s="8">
         <v>38771</v>
       </c>
       <c r="G577" s="1" t="s">
@@ -19788,10 +19825,10 @@
       <c r="D578" s="1">
         <v>4</v>
       </c>
-      <c r="E578" s="4">
+      <c r="E578" s="9">
         <v>2015</v>
       </c>
-      <c r="F578" s="3">
+      <c r="F578" s="8">
         <v>38771</v>
       </c>
       <c r="G578" s="1" t="s">
@@ -19820,10 +19857,10 @@
       <c r="D579" s="1">
         <v>6</v>
       </c>
-      <c r="E579" s="4">
+      <c r="E579" s="9">
         <v>2015</v>
       </c>
-      <c r="F579" s="3">
+      <c r="F579" s="8">
         <v>38771</v>
       </c>
       <c r="G579" s="1" t="s">
@@ -19852,10 +19889,10 @@
       <c r="D580" s="1">
         <v>1</v>
       </c>
-      <c r="E580" s="4">
+      <c r="E580" s="9">
         <v>2015</v>
       </c>
-      <c r="F580" s="2">
+      <c r="F580" s="7">
         <v>38829</v>
       </c>
       <c r="G580" s="1" t="s">
@@ -19884,10 +19921,10 @@
       <c r="D581" s="1">
         <v>2</v>
       </c>
-      <c r="E581" s="4">
+      <c r="E581" s="9">
         <v>2015</v>
       </c>
-      <c r="F581" s="3">
+      <c r="F581" s="8">
         <v>38771</v>
       </c>
       <c r="G581" s="1" t="s">
@@ -19916,10 +19953,10 @@
       <c r="D582" s="1">
         <v>3</v>
       </c>
-      <c r="E582" s="4">
+      <c r="E582" s="9">
         <v>2015</v>
       </c>
-      <c r="F582" s="3">
+      <c r="F582" s="8">
         <v>38771</v>
       </c>
       <c r="G582" s="1" t="s">
@@ -19948,10 +19985,10 @@
       <c r="D583" s="1">
         <v>6</v>
       </c>
-      <c r="E583" s="4">
+      <c r="E583" s="9">
         <v>2015</v>
       </c>
-      <c r="F583" s="3">
+      <c r="F583" s="8">
         <v>38771</v>
       </c>
       <c r="G583" s="1" t="s">
@@ -19980,10 +20017,10 @@
       <c r="D584" s="1">
         <v>9</v>
       </c>
-      <c r="E584" s="4">
+      <c r="E584" s="9">
         <v>2015</v>
       </c>
-      <c r="F584" s="3">
+      <c r="F584" s="8">
         <v>38771</v>
       </c>
       <c r="G584" s="1" t="s">
@@ -20012,10 +20049,10 @@
       <c r="D585" s="1">
         <v>0</v>
       </c>
-      <c r="E585" s="4">
+      <c r="E585" s="9">
         <v>2015</v>
       </c>
-      <c r="F585" s="3">
+      <c r="F585" s="8">
         <v>38771</v>
       </c>
       <c r="G585" s="1" t="s">
@@ -20044,10 +20081,10 @@
       <c r="D586" s="1">
         <v>2</v>
       </c>
-      <c r="E586" s="4">
+      <c r="E586" s="9">
         <v>2015</v>
       </c>
-      <c r="F586" s="3">
+      <c r="F586" s="8">
         <v>38771</v>
       </c>
       <c r="G586" s="1" t="s">
@@ -20076,10 +20113,10 @@
       <c r="D587" s="1">
         <v>3</v>
       </c>
-      <c r="E587" s="4">
+      <c r="E587" s="9">
         <v>2015</v>
       </c>
-      <c r="F587" s="3">
+      <c r="F587" s="8">
         <v>38771</v>
       </c>
       <c r="G587" s="1" t="s">
@@ -20108,10 +20145,10 @@
       <c r="D588" s="1">
         <v>4</v>
       </c>
-      <c r="E588" s="4">
+      <c r="E588" s="9">
         <v>2015</v>
       </c>
-      <c r="F588" s="3">
+      <c r="F588" s="8">
         <v>38771</v>
       </c>
       <c r="G588" s="1" t="s">
@@ -20140,10 +20177,10 @@
       <c r="D589" s="1">
         <v>5</v>
       </c>
-      <c r="E589" s="4">
+      <c r="E589" s="9">
         <v>2015</v>
       </c>
-      <c r="F589" s="3">
+      <c r="F589" s="8">
         <v>38771</v>
       </c>
       <c r="G589" s="1" t="s">
@@ -20172,10 +20209,10 @@
       <c r="D590" s="1">
         <v>6</v>
       </c>
-      <c r="E590" s="4">
+      <c r="E590" s="9">
         <v>2015</v>
       </c>
-      <c r="F590" s="3">
+      <c r="F590" s="8">
         <v>38771</v>
       </c>
       <c r="G590" s="1" t="s">
@@ -20204,10 +20241,10 @@
       <c r="D591" s="1">
         <v>8</v>
       </c>
-      <c r="E591" s="4">
+      <c r="E591" s="9">
         <v>2015</v>
       </c>
-      <c r="F591" s="3">
+      <c r="F591" s="8">
         <v>38771</v>
       </c>
       <c r="G591" s="1" t="s">
@@ -20236,10 +20273,10 @@
       <c r="D592" s="1">
         <v>2</v>
       </c>
-      <c r="E592" s="4">
+      <c r="E592" s="9">
         <v>2015</v>
       </c>
-      <c r="F592" s="3">
+      <c r="F592" s="8">
         <v>38813</v>
       </c>
       <c r="G592" s="1" t="s">
@@ -20268,10 +20305,10 @@
       <c r="D593" s="1">
         <v>3</v>
       </c>
-      <c r="E593" s="4">
+      <c r="E593" s="9">
         <v>2015</v>
       </c>
-      <c r="F593" s="3">
+      <c r="F593" s="8">
         <v>38813</v>
       </c>
       <c r="G593" s="1" t="s">
@@ -20300,10 +20337,10 @@
       <c r="D594" s="1">
         <v>4</v>
       </c>
-      <c r="E594" s="4">
+      <c r="E594" s="9">
         <v>2015</v>
       </c>
-      <c r="F594" s="3">
+      <c r="F594" s="8">
         <v>38813</v>
       </c>
       <c r="G594" s="1" t="s">
@@ -20332,10 +20369,10 @@
       <c r="D595" s="1">
         <v>3</v>
       </c>
-      <c r="E595" s="4">
+      <c r="E595" s="9">
         <v>2015</v>
       </c>
-      <c r="F595" s="3">
+      <c r="F595" s="8">
         <v>38813</v>
       </c>
       <c r="G595" s="1" t="s">
@@ -20364,10 +20401,10 @@
       <c r="D596" s="1">
         <v>0</v>
       </c>
-      <c r="E596" s="4">
+      <c r="E596" s="9">
         <v>2015</v>
       </c>
-      <c r="F596" s="3">
+      <c r="F596" s="8">
         <v>38813</v>
       </c>
       <c r="G596" s="1" t="s">
@@ -20396,10 +20433,10 @@
       <c r="D597" s="1">
         <v>2</v>
       </c>
-      <c r="E597" s="4">
+      <c r="E597" s="9">
         <v>2015</v>
       </c>
-      <c r="F597" s="3">
+      <c r="F597" s="8">
         <v>38813</v>
       </c>
       <c r="G597" s="1" t="s">
@@ -20428,10 +20465,10 @@
       <c r="D598" s="1">
         <v>3</v>
       </c>
-      <c r="E598" s="4">
+      <c r="E598" s="9">
         <v>2015</v>
       </c>
-      <c r="F598" s="3">
+      <c r="F598" s="8">
         <v>38813</v>
       </c>
       <c r="G598" s="1" t="s">
@@ -20460,10 +20497,10 @@
       <c r="D599" s="1">
         <v>4</v>
       </c>
-      <c r="E599" s="4">
+      <c r="E599" s="9">
         <v>2015</v>
       </c>
-      <c r="F599" s="3">
+      <c r="F599" s="8">
         <v>38813</v>
       </c>
       <c r="G599" s="1" t="s">
@@ -20492,10 +20529,10 @@
       <c r="D600" s="1">
         <v>5</v>
       </c>
-      <c r="E600" s="4">
+      <c r="E600" s="9">
         <v>2015</v>
       </c>
-      <c r="F600" s="3">
+      <c r="F600" s="8">
         <v>38813</v>
       </c>
       <c r="G600" s="1" t="s">
@@ -20524,10 +20561,10 @@
       <c r="D601" s="1">
         <v>2</v>
       </c>
-      <c r="E601" s="4">
+      <c r="E601" s="9">
         <v>2015</v>
       </c>
-      <c r="F601" s="3">
+      <c r="F601" s="8">
         <v>38813</v>
       </c>
       <c r="G601" s="1" t="s">
@@ -20556,10 +20593,10 @@
       <c r="D602" s="1">
         <v>1</v>
       </c>
-      <c r="E602" s="4">
+      <c r="E602" s="9">
         <v>2015</v>
       </c>
-      <c r="F602" s="3">
+      <c r="F602" s="8">
         <v>38813</v>
       </c>
       <c r="G602" s="1" t="s">
@@ -20588,10 +20625,10 @@
       <c r="D603" s="1">
         <v>2</v>
       </c>
-      <c r="E603" s="4">
+      <c r="E603" s="9">
         <v>2015</v>
       </c>
-      <c r="F603" s="3">
+      <c r="F603" s="8">
         <v>38813</v>
       </c>
       <c r="G603" s="1" t="s">
@@ -20620,10 +20657,10 @@
       <c r="D604" s="1">
         <v>3</v>
       </c>
-      <c r="E604" s="4">
+      <c r="E604" s="9">
         <v>2015</v>
       </c>
-      <c r="F604" s="3">
+      <c r="F604" s="8">
         <v>38813</v>
       </c>
       <c r="G604" s="1" t="s">
@@ -20652,10 +20689,10 @@
       <c r="D605" s="1">
         <v>1</v>
       </c>
-      <c r="E605" s="4">
+      <c r="E605" s="9">
         <v>2015</v>
       </c>
-      <c r="F605" s="3">
+      <c r="F605" s="8">
         <v>38813</v>
       </c>
       <c r="G605" s="1" t="s">
@@ -20684,10 +20721,10 @@
       <c r="D606" s="1">
         <v>2</v>
       </c>
-      <c r="E606" s="4">
+      <c r="E606" s="9">
         <v>2015</v>
       </c>
-      <c r="F606" s="3">
+      <c r="F606" s="8">
         <v>38813</v>
       </c>
       <c r="G606" s="1" t="s">
@@ -20716,10 +20753,10 @@
       <c r="D607" s="1">
         <v>3</v>
       </c>
-      <c r="E607" s="4">
+      <c r="E607" s="9">
         <v>2015</v>
       </c>
-      <c r="F607" s="3">
+      <c r="F607" s="8">
         <v>38813</v>
       </c>
       <c r="G607" s="1" t="s">
@@ -20748,10 +20785,10 @@
       <c r="D608" s="1">
         <v>4</v>
       </c>
-      <c r="E608" s="4">
+      <c r="E608" s="9">
         <v>2015</v>
       </c>
-      <c r="F608" s="3">
+      <c r="F608" s="8">
         <v>38813</v>
       </c>
       <c r="G608" s="1" t="s">
@@ -20780,10 +20817,10 @@
       <c r="D609" s="1">
         <v>1</v>
       </c>
-      <c r="E609" s="4">
+      <c r="E609" s="9">
         <v>2015</v>
       </c>
-      <c r="F609" s="3">
+      <c r="F609" s="8">
         <v>38813</v>
       </c>
       <c r="G609" s="1" t="s">
@@ -20812,10 +20849,10 @@
       <c r="D610" s="1">
         <v>2</v>
       </c>
-      <c r="E610" s="4">
+      <c r="E610" s="9">
         <v>2015</v>
       </c>
-      <c r="F610" s="3">
+      <c r="F610" s="8">
         <v>38813</v>
       </c>
       <c r="G610" s="1" t="s">
@@ -20844,10 +20881,10 @@
       <c r="D611" s="1">
         <v>3</v>
       </c>
-      <c r="E611" s="4">
+      <c r="E611" s="9">
         <v>2015</v>
       </c>
-      <c r="F611" s="3">
+      <c r="F611" s="8">
         <v>38813</v>
       </c>
       <c r="G611" s="1" t="s">
@@ -20876,10 +20913,10 @@
       <c r="D612" s="1">
         <v>4</v>
       </c>
-      <c r="E612" s="4">
+      <c r="E612" s="9">
         <v>2015</v>
       </c>
-      <c r="F612" s="3">
+      <c r="F612" s="8">
         <v>38813</v>
       </c>
       <c r="G612" s="1" t="s">
@@ -20908,10 +20945,10 @@
       <c r="D613" s="1">
         <v>5</v>
       </c>
-      <c r="E613" s="4">
+      <c r="E613" s="9">
         <v>2015</v>
       </c>
-      <c r="F613" s="3">
+      <c r="F613" s="8">
         <v>38813</v>
       </c>
       <c r="G613" s="1" t="s">
@@ -20940,10 +20977,10 @@
       <c r="D614" s="1">
         <v>0</v>
       </c>
-      <c r="E614" s="4">
+      <c r="E614" s="9">
         <v>2015</v>
       </c>
-      <c r="F614" s="3">
+      <c r="F614" s="8">
         <v>38813</v>
       </c>
       <c r="G614" s="1" t="s">
@@ -20972,10 +21009,10 @@
       <c r="D615" s="1">
         <v>1</v>
       </c>
-      <c r="E615" s="4">
+      <c r="E615" s="9">
         <v>2015</v>
       </c>
-      <c r="F615" s="3">
+      <c r="F615" s="8">
         <v>38813</v>
       </c>
       <c r="G615" s="1" t="s">
@@ -21004,10 +21041,10 @@
       <c r="D616" s="1">
         <v>2</v>
       </c>
-      <c r="E616" s="4">
+      <c r="E616" s="9">
         <v>2015</v>
       </c>
-      <c r="F616" s="3">
+      <c r="F616" s="8">
         <v>38813</v>
       </c>
       <c r="G616" s="1" t="s">
@@ -21036,10 +21073,10 @@
       <c r="D617" s="1">
         <v>3</v>
       </c>
-      <c r="E617" s="4">
+      <c r="E617" s="9">
         <v>2015</v>
       </c>
-      <c r="F617" s="3">
+      <c r="F617" s="8">
         <v>38813</v>
       </c>
       <c r="G617" s="1" t="s">
@@ -21068,10 +21105,10 @@
       <c r="D618" s="1">
         <v>2</v>
       </c>
-      <c r="E618" s="4">
+      <c r="E618" s="9">
         <v>2015</v>
       </c>
-      <c r="F618" s="3">
+      <c r="F618" s="8">
         <v>38813</v>
       </c>
       <c r="G618" s="1" t="s">
@@ -21100,10 +21137,10 @@
       <c r="D619" s="1">
         <v>3</v>
       </c>
-      <c r="E619" s="4">
+      <c r="E619" s="9">
         <v>2015</v>
       </c>
-      <c r="F619" s="3">
+      <c r="F619" s="8">
         <v>38813</v>
       </c>
       <c r="G619" s="1" t="s">
@@ -21132,10 +21169,10 @@
       <c r="D620" s="1">
         <v>4</v>
       </c>
-      <c r="E620" s="4">
+      <c r="E620" s="9">
         <v>2015</v>
       </c>
-      <c r="F620" s="3">
+      <c r="F620" s="8">
         <v>38813</v>
       </c>
       <c r="G620" s="1" t="s">
@@ -21164,10 +21201,10 @@
       <c r="D621" s="1">
         <v>5</v>
       </c>
-      <c r="E621" s="4">
+      <c r="E621" s="9">
         <v>2015</v>
       </c>
-      <c r="F621" s="3">
+      <c r="F621" s="8">
         <v>38813</v>
       </c>
       <c r="G621" s="1" t="s">
@@ -21196,10 +21233,10 @@
       <c r="D622" s="1">
         <v>1</v>
       </c>
-      <c r="E622" s="4">
+      <c r="E622" s="9">
         <v>2015</v>
       </c>
-      <c r="F622" s="3">
+      <c r="F622" s="8">
         <v>38813</v>
       </c>
       <c r="G622" s="1" t="s">
@@ -21228,10 +21265,10 @@
       <c r="D623" s="1">
         <v>2</v>
       </c>
-      <c r="E623" s="4">
+      <c r="E623" s="9">
         <v>2015</v>
       </c>
-      <c r="F623" s="3">
+      <c r="F623" s="8">
         <v>38813</v>
       </c>
       <c r="G623" s="1" t="s">
@@ -21260,10 +21297,10 @@
       <c r="D624" s="1">
         <v>3</v>
       </c>
-      <c r="E624" s="4">
+      <c r="E624" s="9">
         <v>2015</v>
       </c>
-      <c r="F624" s="3">
+      <c r="F624" s="8">
         <v>38813</v>
       </c>
       <c r="G624" s="1" t="s">
@@ -21292,10 +21329,10 @@
       <c r="D625" s="1">
         <v>6</v>
       </c>
-      <c r="E625" s="4">
+      <c r="E625" s="9">
         <v>2015</v>
       </c>
-      <c r="F625" s="3">
+      <c r="F625" s="8">
         <v>38813</v>
       </c>
       <c r="G625" s="1" t="s">
@@ -21324,10 +21361,10 @@
       <c r="D626" s="1">
         <v>3</v>
       </c>
-      <c r="E626" s="4">
+      <c r="E626" s="9">
         <v>2015</v>
       </c>
-      <c r="F626" s="3">
+      <c r="F626" s="8">
         <v>38813</v>
       </c>
       <c r="G626" s="1" t="s">
@@ -21356,10 +21393,10 @@
       <c r="D627" s="1">
         <v>0</v>
       </c>
-      <c r="E627" s="4">
+      <c r="E627" s="9">
         <v>2015</v>
       </c>
-      <c r="F627" s="3">
+      <c r="F627" s="8">
         <v>38813</v>
       </c>
       <c r="G627" s="1" t="s">
@@ -21388,10 +21425,10 @@
       <c r="D628" s="1">
         <v>1</v>
       </c>
-      <c r="E628" s="4">
+      <c r="E628" s="9">
         <v>2015</v>
       </c>
-      <c r="F628" s="3">
+      <c r="F628" s="8">
         <v>38813</v>
       </c>
       <c r="G628" s="1" t="s">
@@ -21420,10 +21457,10 @@
       <c r="D629" s="1">
         <v>2</v>
       </c>
-      <c r="E629" s="4">
+      <c r="E629" s="9">
         <v>2015</v>
       </c>
-      <c r="F629" s="3">
+      <c r="F629" s="8">
         <v>38813</v>
       </c>
       <c r="G629" s="1" t="s">
@@ -21452,10 +21489,10 @@
       <c r="D630" s="1">
         <v>4</v>
       </c>
-      <c r="E630" s="4">
+      <c r="E630" s="9">
         <v>2015</v>
       </c>
-      <c r="F630" s="3">
+      <c r="F630" s="8">
         <v>38813</v>
       </c>
       <c r="G630" s="1" t="s">
@@ -21484,10 +21521,10 @@
       <c r="D631" s="1">
         <v>5</v>
       </c>
-      <c r="E631" s="4">
+      <c r="E631" s="9">
         <v>2015</v>
       </c>
-      <c r="F631" s="3">
+      <c r="F631" s="8">
         <v>38813</v>
       </c>
       <c r="G631" s="1" t="s">
@@ -21516,10 +21553,10 @@
       <c r="D632" s="1">
         <v>6</v>
       </c>
-      <c r="E632" s="4">
+      <c r="E632" s="9">
         <v>2015</v>
       </c>
-      <c r="F632" s="3">
+      <c r="F632" s="8">
         <v>38813</v>
       </c>
       <c r="G632" s="1" t="s">
@@ -21548,10 +21585,10 @@
       <c r="D633" s="1">
         <v>8</v>
       </c>
-      <c r="E633" s="4">
+      <c r="E633" s="9">
         <v>2015</v>
       </c>
-      <c r="F633" s="3">
+      <c r="F633" s="8">
         <v>38813</v>
       </c>
       <c r="G633" s="1" t="s">
@@ -21580,10 +21617,10 @@
       <c r="D634" s="1">
         <v>4</v>
       </c>
-      <c r="E634" s="4">
+      <c r="E634" s="9">
         <v>2015</v>
       </c>
-      <c r="F634" s="2">
+      <c r="F634" s="7">
         <v>38829</v>
       </c>
       <c r="G634" s="1" t="s">
@@ -21612,10 +21649,10 @@
       <c r="D635" s="1">
         <v>4</v>
       </c>
-      <c r="E635" s="4">
+      <c r="E635" s="9">
         <v>2015</v>
       </c>
-      <c r="F635" s="2">
+      <c r="F635" s="7">
         <v>38829</v>
       </c>
       <c r="G635" s="1" t="s">
@@ -21644,10 +21681,10 @@
       <c r="D636" s="1">
         <v>0</v>
       </c>
-      <c r="E636" s="4">
+      <c r="E636" s="9">
         <v>2015</v>
       </c>
-      <c r="F636" s="2">
+      <c r="F636" s="7">
         <v>38829</v>
       </c>
       <c r="G636" s="1" t="s">
@@ -21676,10 +21713,10 @@
       <c r="D637" s="1">
         <v>1</v>
       </c>
-      <c r="E637" s="4">
+      <c r="E637" s="9">
         <v>2015</v>
       </c>
-      <c r="F637" s="2">
+      <c r="F637" s="7">
         <v>38829</v>
       </c>
       <c r="G637" s="1" t="s">
@@ -21708,10 +21745,10 @@
       <c r="D638" s="1">
         <v>2</v>
       </c>
-      <c r="E638" s="4">
+      <c r="E638" s="9">
         <v>2015</v>
       </c>
-      <c r="F638" s="2">
+      <c r="F638" s="7">
         <v>38829</v>
       </c>
       <c r="G638" s="1" t="s">
@@ -21740,10 +21777,10 @@
       <c r="D639" s="1">
         <v>3</v>
       </c>
-      <c r="E639" s="4">
+      <c r="E639" s="9">
         <v>2015</v>
       </c>
-      <c r="F639" s="2">
+      <c r="F639" s="7">
         <v>38829</v>
       </c>
       <c r="G639" s="1" t="s">
@@ -21772,10 +21809,10 @@
       <c r="D640" s="1">
         <v>2</v>
       </c>
-      <c r="E640" s="4">
+      <c r="E640" s="9">
         <v>2015</v>
       </c>
-      <c r="F640" s="2">
+      <c r="F640" s="7">
         <v>38829</v>
       </c>
       <c r="G640" s="1" t="s">
@@ -21804,10 +21841,10 @@
       <c r="D641" s="1">
         <v>1</v>
       </c>
-      <c r="E641" s="4">
+      <c r="E641" s="9">
         <v>2015</v>
       </c>
-      <c r="F641" s="2">
+      <c r="F641" s="7">
         <v>38829</v>
       </c>
       <c r="G641" s="1" t="s">
@@ -21836,10 +21873,10 @@
       <c r="D642" s="1">
         <v>2</v>
       </c>
-      <c r="E642" s="4">
+      <c r="E642" s="9">
         <v>2015</v>
       </c>
-      <c r="F642" s="2">
+      <c r="F642" s="7">
         <v>38829</v>
       </c>
       <c r="G642" s="1" t="s">
@@ -21868,10 +21905,10 @@
       <c r="D643" s="1">
         <v>3</v>
       </c>
-      <c r="E643" s="4">
+      <c r="E643" s="9">
         <v>2015</v>
       </c>
-      <c r="F643" s="2">
+      <c r="F643" s="7">
         <v>38829</v>
       </c>
       <c r="G643" s="1" t="s">
@@ -21900,10 +21937,10 @@
       <c r="D644" s="1">
         <v>3</v>
       </c>
-      <c r="E644" s="4">
+      <c r="E644" s="9">
         <v>2015</v>
       </c>
-      <c r="F644" s="2">
+      <c r="F644" s="7">
         <v>38829</v>
       </c>
       <c r="G644" s="1" t="s">
@@ -21932,10 +21969,10 @@
       <c r="D645" s="1">
         <v>2</v>
       </c>
-      <c r="E645" s="4">
+      <c r="E645" s="9">
         <v>2015</v>
       </c>
-      <c r="F645" s="2">
+      <c r="F645" s="7">
         <v>38829</v>
       </c>
       <c r="G645" s="1" t="s">
@@ -21964,10 +22001,10 @@
       <c r="D646" s="1">
         <v>3</v>
       </c>
-      <c r="E646" s="4">
+      <c r="E646" s="9">
         <v>2015</v>
       </c>
-      <c r="F646" s="2">
+      <c r="F646" s="7">
         <v>38829</v>
       </c>
       <c r="G646" s="1" t="s">
@@ -21996,10 +22033,10 @@
       <c r="D647" s="1">
         <v>5</v>
       </c>
-      <c r="E647" s="4">
+      <c r="E647" s="9">
         <v>2015</v>
       </c>
-      <c r="F647" s="2">
+      <c r="F647" s="7">
         <v>38829</v>
       </c>
       <c r="G647" s="1" t="s">
@@ -22028,10 +22065,10 @@
       <c r="D648" s="1">
         <v>2</v>
       </c>
-      <c r="E648" s="4">
+      <c r="E648" s="9">
         <v>2015</v>
       </c>
-      <c r="F648" s="2">
+      <c r="F648" s="7">
         <v>38829</v>
       </c>
       <c r="G648" s="1" t="s">
@@ -22060,10 +22097,10 @@
       <c r="D649" s="1">
         <v>2</v>
       </c>
-      <c r="E649" s="4">
+      <c r="E649" s="9">
         <v>2015</v>
       </c>
-      <c r="F649" s="2">
+      <c r="F649" s="7">
         <v>38829</v>
       </c>
       <c r="G649" s="1" t="s">
@@ -22092,10 +22129,10 @@
       <c r="D650" s="1">
         <v>3</v>
       </c>
-      <c r="E650" s="4">
+      <c r="E650" s="9">
         <v>2015</v>
       </c>
-      <c r="F650" s="2">
+      <c r="F650" s="7">
         <v>38829</v>
       </c>
       <c r="G650" s="1" t="s">
@@ -22124,10 +22161,10 @@
       <c r="D651" s="1">
         <v>4</v>
       </c>
-      <c r="E651" s="4">
+      <c r="E651" s="9">
         <v>2015</v>
       </c>
-      <c r="F651" s="2">
+      <c r="F651" s="7">
         <v>38829</v>
       </c>
       <c r="G651" s="1" t="s">
@@ -22156,10 +22193,10 @@
       <c r="D652" s="1">
         <v>0</v>
       </c>
-      <c r="E652" s="4">
+      <c r="E652" s="9">
         <v>2015</v>
       </c>
-      <c r="F652" s="2">
+      <c r="F652" s="7">
         <v>38829</v>
       </c>
       <c r="G652" s="1" t="s">
@@ -22188,10 +22225,10 @@
       <c r="D653" s="1">
         <v>1</v>
       </c>
-      <c r="E653" s="4">
+      <c r="E653" s="9">
         <v>2015</v>
       </c>
-      <c r="F653" s="2">
+      <c r="F653" s="7">
         <v>38829</v>
       </c>
       <c r="G653" s="1" t="s">
@@ -22220,10 +22257,10 @@
       <c r="D654" s="1">
         <v>2</v>
       </c>
-      <c r="E654" s="4">
+      <c r="E654" s="9">
         <v>2015</v>
       </c>
-      <c r="F654" s="2">
+      <c r="F654" s="7">
         <v>38829</v>
       </c>
       <c r="G654" s="1" t="s">
@@ -22252,10 +22289,10 @@
       <c r="D655" s="1">
         <v>4</v>
       </c>
-      <c r="E655" s="4">
+      <c r="E655" s="9">
         <v>2015</v>
       </c>
-      <c r="F655" s="2">
+      <c r="F655" s="7">
         <v>38829</v>
       </c>
       <c r="G655" s="1" t="s">
@@ -22284,10 +22321,10 @@
       <c r="D656" s="1">
         <v>5</v>
       </c>
-      <c r="E656" s="4">
+      <c r="E656" s="9">
         <v>2015</v>
       </c>
-      <c r="F656" s="2">
+      <c r="F656" s="7">
         <v>38829</v>
       </c>
       <c r="G656" s="1" t="s">
@@ -22316,10 +22353,10 @@
       <c r="D657" s="1">
         <v>2</v>
       </c>
-      <c r="E657" s="4">
+      <c r="E657" s="9">
         <v>2015</v>
       </c>
-      <c r="F657" s="2">
+      <c r="F657" s="7">
         <v>38829</v>
       </c>
       <c r="G657" s="1" t="s">
@@ -22348,10 +22385,10 @@
       <c r="D658" s="1">
         <v>1</v>
       </c>
-      <c r="E658" s="4">
+      <c r="E658" s="9">
         <v>2015</v>
       </c>
-      <c r="F658" s="2">
+      <c r="F658" s="7">
         <v>38829</v>
       </c>
       <c r="G658" s="1" t="s">
@@ -22380,10 +22417,10 @@
       <c r="D659" s="1">
         <v>2</v>
       </c>
-      <c r="E659" s="4">
+      <c r="E659" s="9">
         <v>2015</v>
       </c>
-      <c r="F659" s="2">
+      <c r="F659" s="7">
         <v>38829</v>
       </c>
       <c r="G659" s="1" t="s">
@@ -22412,10 +22449,10 @@
       <c r="D660" s="1">
         <v>4</v>
       </c>
-      <c r="E660" s="4">
+      <c r="E660" s="9">
         <v>2015</v>
       </c>
-      <c r="F660" s="2">
+      <c r="F660" s="7">
         <v>38829</v>
       </c>
       <c r="G660" s="1" t="s">
@@ -22444,10 +22481,10 @@
       <c r="D661" s="1">
         <v>0</v>
       </c>
-      <c r="E661" s="4">
+      <c r="E661" s="9">
         <v>2015</v>
       </c>
-      <c r="F661" s="2">
+      <c r="F661" s="7">
         <v>38829</v>
       </c>
       <c r="G661" s="1" t="s">
@@ -22476,10 +22513,10 @@
       <c r="D662" s="1">
         <v>1</v>
       </c>
-      <c r="E662" s="4">
+      <c r="E662" s="9">
         <v>2015</v>
       </c>
-      <c r="F662" s="2">
+      <c r="F662" s="7">
         <v>38829</v>
       </c>
       <c r="G662" s="1" t="s">
@@ -22508,10 +22545,10 @@
       <c r="D663" s="1">
         <v>2</v>
       </c>
-      <c r="E663" s="4">
+      <c r="E663" s="9">
         <v>2015</v>
       </c>
-      <c r="F663" s="2">
+      <c r="F663" s="7">
         <v>38829</v>
       </c>
       <c r="G663" s="1" t="s">
@@ -22540,10 +22577,10 @@
       <c r="D664" s="1">
         <v>3</v>
       </c>
-      <c r="E664" s="4">
+      <c r="E664" s="9">
         <v>2015</v>
       </c>
-      <c r="F664" s="2">
+      <c r="F664" s="7">
         <v>38829</v>
       </c>
       <c r="G664" s="1" t="s">
@@ -22572,10 +22609,10 @@
       <c r="D665" s="1">
         <v>5</v>
       </c>
-      <c r="E665" s="4">
+      <c r="E665" s="9">
         <v>2015</v>
       </c>
-      <c r="F665" s="2">
+      <c r="F665" s="7">
         <v>38829</v>
       </c>
       <c r="G665" s="1" t="s">
@@ -22604,10 +22641,10 @@
       <c r="D666" s="1">
         <v>6</v>
       </c>
-      <c r="E666" s="4">
+      <c r="E666" s="9">
         <v>2015</v>
       </c>
-      <c r="F666" s="2">
+      <c r="F666" s="7">
         <v>38829</v>
       </c>
       <c r="G666" s="1" t="s">
@@ -22624,40 +22661,40 @@
       </c>
     </row>
     <row r="667" spans="6:6">
-      <c r="F667" s="2"/>
+      <c r="F667" s="7"/>
     </row>
     <row r="668" spans="6:6">
-      <c r="F668" s="2"/>
+      <c r="F668" s="7"/>
     </row>
     <row r="669" spans="6:6">
-      <c r="F669" s="2"/>
+      <c r="F669" s="7"/>
     </row>
     <row r="670" spans="6:6">
-      <c r="F670" s="2"/>
+      <c r="F670" s="7"/>
     </row>
     <row r="671" spans="6:6">
-      <c r="F671" s="2"/>
+      <c r="F671" s="7"/>
     </row>
     <row r="672" spans="6:6">
-      <c r="F672" s="2"/>
+      <c r="F672" s="7"/>
     </row>
     <row r="673" spans="6:6">
-      <c r="F673" s="2"/>
+      <c r="F673" s="7"/>
     </row>
     <row r="674" spans="6:6">
-      <c r="F674" s="2"/>
+      <c r="F674" s="7"/>
     </row>
     <row r="675" spans="6:6">
-      <c r="F675" s="2"/>
+      <c r="F675" s="7"/>
     </row>
     <row r="676" spans="6:6">
-      <c r="F676" s="2"/>
+      <c r="F676" s="7"/>
     </row>
     <row r="677" spans="6:6">
-      <c r="F677" s="2"/>
+      <c r="F677" s="7"/>
     </row>
     <row r="678" spans="6:6">
-      <c r="F678" s="2"/>
+      <c r="F678" s="7"/>
     </row>
     <row r="1048546" customFormat="1"/>
     <row r="1048547" customFormat="1"/>
@@ -22674,7 +22711,7 @@
     <row r="1048558" customFormat="1"/>
     <row r="1048559" customFormat="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:J334" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:J666" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:J666">
@@ -22683,4 +22720,3033 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K94"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="40.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G2" s="5">
+        <v>38815</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G3" s="5">
+        <v>38815</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G4" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4">
+        <v>8</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G5" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="4">
+        <v>5</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G6" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G7" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="4">
+        <v>5</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G8" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G9" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2006</v>
+      </c>
+      <c r="G10" s="5">
+        <v>38820</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>7</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4">
+        <v>9</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G11" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="4">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G12" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="4">
+        <v>12</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="2">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G13" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>5</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G14" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="4">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="2">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>7</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G15" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="4">
+        <v>5</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="2">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2007</v>
+      </c>
+      <c r="G16" s="5">
+        <v>38789</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>14</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="2">
+        <v>169</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="4">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G17" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="4">
+        <v>2</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="2">
+        <v>170</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="4">
+        <v>6</v>
+      </c>
+      <c r="E18" s="4">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G18" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="4">
+        <v>4</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="2">
+        <v>171</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G19" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="4">
+        <v>5</v>
+      </c>
+      <c r="J19" s="4">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="2">
+        <v>172</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="4">
+        <v>6</v>
+      </c>
+      <c r="E20" s="4">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G20" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="4">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="2">
+        <v>173</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G21" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="2">
+        <v>175</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4">
+        <v>6</v>
+      </c>
+      <c r="E22" s="4">
+        <v>8</v>
+      </c>
+      <c r="F22" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G22" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="4">
+        <v>16</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="2">
+        <v>176</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="4">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4">
+        <v>10</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G23" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="4">
+        <v>4</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="2">
+        <v>177</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G24" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="2">
+        <v>178</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G25" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="4">
+        <v>4</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2">
+        <v>179</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>4</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G26" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="4">
+        <v>6</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="2">
+        <v>180</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G27" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="2">
+        <v>181</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4">
+        <v>2009</v>
+      </c>
+      <c r="G28" s="5">
+        <v>38804</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="4">
+        <v>3</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="2">
+        <v>237</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="4">
+        <v>6</v>
+      </c>
+      <c r="E29" s="4">
+        <v>9</v>
+      </c>
+      <c r="F29" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G29" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="4">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="2">
+        <v>238</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="4">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4">
+        <v>9</v>
+      </c>
+      <c r="F30" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G30" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="4">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="2">
+        <v>239</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G31" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="2">
+        <v>240</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G32" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="4">
+        <v>4</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="2">
+        <v>241</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G33" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2">
+        <v>242</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="4">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G34" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>6</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="2">
+        <v>243</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="4">
+        <v>6</v>
+      </c>
+      <c r="E35" s="4">
+        <v>9</v>
+      </c>
+      <c r="F35" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G35" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="4">
+        <v>2</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="2">
+        <v>244</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="4">
+        <v>6</v>
+      </c>
+      <c r="E36" s="4">
+        <v>10</v>
+      </c>
+      <c r="F36" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G36" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2">
+        <v>245</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G37" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="4">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="2">
+        <v>246</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G38" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="4">
+        <v>3</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2">
+        <v>247</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
+        <v>4</v>
+      </c>
+      <c r="F39" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G39" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="4">
+        <v>2</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="2">
+        <v>248</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="4">
+        <v>10</v>
+      </c>
+      <c r="E40" s="4">
+        <v>9</v>
+      </c>
+      <c r="F40" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G40" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="4">
+        <v>2</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="2">
+        <v>249</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="4">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G41" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4">
+        <v>5</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="2">
+        <v>250</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="4">
+        <v>7</v>
+      </c>
+      <c r="E42" s="4">
+        <v>8</v>
+      </c>
+      <c r="F42" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G42" s="5">
+        <v>38813</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="4">
+        <v>2</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="2">
+        <v>252</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="4">
+        <v>6</v>
+      </c>
+      <c r="E43" s="4">
+        <v>8</v>
+      </c>
+      <c r="F43" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G43" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" s="4">
+        <v>4</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2">
+        <v>253</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="4">
+        <v>6</v>
+      </c>
+      <c r="E44" s="4">
+        <v>9</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G44" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="4">
+        <v>5</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="2">
+        <v>254</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G45" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="4">
+        <v>2</v>
+      </c>
+      <c r="J45" s="4">
+        <v>25</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="2">
+        <v>255</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="4">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G46" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="4">
+        <v>12</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="2">
+        <v>256</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="4">
+        <v>3</v>
+      </c>
+      <c r="E47" s="4">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G47" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="4">
+        <v>8</v>
+      </c>
+      <c r="J47" s="4">
+        <v>3</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="2">
+        <v>257</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4">
+        <v>2</v>
+      </c>
+      <c r="F48" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G48" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="4">
+        <v>1</v>
+      </c>
+      <c r="J48" s="4">
+        <v>5</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="2">
+        <v>258</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="4">
+        <v>2</v>
+      </c>
+      <c r="E49" s="4">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G49" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="4">
+        <v>4</v>
+      </c>
+      <c r="J49" s="4">
+        <v>1</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="2">
+        <v>259</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="4">
+        <v>7</v>
+      </c>
+      <c r="E50" s="4">
+        <v>8</v>
+      </c>
+      <c r="F50" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G50" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="4">
+        <v>7</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="2">
+        <v>260</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="4">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4">
+        <v>9</v>
+      </c>
+      <c r="F51" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G51" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="4">
+        <v>2</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="2">
+        <v>261</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G52" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="4">
+        <v>1</v>
+      </c>
+      <c r="J52" s="4">
+        <v>3</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="2">
+        <v>262</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="4">
+        <v>2</v>
+      </c>
+      <c r="E53" s="4">
+        <v>3</v>
+      </c>
+      <c r="F53" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G53" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="4">
+        <v>3</v>
+      </c>
+      <c r="J53" s="4">
+        <v>4</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="2">
+        <v>263</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="4">
+        <v>3</v>
+      </c>
+      <c r="E54" s="4">
+        <v>4</v>
+      </c>
+      <c r="F54" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G54" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="4">
+        <v>3</v>
+      </c>
+      <c r="J54" s="4">
+        <v>2</v>
+      </c>
+      <c r="K54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="2">
+        <v>264</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="4">
+        <v>7</v>
+      </c>
+      <c r="E55" s="4">
+        <v>8</v>
+      </c>
+      <c r="F55" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G55" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="4">
+        <v>5</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="2">
+        <v>265</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="4">
+        <v>2</v>
+      </c>
+      <c r="E56" s="4">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G56" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="4">
+        <v>5</v>
+      </c>
+      <c r="J56" s="4">
+        <v>16</v>
+      </c>
+      <c r="K56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="2">
+        <v>266</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="4">
+        <v>6</v>
+      </c>
+      <c r="E57" s="4">
+        <v>7</v>
+      </c>
+      <c r="F57" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G57" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="4">
+        <v>3</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="2">
+        <v>267</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="4">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4">
+        <v>8</v>
+      </c>
+      <c r="F58" s="4">
+        <v>2010</v>
+      </c>
+      <c r="G58" s="5">
+        <v>38819</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="4">
+        <v>2</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="2">
+        <v>296</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G59" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" s="4">
+        <v>5</v>
+      </c>
+      <c r="J59" s="4">
+        <v>6</v>
+      </c>
+      <c r="K59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="2">
+        <v>297</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="4">
+        <v>4</v>
+      </c>
+      <c r="E60" s="4">
+        <v>8</v>
+      </c>
+      <c r="F60" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G60" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="4">
+        <v>5</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="2">
+        <v>298</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="4">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G61" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="4">
+        <v>6</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="2">
+        <v>299</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G62" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="4">
+        <v>3</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="2">
+        <v>300</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="4">
+        <v>6</v>
+      </c>
+      <c r="E63" s="4">
+        <v>8</v>
+      </c>
+      <c r="F63" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G63" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="4">
+        <v>4</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="2">
+        <v>301</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G64" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="4">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="2">
+        <v>302</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="4">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4">
+        <v>3</v>
+      </c>
+      <c r="F65" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G65" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="4">
+        <v>3</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="2">
+        <v>303</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="4">
+        <v>3</v>
+      </c>
+      <c r="E66" s="4">
+        <v>4</v>
+      </c>
+      <c r="F66" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G66" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="4">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="2">
+        <v>304</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G67" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="4">
+        <v>4</v>
+      </c>
+      <c r="J67" s="4">
+        <v>6</v>
+      </c>
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="2">
+        <v>305</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="4">
+        <v>7</v>
+      </c>
+      <c r="E68" s="4">
+        <v>8</v>
+      </c>
+      <c r="F68" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G68" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" s="4">
+        <v>12</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="2">
+        <v>307</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G69" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" s="4">
+        <v>3</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="2">
+        <v>308</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="4">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G70" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I70" s="4">
+        <v>2</v>
+      </c>
+      <c r="J70" s="4">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="2">
+        <v>309</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G71" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I71" s="4">
+        <v>2</v>
+      </c>
+      <c r="J71" s="4">
+        <v>5</v>
+      </c>
+      <c r="K71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="2">
+        <v>310</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="4">
+        <v>2</v>
+      </c>
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G72" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="4">
+        <v>5</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="2">
+        <v>311</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="4">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G73" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="4">
+        <v>2</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="2">
+        <v>312</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="4">
+        <v>2</v>
+      </c>
+      <c r="E74" s="4">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G74" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="4">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4">
+        <v>3</v>
+      </c>
+      <c r="K74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="2">
+        <v>313</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="4">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G75" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" s="4">
+        <v>3</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+      <c r="K75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="2">
+        <v>314</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G76" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="4">
+        <v>5</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0</v>
+      </c>
+      <c r="K76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="2">
+        <v>315</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G77" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="4">
+        <v>1</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1</v>
+      </c>
+      <c r="K77" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="2">
+        <v>316</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="4">
+        <v>2</v>
+      </c>
+      <c r="E78" s="4">
+        <v>3</v>
+      </c>
+      <c r="F78" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G78" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="4">
+        <v>4</v>
+      </c>
+      <c r="J78" s="4">
+        <v>7</v>
+      </c>
+      <c r="K78" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="2">
+        <v>317</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="4">
+        <v>3</v>
+      </c>
+      <c r="E79" s="4">
+        <v>4</v>
+      </c>
+      <c r="F79" s="4">
+        <v>2011</v>
+      </c>
+      <c r="G79" s="5">
+        <v>38832</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="4">
+        <v>2</v>
+      </c>
+      <c r="J79" s="4">
+        <v>1</v>
+      </c>
+      <c r="K79" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2">
+        <v>353</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G80" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="4">
+        <v>2</v>
+      </c>
+      <c r="J80" s="4">
+        <v>6</v>
+      </c>
+      <c r="K80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="2">
+        <v>354</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="4">
+        <v>6</v>
+      </c>
+      <c r="E81" s="4">
+        <v>9</v>
+      </c>
+      <c r="F81" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G81" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="4">
+        <v>2</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="2">
+        <v>355</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="4">
+        <v>6</v>
+      </c>
+      <c r="E82" s="4">
+        <v>8</v>
+      </c>
+      <c r="F82" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G82" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I82" s="4">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4">
+        <v>6</v>
+      </c>
+      <c r="K82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="2">
+        <v>357</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="4">
+        <v>2</v>
+      </c>
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G83" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="4">
+        <v>2</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0</v>
+      </c>
+      <c r="K83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="2">
+        <v>358</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4">
+        <v>2</v>
+      </c>
+      <c r="F84" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G84" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="4">
+        <v>1</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="2">
+        <v>359</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="4">
+        <v>7</v>
+      </c>
+      <c r="E85" s="4">
+        <v>9</v>
+      </c>
+      <c r="F85" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G85" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" s="4">
+        <v>2</v>
+      </c>
+      <c r="J85" s="4">
+        <v>0</v>
+      </c>
+      <c r="K85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="2">
+        <v>360</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" s="4">
+        <v>6</v>
+      </c>
+      <c r="E86" s="4">
+        <v>8</v>
+      </c>
+      <c r="F86" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G86" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="4">
+        <v>2</v>
+      </c>
+      <c r="J86" s="4">
+        <v>0</v>
+      </c>
+      <c r="K86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="2">
+        <v>361</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="4">
+        <v>6</v>
+      </c>
+      <c r="E87" s="4">
+        <v>5</v>
+      </c>
+      <c r="F87" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G87" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" s="4">
+        <v>5</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0</v>
+      </c>
+      <c r="K87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="2">
+        <v>363</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G88" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" s="4">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4">
+        <v>6</v>
+      </c>
+      <c r="K88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="2">
+        <v>364</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="4">
+        <v>7</v>
+      </c>
+      <c r="E89" s="4">
+        <v>8</v>
+      </c>
+      <c r="F89" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G89" s="5">
+        <v>38821</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89" s="4">
+        <v>5</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0</v>
+      </c>
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="2">
+        <v>426</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="4">
+        <v>6</v>
+      </c>
+      <c r="E90" s="4">
+        <v>9</v>
+      </c>
+      <c r="F90" s="4">
+        <v>2013</v>
+      </c>
+      <c r="G90" s="5">
+        <v>38814</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="4">
+        <v>2</v>
+      </c>
+      <c r="J90" s="4">
+        <v>0</v>
+      </c>
+      <c r="K90" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="2">
+        <v>429</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="4">
+        <v>6</v>
+      </c>
+      <c r="E91" s="4">
+        <v>6</v>
+      </c>
+      <c r="F91" s="4">
+        <v>2013</v>
+      </c>
+      <c r="G91" s="5">
+        <v>38814</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91" s="4">
+        <v>2</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="2">
+        <v>433</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="4">
+        <v>6</v>
+      </c>
+      <c r="E92" s="4">
+        <v>10</v>
+      </c>
+      <c r="F92" s="4">
+        <v>2013</v>
+      </c>
+      <c r="G92" s="5">
+        <v>38814</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="4">
+        <v>2</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="2">
+        <v>434</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4">
+        <v>2</v>
+      </c>
+      <c r="F93" s="4">
+        <v>2013</v>
+      </c>
+      <c r="G93" s="5">
+        <v>38814</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="4">
+        <v>1</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="2">
+        <v>436</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" s="4">
+        <v>7</v>
+      </c>
+      <c r="E94" s="4">
+        <v>8</v>
+      </c>
+      <c r="F94" s="4">
+        <v>2013</v>
+      </c>
+      <c r="G94" s="5">
+        <v>38814</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94" s="4">
+        <v>4</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+      <c r="K94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K94" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Swans/R_calc_swans/Data/swans.xlsx
+++ b/Swans/R_calc_swans/Data/swans.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Text\Article\Articles_in_progress\Swans\R_calc_swans\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B353BA59-BCDA-412B-B0BF-1E2482E6451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_data" sheetId="1" r:id="rId1"/>
@@ -24,9 +30,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -54,15 +61,6 @@
   </si>
   <si>
     <t>Site</t>
-  </si>
-  <si>
-    <t>Sp1</t>
-  </si>
-  <si>
-    <t>Sp2</t>
-  </si>
-  <si>
-    <t>Sp3</t>
   </si>
   <si>
     <t>Нарвский залив у Гакково</t>
@@ -139,19 +137,24 @@
   <si>
     <t>coastal shallow ice floes</t>
   </si>
+  <si>
+    <t>C.olor</t>
+  </si>
+  <si>
+    <t>C.cygnus</t>
+  </si>
+  <si>
+    <t>C.bewickii</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="[$-419]d\ mmm;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="[$-419]d\ mmm;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,152 +182,8 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,194 +196,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -532,251 +205,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -787,97 +218,166 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -888,7 +388,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -916,159 +416,45 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="00FFFF00"/>
+      <color rgb="FFFFFF00"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1326,16 +712,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1048559"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="10" width="8.88888888888889" style="1"/>
+    <col min="2" max="10" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1361,13 +747,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1390,7 +776,7 @@
         <v>38815</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1">
         <v>6</v>
@@ -1422,7 +808,7 @@
         <v>38815</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1">
         <v>6</v>
@@ -1454,7 +840,7 @@
         <v>38820</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1">
         <v>6</v>
@@ -1486,7 +872,7 @@
         <v>38820</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1">
         <v>5</v>
@@ -1518,7 +904,7 @@
         <v>38820</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -1550,7 +936,7 @@
         <v>38820</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
         <v>5</v>
@@ -1582,7 +968,7 @@
         <v>38820</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1614,7 +1000,7 @@
         <v>38820</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
@@ -1646,7 +1032,7 @@
         <v>38820</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -1678,7 +1064,7 @@
         <v>38827</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -1710,7 +1096,7 @@
         <v>38827</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -1742,7 +1128,7 @@
         <v>38827</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H13" s="1">
         <v>4</v>
@@ -1774,7 +1160,7 @@
         <v>38827</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1806,7 +1192,7 @@
         <v>38827</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1838,7 +1224,7 @@
         <v>38827</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1">
         <v>2</v>
@@ -1870,7 +1256,7 @@
         <v>38827</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
@@ -1902,7 +1288,7 @@
         <v>38827</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1934,7 +1320,7 @@
         <v>38827</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1966,7 +1352,7 @@
         <v>38827</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1">
         <v>2</v>
@@ -1998,7 +1384,7 @@
         <v>38827</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -2030,7 +1416,7 @@
         <v>38827</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H22" s="1">
         <v>7</v>
@@ -2062,7 +1448,7 @@
         <v>38827</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H23" s="1">
         <v>6</v>
@@ -2094,7 +1480,7 @@
         <v>38827</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H24" s="1">
         <v>5</v>
@@ -2126,7 +1512,7 @@
         <v>38827</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -2158,7 +1544,7 @@
         <v>38827</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -2190,7 +1576,7 @@
         <v>38827</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H27" s="1">
         <v>2</v>
@@ -2222,7 +1608,7 @@
         <v>38827</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
@@ -2254,7 +1640,7 @@
         <v>38827</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2286,7 +1672,7 @@
         <v>38827</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1">
         <v>2</v>
@@ -2318,7 +1704,7 @@
         <v>38827</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2350,7 +1736,7 @@
         <v>38827</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2382,7 +1768,7 @@
         <v>38789</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H33" s="1">
         <v>2</v>
@@ -2414,7 +1800,7 @@
         <v>38789</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H34" s="1">
         <v>12</v>
@@ -2446,7 +1832,7 @@
         <v>38789</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -2478,7 +1864,7 @@
         <v>38789</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H36" s="1">
         <v>4</v>
@@ -2510,7 +1896,7 @@
         <v>38789</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H37" s="1">
         <v>5</v>
@@ -2542,7 +1928,7 @@
         <v>38789</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H38" s="1">
         <v>12</v>
@@ -2574,7 +1960,7 @@
         <v>38789</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H39" s="1">
         <v>7</v>
@@ -2606,7 +1992,7 @@
         <v>38789</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H40" s="1">
         <v>3</v>
@@ -2638,7 +2024,7 @@
         <v>38789</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -2670,7 +2056,7 @@
         <v>38810</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H42" s="1">
         <v>9</v>
@@ -2702,7 +2088,7 @@
         <v>38810</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H43" s="1">
         <v>5</v>
@@ -2734,7 +2120,7 @@
         <v>38810</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H44" s="1">
         <v>6</v>
@@ -2766,7 +2152,7 @@
         <v>38810</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H45" s="1">
         <v>12</v>
@@ -2798,7 +2184,7 @@
         <v>38810</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H46" s="1">
         <v>2</v>
@@ -2830,7 +2216,7 @@
         <v>38810</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H47" s="1">
         <v>4</v>
@@ -2862,7 +2248,7 @@
         <v>38810</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H48" s="1">
         <v>2</v>
@@ -2894,7 +2280,7 @@
         <v>38810</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -2926,7 +2312,7 @@
         <v>38810</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
@@ -2958,7 +2344,7 @@
         <v>38810</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H51" s="1">
         <v>8</v>
@@ -2990,7 +2376,7 @@
         <v>38810</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H52" s="1">
         <v>12</v>
@@ -3022,7 +2408,7 @@
         <v>38810</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -3054,7 +2440,7 @@
         <v>38810</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H54" s="1">
         <v>2</v>
@@ -3086,7 +2472,7 @@
         <v>38810</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H55" s="1">
         <v>2</v>
@@ -3118,7 +2504,7 @@
         <v>38810</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H56" s="1">
         <v>2</v>
@@ -3150,7 +2536,7 @@
         <v>38810</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H57" s="1">
         <v>3</v>
@@ -3182,7 +2568,7 @@
         <v>38810</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H58" s="1">
         <v>4</v>
@@ -3214,7 +2600,7 @@
         <v>38810</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
@@ -3246,7 +2632,7 @@
         <v>38810</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H60" s="1">
         <v>2</v>
@@ -3278,7 +2664,7 @@
         <v>38810</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H61" s="1">
         <v>1</v>
@@ -3310,7 +2696,7 @@
         <v>38810</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H62" s="1">
         <v>6</v>
@@ -3342,7 +2728,7 @@
         <v>38810</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H63" s="1">
         <v>3</v>
@@ -3374,7 +2760,7 @@
         <v>38810</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H64" s="1">
         <v>6</v>
@@ -3406,7 +2792,7 @@
         <v>38824</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H65" s="1">
         <v>14</v>
@@ -3438,7 +2824,7 @@
         <v>38824</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -3470,7 +2856,7 @@
         <v>38824</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H67" s="1">
         <v>12</v>
@@ -3502,7 +2888,7 @@
         <v>38824</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -3534,7 +2920,7 @@
         <v>38824</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H69" s="1">
         <v>12</v>
@@ -3566,7 +2952,7 @@
         <v>38824</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H70" s="1">
         <v>2</v>
@@ -3598,7 +2984,7 @@
         <v>38824</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H71" s="1">
         <v>4</v>
@@ -3630,7 +3016,7 @@
         <v>38824</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H72" s="1">
         <v>4</v>
@@ -3662,7 +3048,7 @@
         <v>38824</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3694,7 +3080,7 @@
         <v>38824</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -3726,7 +3112,7 @@
         <v>38824</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H75" s="1">
         <v>11</v>
@@ -3758,7 +3144,7 @@
         <v>38824</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H76" s="1">
         <v>8</v>
@@ -3790,7 +3176,7 @@
         <v>38824</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -3822,7 +3208,7 @@
         <v>38824</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H78" s="1">
         <v>2</v>
@@ -3854,7 +3240,7 @@
         <v>38824</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H79" s="1">
         <v>1</v>
@@ -3886,7 +3272,7 @@
         <v>38824</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H80" s="1">
         <v>2</v>
@@ -3918,7 +3304,7 @@
         <v>38824</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H81" s="1">
         <v>2</v>
@@ -3950,7 +3336,7 @@
         <v>38824</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H82" s="1">
         <v>2</v>
@@ -3982,7 +3368,7 @@
         <v>38824</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H83" s="1">
         <v>3</v>
@@ -4014,7 +3400,7 @@
         <v>38824</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H84" s="1">
         <v>4</v>
@@ -4046,7 +3432,7 @@
         <v>38824</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H85" s="1">
         <v>12</v>
@@ -4078,7 +3464,7 @@
         <v>38824</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H86" s="1">
         <v>5</v>
@@ -4110,7 +3496,7 @@
         <v>38824</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H87" s="1">
         <v>4</v>
@@ -4142,7 +3528,7 @@
         <v>38824</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H88" s="1">
         <v>4</v>
@@ -4174,7 +3560,7 @@
         <v>38824</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H89" s="1">
         <v>7</v>
@@ -4206,7 +3592,7 @@
         <v>38824</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H90" s="1">
         <v>2</v>
@@ -4238,7 +3624,7 @@
         <v>38824</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -4270,7 +3656,7 @@
         <v>38824</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H92" s="1">
         <v>2</v>
@@ -4302,7 +3688,7 @@
         <v>38824</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H93" s="1">
         <v>3</v>
@@ -4334,7 +3720,7 @@
         <v>38824</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H94" s="1">
         <v>5</v>
@@ -4366,7 +3752,7 @@
         <v>38824</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H95" s="1">
         <v>4</v>
@@ -4398,7 +3784,7 @@
         <v>38824</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H96" s="1">
         <v>2</v>
@@ -4430,7 +3816,7 @@
         <v>38776</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -4462,7 +3848,7 @@
         <v>38776</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H98" s="1">
         <v>6</v>
@@ -4494,7 +3880,7 @@
         <v>38776</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -4526,7 +3912,7 @@
         <v>38776</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -4558,7 +3944,7 @@
         <v>38776</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -4590,7 +3976,7 @@
         <v>38776</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -4622,7 +4008,7 @@
         <v>38776</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -4654,7 +4040,7 @@
         <v>38776</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H104" s="1">
         <v>6</v>
@@ -4686,7 +4072,7 @@
         <v>38776</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -4718,7 +4104,7 @@
         <v>38776</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -4750,7 +4136,7 @@
         <v>38776</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -4782,7 +4168,7 @@
         <v>38776</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -4814,7 +4200,7 @@
         <v>38776</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -4846,7 +4232,7 @@
         <v>38776</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4878,7 +4264,7 @@
         <v>38804</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H111" s="1">
         <v>2</v>
@@ -4910,7 +4296,7 @@
         <v>38804</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H112" s="1">
         <v>5</v>
@@ -4942,7 +4328,7 @@
         <v>38804</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H113" s="1">
         <v>8</v>
@@ -4974,7 +4360,7 @@
         <v>38804</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H114" s="1">
         <v>12</v>
@@ -5006,7 +4392,7 @@
         <v>38804</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H115" s="1">
         <v>10</v>
@@ -5038,7 +4424,7 @@
         <v>38804</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H116" s="1">
         <v>5</v>
@@ -5070,7 +4456,7 @@
         <v>38804</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H117" s="1">
         <v>8</v>
@@ -5102,7 +4488,7 @@
         <v>38804</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H118" s="1">
         <v>17</v>
@@ -5134,7 +4520,7 @@
         <v>38804</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H119" s="1">
         <v>6</v>
@@ -5166,7 +4552,7 @@
         <v>38804</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -5198,7 +4584,7 @@
         <v>38804</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -5230,7 +4616,7 @@
         <v>38804</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H122" s="1">
         <v>11</v>
@@ -5262,7 +4648,7 @@
         <v>38804</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H123" s="1">
         <v>8</v>
@@ -5294,7 +4680,7 @@
         <v>38804</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -5326,7 +4712,7 @@
         <v>38804</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H125" s="1">
         <v>1</v>
@@ -5358,7 +4744,7 @@
         <v>38804</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H126" s="1">
         <v>2</v>
@@ -5390,7 +4776,7 @@
         <v>38804</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H127" s="1">
         <v>6</v>
@@ -5422,7 +4808,7 @@
         <v>38804</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H128" s="1">
         <v>2</v>
@@ -5454,7 +4840,7 @@
         <v>38804</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H129" s="1">
         <v>3</v>
@@ -5486,7 +4872,7 @@
         <v>38804</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H130" s="1">
         <v>5</v>
@@ -5518,7 +4904,7 @@
         <v>38804</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H131" s="1">
         <v>5</v>
@@ -5550,7 +4936,7 @@
         <v>38804</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -5582,7 +4968,7 @@
         <v>38804</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H133" s="1">
         <v>2</v>
@@ -5614,7 +5000,7 @@
         <v>38825</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H134" s="1">
         <v>17</v>
@@ -5646,7 +5032,7 @@
         <v>38825</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H135" s="1">
         <v>22</v>
@@ -5678,7 +5064,7 @@
         <v>38825</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H136" s="1">
         <v>12</v>
@@ -5710,7 +5096,7 @@
         <v>38825</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H137" s="1">
         <v>15</v>
@@ -5742,7 +5128,7 @@
         <v>38825</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H138" s="1">
         <v>6</v>
@@ -5774,7 +5160,7 @@
         <v>38825</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H139" s="1">
         <v>12</v>
@@ -5806,7 +5192,7 @@
         <v>38825</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H140" s="1">
         <v>3</v>
@@ -5838,7 +5224,7 @@
         <v>38825</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H141" s="1">
         <v>51</v>
@@ -5870,7 +5256,7 @@
         <v>38825</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H142" s="1">
         <v>32</v>
@@ -5902,7 +5288,7 @@
         <v>38825</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H143" s="1">
         <v>2</v>
@@ -5934,7 +5320,7 @@
         <v>38825</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H144" s="1">
         <v>5</v>
@@ -5966,7 +5352,7 @@
         <v>38825</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H145" s="1">
         <v>4</v>
@@ -5998,7 +5384,7 @@
         <v>38825</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H146" s="1">
         <v>14</v>
@@ -6030,7 +5416,7 @@
         <v>38825</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H147" s="1">
         <v>24</v>
@@ -6062,7 +5448,7 @@
         <v>38825</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H148" s="1">
         <v>19</v>
@@ -6094,7 +5480,7 @@
         <v>38825</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H149" s="1">
         <v>7</v>
@@ -6126,7 +5512,7 @@
         <v>38825</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H150" s="1">
         <v>7</v>
@@ -6158,7 +5544,7 @@
         <v>38825</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H151" s="1">
         <v>7</v>
@@ -6190,7 +5576,7 @@
         <v>38825</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H152" s="1">
         <v>11</v>
@@ -6222,7 +5608,7 @@
         <v>38825</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H153" s="1">
         <v>8</v>
@@ -6254,7 +5640,7 @@
         <v>38825</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H154" s="1">
         <v>3</v>
@@ -6286,7 +5672,7 @@
         <v>38825</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
@@ -6318,7 +5704,7 @@
         <v>38825</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
@@ -6350,7 +5736,7 @@
         <v>38825</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H157" s="1">
         <v>4</v>
@@ -6382,7 +5768,7 @@
         <v>38825</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H158" s="1">
         <v>6</v>
@@ -6414,7 +5800,7 @@
         <v>38825</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H159" s="1">
         <v>7</v>
@@ -6446,7 +5832,7 @@
         <v>38804</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H160" s="1">
         <v>2</v>
@@ -6478,7 +5864,7 @@
         <v>38804</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H161" s="1">
         <v>4</v>
@@ -6510,7 +5896,7 @@
         <v>38804</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H162" s="1">
         <v>5</v>
@@ -6542,7 +5928,7 @@
         <v>38804</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H163" s="1">
         <v>2</v>
@@ -6574,7 +5960,7 @@
         <v>38804</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H164" s="1">
         <v>3</v>
@@ -6606,7 +5992,7 @@
         <v>38804</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
@@ -6638,7 +6024,7 @@
         <v>38804</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H166" s="1">
         <v>16</v>
@@ -6670,7 +6056,7 @@
         <v>38804</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H167" s="1">
         <v>4</v>
@@ -6702,7 +6088,7 @@
         <v>38804</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H168" s="1">
         <v>2</v>
@@ -6734,7 +6120,7 @@
         <v>38804</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H169" s="1">
         <v>4</v>
@@ -6766,7 +6152,7 @@
         <v>38804</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H170" s="1">
         <v>6</v>
@@ -6798,7 +6184,7 @@
         <v>38804</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H171" s="1">
         <v>1</v>
@@ -6830,7 +6216,7 @@
         <v>38804</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H172" s="1">
         <v>3</v>
@@ -6862,7 +6248,7 @@
         <v>38813</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H173" s="1">
         <v>5</v>
@@ -6894,7 +6280,7 @@
         <v>38813</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H174" s="1">
         <v>25</v>
@@ -6926,7 +6312,7 @@
         <v>38813</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H175" s="1">
         <v>8</v>
@@ -6958,7 +6344,7 @@
         <v>38813</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -6990,7 +6376,7 @@
         <v>38813</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H177" s="1">
         <v>24</v>
@@ -7022,7 +6408,7 @@
         <v>38813</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H178" s="1">
         <v>5</v>
@@ -7054,7 +6440,7 @@
         <v>38813</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H179" s="1">
         <v>2</v>
@@ -7086,7 +6472,7 @@
         <v>38813</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H180" s="1">
         <v>35</v>
@@ -7118,7 +6504,7 @@
         <v>38813</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H181" s="1">
         <v>14</v>
@@ -7150,7 +6536,7 @@
         <v>38813</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -7182,7 +6568,7 @@
         <v>38813</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H183" s="1">
         <v>3</v>
@@ -7214,7 +6600,7 @@
         <v>38813</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H184" s="1">
         <v>1</v>
@@ -7246,7 +6632,7 @@
         <v>38813</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H185" s="1">
         <v>2</v>
@@ -7278,7 +6664,7 @@
         <v>38813</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H186" s="1">
         <v>5</v>
@@ -7310,7 +6696,7 @@
         <v>38813</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H187" s="1">
         <v>3</v>
@@ -7342,7 +6728,7 @@
         <v>38813</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H188" s="1">
         <v>5</v>
@@ -7374,7 +6760,7 @@
         <v>38813</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H189" s="1">
         <v>2</v>
@@ -7406,7 +6792,7 @@
         <v>38813</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -7438,7 +6824,7 @@
         <v>38813</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H191" s="1">
         <v>3</v>
@@ -7470,7 +6856,7 @@
         <v>38813</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H192" s="1">
         <v>5</v>
@@ -7502,7 +6888,7 @@
         <v>38813</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H193" s="1">
         <v>5</v>
@@ -7534,7 +6920,7 @@
         <v>38813</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H194" s="1">
         <v>3</v>
@@ -7566,7 +6952,7 @@
         <v>38813</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H195" s="1">
         <v>6</v>
@@ -7598,7 +6984,7 @@
         <v>38813</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H196" s="1">
         <v>1</v>
@@ -7630,7 +7016,7 @@
         <v>38825</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H197" s="1">
         <v>2</v>
@@ -7662,7 +7048,7 @@
         <v>38825</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H198" s="1">
         <v>2</v>
@@ -7694,7 +7080,7 @@
         <v>38825</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H199" s="1">
         <v>3</v>
@@ -7726,7 +7112,7 @@
         <v>38825</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H200" s="1">
         <v>4</v>
@@ -7758,7 +7144,7 @@
         <v>38825</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H201" s="1">
         <v>7</v>
@@ -7790,7 +7176,7 @@
         <v>38825</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H202" s="1">
         <v>4</v>
@@ -7822,7 +7208,7 @@
         <v>38825</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H203" s="1">
         <v>8</v>
@@ -7854,7 +7240,7 @@
         <v>38825</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H204" s="1">
         <v>16</v>
@@ -7886,7 +7272,7 @@
         <v>38825</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H205" s="1">
         <v>8</v>
@@ -7918,7 +7304,7 @@
         <v>38825</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H206" s="1">
         <v>4</v>
@@ -7950,7 +7336,7 @@
         <v>38825</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -7982,7 +7368,7 @@
         <v>38825</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -8014,7 +7400,7 @@
         <v>38825</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H209" s="1">
         <v>46</v>
@@ -8046,7 +7432,7 @@
         <v>38825</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H210" s="1">
         <v>24</v>
@@ -8078,7 +7464,7 @@
         <v>38825</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -8110,7 +7496,7 @@
         <v>38825</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H212" s="1">
         <v>1</v>
@@ -8142,7 +7528,7 @@
         <v>38825</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H213" s="1">
         <v>3</v>
@@ -8174,7 +7560,7 @@
         <v>38825</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H214" s="1">
         <v>2</v>
@@ -8206,7 +7592,7 @@
         <v>38825</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H215" s="1">
         <v>6</v>
@@ -8238,7 +7624,7 @@
         <v>38825</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H216" s="1">
         <v>16</v>
@@ -8270,7 +7656,7 @@
         <v>38825</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H217" s="1">
         <v>21</v>
@@ -8302,7 +7688,7 @@
         <v>38825</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H218" s="1">
         <v>5</v>
@@ -8334,7 +7720,7 @@
         <v>38825</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H219" s="1">
         <v>16</v>
@@ -8366,7 +7752,7 @@
         <v>38825</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H220" s="1">
         <v>11</v>
@@ -8398,7 +7784,7 @@
         <v>38825</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H221" s="1">
         <v>2</v>
@@ -8430,7 +7816,7 @@
         <v>38825</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -8462,7 +7848,7 @@
         <v>38825</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H223" s="1">
         <v>9</v>
@@ -8494,7 +7880,7 @@
         <v>38825</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H224" s="1">
         <v>4</v>
@@ -8526,7 +7912,7 @@
         <v>38813</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H225" s="1">
         <v>2</v>
@@ -8558,7 +7944,7 @@
         <v>38813</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H226" s="1">
         <v>5</v>
@@ -8590,7 +7976,7 @@
         <v>38813</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -8622,7 +8008,7 @@
         <v>38813</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H228" s="1">
         <v>4</v>
@@ -8651,7 +8037,7 @@
         <v>38813</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -8683,7 +8069,7 @@
         <v>38813</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H230" s="1">
         <v>1</v>
@@ -8715,7 +8101,7 @@
         <v>38813</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H231" s="1">
         <v>2</v>
@@ -8747,7 +8133,7 @@
         <v>38813</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -8779,7 +8165,7 @@
         <v>38813</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H233" s="1">
         <v>1</v>
@@ -8811,7 +8197,7 @@
         <v>38813</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H234" s="1">
         <v>3</v>
@@ -8843,7 +8229,7 @@
         <v>38813</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H235" s="1">
         <v>2</v>
@@ -8875,7 +8261,7 @@
         <v>38813</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H236" s="1">
         <v>2</v>
@@ -8907,7 +8293,7 @@
         <v>38813</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -8939,7 +8325,7 @@
         <v>38813</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H238" s="1">
         <v>2</v>
@@ -8971,7 +8357,7 @@
         <v>38819</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H239" s="1">
         <v>4</v>
@@ -9003,7 +8389,7 @@
         <v>38819</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H240" s="1">
         <v>5</v>
@@ -9035,7 +8421,7 @@
         <v>38819</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H241" s="1">
         <v>2</v>
@@ -9067,7 +8453,7 @@
         <v>38819</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H242" s="1">
         <v>12</v>
@@ -9099,7 +8485,7 @@
         <v>38819</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H243" s="1">
         <v>8</v>
@@ -9131,7 +8517,7 @@
         <v>38819</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H244" s="1">
         <v>1</v>
@@ -9163,7 +8549,7 @@
         <v>38819</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H245" s="1">
         <v>4</v>
@@ -9195,7 +8581,7 @@
         <v>38819</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H246" s="1">
         <v>7</v>
@@ -9227,7 +8613,7 @@
         <v>38819</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H247" s="1">
         <v>2</v>
@@ -9259,7 +8645,7 @@
         <v>38819</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H248" s="1">
         <v>1</v>
@@ -9291,7 +8677,7 @@
         <v>38819</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H249" s="1">
         <v>3</v>
@@ -9323,7 +8709,7 @@
         <v>38819</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H250" s="1">
         <v>3</v>
@@ -9355,7 +8741,7 @@
         <v>38819</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H251" s="1">
         <v>5</v>
@@ -9387,7 +8773,7 @@
         <v>38819</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H252" s="1">
         <v>5</v>
@@ -9419,7 +8805,7 @@
         <v>38819</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H253" s="1">
         <v>3</v>
@@ -9451,7 +8837,7 @@
         <v>38819</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H254" s="1">
         <v>2</v>
@@ -9483,7 +8869,7 @@
         <v>38830</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H255" s="1">
         <v>1</v>
@@ -9515,7 +8901,7 @@
         <v>38830</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H256" s="1">
         <v>4</v>
@@ -9547,7 +8933,7 @@
         <v>38830</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H257" s="1">
         <v>6</v>
@@ -9579,7 +8965,7 @@
         <v>38830</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H258" s="1">
         <v>4</v>
@@ -9611,7 +8997,7 @@
         <v>38830</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H259" s="1">
         <v>6</v>
@@ -9643,7 +9029,7 @@
         <v>38830</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H260" s="1">
         <v>2</v>
@@ -9675,7 +9061,7 @@
         <v>38830</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -9707,7 +9093,7 @@
         <v>38830</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H262" s="1">
         <v>2</v>
@@ -9739,7 +9125,7 @@
         <v>38830</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H263" s="1">
         <v>9</v>
@@ -9771,7 +9157,7 @@
         <v>38830</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H264" s="1">
         <v>8</v>
@@ -9803,7 +9189,7 @@
         <v>38830</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
@@ -9835,7 +9221,7 @@
         <v>38830</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H266" s="1">
         <v>2</v>
@@ -9867,7 +9253,7 @@
         <v>38830</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H267" s="1">
         <v>2</v>
@@ -9899,7 +9285,7 @@
         <v>38830</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H268" s="1">
         <v>4</v>
@@ -9931,7 +9317,7 @@
         <v>38830</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H269" s="1">
         <v>2</v>
@@ -9963,7 +9349,7 @@
         <v>38830</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H270" s="1">
         <v>4</v>
@@ -9995,7 +9381,7 @@
         <v>38830</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H271" s="1">
         <v>2</v>
@@ -10027,7 +9413,7 @@
         <v>38830</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H272" s="1">
         <v>1</v>
@@ -10059,7 +9445,7 @@
         <v>38830</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H273" s="1">
         <v>2</v>
@@ -10091,7 +9477,7 @@
         <v>38830</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H274" s="1">
         <v>12</v>
@@ -10123,7 +9509,7 @@
         <v>38830</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H275" s="1">
         <v>7</v>
@@ -10155,7 +9541,7 @@
         <v>38830</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -10187,7 +9573,7 @@
         <v>38830</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -10219,7 +9605,7 @@
         <v>38830</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
@@ -10251,7 +9637,7 @@
         <v>38830</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H279" s="1">
         <v>2</v>
@@ -10283,7 +9669,7 @@
         <v>38830</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -10315,7 +9701,7 @@
         <v>38821</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H281" s="1">
         <v>5</v>
@@ -10347,7 +9733,7 @@
         <v>38821</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H282" s="1">
         <v>5</v>
@@ -10379,7 +9765,7 @@
         <v>38821</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H283" s="1">
         <v>6</v>
@@ -10411,7 +9797,7 @@
         <v>38821</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H284" s="1">
         <v>3</v>
@@ -10443,7 +9829,7 @@
         <v>38821</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H285" s="1">
         <v>4</v>
@@ -10475,7 +9861,7 @@
         <v>38821</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H286" s="1">
         <v>1</v>
@@ -10507,7 +9893,7 @@
         <v>38821</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H287" s="1">
         <v>3</v>
@@ -10539,7 +9925,7 @@
         <v>38821</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H288" s="1">
         <v>1</v>
@@ -10571,7 +9957,7 @@
         <v>38821</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H289" s="1">
         <v>4</v>
@@ -10603,7 +9989,7 @@
         <v>38821</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H290" s="1">
         <v>12</v>
@@ -10635,7 +10021,7 @@
         <v>38832</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H291" s="1">
         <v>3</v>
@@ -10667,7 +10053,7 @@
         <v>38832</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H292" s="1">
         <v>2</v>
@@ -10699,7 +10085,7 @@
         <v>38832</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H293" s="1">
         <v>2</v>
@@ -10731,7 +10117,7 @@
         <v>38832</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H294" s="1">
         <v>5</v>
@@ -10763,7 +10149,7 @@
         <v>38832</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H295" s="1">
         <v>2</v>
@@ -10795,7 +10181,7 @@
         <v>38832</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -10827,7 +10213,7 @@
         <v>38832</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H297" s="1">
         <v>3</v>
@@ -10859,7 +10245,7 @@
         <v>38832</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H298" s="1">
         <v>5</v>
@@ -10891,7 +10277,7 @@
         <v>38832</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H299" s="1">
         <v>1</v>
@@ -10923,7 +10309,7 @@
         <v>38832</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H300" s="1">
         <v>4</v>
@@ -10955,7 +10341,7 @@
         <v>38832</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H301" s="1">
         <v>2</v>
@@ -10987,7 +10373,7 @@
         <v>38832</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H302" s="1">
         <v>7</v>
@@ -11019,7 +10405,7 @@
         <v>38832</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H303" s="1">
         <v>2</v>
@@ -11051,7 +10437,7 @@
         <v>38832</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H304" s="1">
         <v>6</v>
@@ -11083,7 +10469,7 @@
         <v>38832</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H305" s="1">
         <v>3</v>
@@ -11115,7 +10501,7 @@
         <v>38832</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -11147,7 +10533,7 @@
         <v>38832</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H307" s="1">
         <v>2</v>
@@ -11179,7 +10565,7 @@
         <v>38832</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H308" s="1">
         <v>4</v>
@@ -11211,7 +10597,7 @@
         <v>38832</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H309" s="1">
         <v>7</v>
@@ -11243,7 +10629,7 @@
         <v>38832</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H310" s="1">
         <v>5</v>
@@ -11275,7 +10661,7 @@
         <v>38832</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
@@ -11307,7 +10693,7 @@
         <v>38839</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H312" s="1">
         <v>4</v>
@@ -11339,7 +10725,7 @@
         <v>38839</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H313" s="1">
         <v>5</v>
@@ -11371,7 +10757,7 @@
         <v>38839</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H314" s="1">
         <v>6</v>
@@ -11403,7 +10789,7 @@
         <v>38839</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H315" s="1">
         <v>2</v>
@@ -11435,7 +10821,7 @@
         <v>38839</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H316" s="1">
         <v>2</v>
@@ -11467,7 +10853,7 @@
         <v>38839</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H317" s="1">
         <v>2</v>
@@ -11499,7 +10885,7 @@
         <v>38839</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H318" s="1">
         <v>2</v>
@@ -11531,7 +10917,7 @@
         <v>38839</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H319" s="1">
         <v>2</v>
@@ -11563,7 +10949,7 @@
         <v>38839</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H320" s="1">
         <v>3</v>
@@ -11595,7 +10981,7 @@
         <v>38839</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H321" s="1">
         <v>4</v>
@@ -11627,7 +11013,7 @@
         <v>38839</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H322" s="1">
         <v>2</v>
@@ -11659,7 +11045,7 @@
         <v>38839</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H323" s="1">
         <v>3</v>
@@ -11691,7 +11077,7 @@
         <v>38839</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H324" s="1">
         <v>2</v>
@@ -11723,7 +11109,7 @@
         <v>38839</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H325" s="1">
         <v>3</v>
@@ -11755,7 +11141,7 @@
         <v>38839</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H326" s="1">
         <v>5</v>
@@ -11787,7 +11173,7 @@
         <v>38839</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H327" s="1">
         <v>4</v>
@@ -11819,7 +11205,7 @@
         <v>38839</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H328" s="1">
         <v>2</v>
@@ -11851,7 +11237,7 @@
         <v>38839</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H329" s="1">
         <v>0</v>
@@ -11883,7 +11269,7 @@
         <v>38839</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H330" s="1">
         <v>5</v>
@@ -11915,7 +11301,7 @@
         <v>38839</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H331" s="1">
         <v>3</v>
@@ -11947,7 +11333,7 @@
         <v>38839</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H332" s="1">
         <v>3</v>
@@ -11979,7 +11365,7 @@
         <v>38839</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H333" s="1">
         <v>3</v>
@@ -12011,7 +11397,7 @@
         <v>38839</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H334" s="1">
         <v>2</v>
@@ -12043,7 +11429,7 @@
         <v>38821</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H335" s="1">
         <v>2</v>
@@ -12075,7 +11461,7 @@
         <v>38821</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H336" s="1">
         <v>2</v>
@@ -12107,7 +11493,7 @@
         <v>38821</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H337" s="1">
         <v>6</v>
@@ -12139,7 +11525,7 @@
         <v>38821</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H338" s="1">
         <v>0</v>
@@ -12171,7 +11557,7 @@
         <v>38821</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H339" s="1">
         <v>2</v>
@@ -12203,7 +11589,7 @@
         <v>38821</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H340" s="1">
         <v>1</v>
@@ -12235,7 +11621,7 @@
         <v>38821</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H341" s="1">
         <v>2</v>
@@ -12267,7 +11653,7 @@
         <v>38821</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H342" s="1">
         <v>2</v>
@@ -12299,7 +11685,7 @@
         <v>38821</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H343" s="1">
         <v>5</v>
@@ -12331,7 +11717,7 @@
         <v>38821</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H344" s="1">
         <v>0</v>
@@ -12363,7 +11749,7 @@
         <v>38821</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H345" s="1">
         <v>0</v>
@@ -12395,7 +11781,7 @@
         <v>38821</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H346" s="1">
         <v>5</v>
@@ -12427,7 +11813,7 @@
         <v>38829</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H347" s="1">
         <v>8</v>
@@ -12459,7 +11845,7 @@
         <v>38829</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H348" s="1">
         <v>6</v>
@@ -12491,7 +11877,7 @@
         <v>38829</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H349" s="1">
         <v>2</v>
@@ -12523,7 +11909,7 @@
         <v>38829</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H350" s="1">
         <v>9</v>
@@ -12555,7 +11941,7 @@
         <v>38829</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H351" s="1">
         <v>4</v>
@@ -12587,7 +11973,7 @@
         <v>38829</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H352" s="1">
         <v>2</v>
@@ -12619,7 +12005,7 @@
         <v>38829</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H353" s="1">
         <v>4</v>
@@ -12651,7 +12037,7 @@
         <v>38829</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H354" s="1">
         <v>2</v>
@@ -12683,7 +12069,7 @@
         <v>38829</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
@@ -12715,7 +12101,7 @@
         <v>38829</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H356" s="1">
         <v>2</v>
@@ -12747,7 +12133,7 @@
         <v>38829</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H357" s="1">
         <v>3</v>
@@ -12779,7 +12165,7 @@
         <v>38829</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H358" s="1">
         <v>5</v>
@@ -12811,7 +12197,7 @@
         <v>38829</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H359" s="1">
         <v>2</v>
@@ -12843,7 +12229,7 @@
         <v>38829</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H360" s="1">
         <v>2</v>
@@ -12875,7 +12261,7 @@
         <v>38829</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H361" s="1">
         <v>4</v>
@@ -12907,7 +12293,7 @@
         <v>38829</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H362" s="1">
         <v>11</v>
@@ -12939,7 +12325,7 @@
         <v>38829</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H363" s="1">
         <v>6</v>
@@ -12971,7 +12357,7 @@
         <v>38829</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H364" s="1">
         <v>0</v>
@@ -13003,7 +12389,7 @@
         <v>38829</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H365" s="1">
         <v>0</v>
@@ -13035,7 +12421,7 @@
         <v>38829</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H366" s="1">
         <v>4</v>
@@ -13067,7 +12453,7 @@
         <v>38829</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H367" s="1">
         <v>2</v>
@@ -13099,7 +12485,7 @@
         <v>38829</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H368" s="1">
         <v>2</v>
@@ -13131,7 +12517,7 @@
         <v>38829</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H369" s="1">
         <v>3</v>
@@ -13163,7 +12549,7 @@
         <v>38829</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H370" s="1">
         <v>4</v>
@@ -13195,7 +12581,7 @@
         <v>38829</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H371" s="1">
         <v>0</v>
@@ -13227,7 +12613,7 @@
         <v>38829</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H372" s="1">
         <v>0</v>
@@ -13259,7 +12645,7 @@
         <v>38829</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H373" s="1">
         <v>0</v>
@@ -13291,7 +12677,7 @@
         <v>38829</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H374" s="1">
         <v>5</v>
@@ -13323,7 +12709,7 @@
         <v>38829</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H375" s="1">
         <v>2</v>
@@ -13355,7 +12741,7 @@
         <v>38829</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H376" s="1">
         <v>0</v>
@@ -13384,10 +12770,10 @@
         <v>2012</v>
       </c>
       <c r="F377" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H377" s="1">
         <v>2</v>
@@ -13416,10 +12802,10 @@
         <v>2012</v>
       </c>
       <c r="F378" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H378" s="1">
         <v>0</v>
@@ -13448,10 +12834,10 @@
         <v>2012</v>
       </c>
       <c r="F379" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H379" s="1">
         <v>0</v>
@@ -13480,10 +12866,10 @@
         <v>2012</v>
       </c>
       <c r="F380" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H380" s="1">
         <v>3</v>
@@ -13512,10 +12898,10 @@
         <v>2012</v>
       </c>
       <c r="F381" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H381" s="1">
         <v>1</v>
@@ -13544,10 +12930,10 @@
         <v>2012</v>
       </c>
       <c r="F382" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H382" s="1">
         <v>2</v>
@@ -13576,10 +12962,10 @@
         <v>2012</v>
       </c>
       <c r="F383" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H383" s="1">
         <v>6</v>
@@ -13608,10 +12994,10 @@
         <v>2012</v>
       </c>
       <c r="F384" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H384" s="1">
         <v>4</v>
@@ -13640,10 +13026,10 @@
         <v>2012</v>
       </c>
       <c r="F385" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H385" s="1">
         <v>2</v>
@@ -13672,10 +13058,10 @@
         <v>2012</v>
       </c>
       <c r="F386" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H386" s="1">
         <v>2</v>
@@ -13704,10 +13090,10 @@
         <v>2012</v>
       </c>
       <c r="F387" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H387" s="1">
         <v>0</v>
@@ -13736,10 +13122,10 @@
         <v>2012</v>
       </c>
       <c r="F388" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H388" s="1">
         <v>0</v>
@@ -13768,10 +13154,10 @@
         <v>2012</v>
       </c>
       <c r="F389" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H389" s="1">
         <v>2</v>
@@ -13800,10 +13186,10 @@
         <v>2012</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H390" s="1">
         <v>4</v>
@@ -13832,10 +13218,10 @@
         <v>2012</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H391" s="1">
         <v>2</v>
@@ -13864,10 +13250,10 @@
         <v>2012</v>
       </c>
       <c r="F392" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H392" s="1">
         <v>2</v>
@@ -13896,10 +13282,10 @@
         <v>2012</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H393" s="1">
         <v>5</v>
@@ -13928,10 +13314,10 @@
         <v>2012</v>
       </c>
       <c r="F394" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H394" s="1">
         <v>9</v>
@@ -13960,10 +13346,10 @@
         <v>2012</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H395" s="1">
         <v>5</v>
@@ -13992,10 +13378,10 @@
         <v>2012</v>
       </c>
       <c r="F396" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H396" s="1">
         <v>0</v>
@@ -14024,10 +13410,10 @@
         <v>2012</v>
       </c>
       <c r="F397" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H397" s="1">
         <v>5</v>
@@ -14056,10 +13442,10 @@
         <v>2012</v>
       </c>
       <c r="F398" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H398" s="1">
         <v>8</v>
@@ -14088,10 +13474,10 @@
         <v>2012</v>
       </c>
       <c r="F399" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H399" s="1">
         <v>8</v>
@@ -14120,10 +13506,10 @@
         <v>2012</v>
       </c>
       <c r="F400" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H400" s="1">
         <v>7</v>
@@ -14152,10 +13538,10 @@
         <v>2012</v>
       </c>
       <c r="F401" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H401" s="1">
         <v>0</v>
@@ -14184,10 +13570,10 @@
         <v>2012</v>
       </c>
       <c r="F402" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H402" s="1">
         <v>0</v>
@@ -14216,10 +13602,10 @@
         <v>2012</v>
       </c>
       <c r="F403" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H403" s="1">
         <v>3</v>
@@ -14248,10 +13634,10 @@
         <v>2012</v>
       </c>
       <c r="F404" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H404" s="1">
         <v>1</v>
@@ -14283,7 +13669,7 @@
         <v>38814</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H405" s="1">
         <v>2</v>
@@ -14315,7 +13701,7 @@
         <v>38814</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H406" s="1">
         <v>0</v>
@@ -14347,7 +13733,7 @@
         <v>38814</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H407" s="1">
         <v>0</v>
@@ -14379,7 +13765,7 @@
         <v>38814</v>
       </c>
       <c r="G408" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H408" s="1">
         <v>2</v>
@@ -14411,7 +13797,7 @@
         <v>38814</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H409" s="1">
         <v>0</v>
@@ -14443,7 +13829,7 @@
         <v>38814</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H410" s="1">
         <v>0</v>
@@ -14475,7 +13861,7 @@
         <v>38814</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H411" s="1">
         <v>0</v>
@@ -14507,7 +13893,7 @@
         <v>38814</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H412" s="1">
         <v>2</v>
@@ -14539,7 +13925,7 @@
         <v>38814</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H413" s="1">
         <v>1</v>
@@ -14571,7 +13957,7 @@
         <v>38814</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H414" s="1">
         <v>0</v>
@@ -14603,7 +13989,7 @@
         <v>38814</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H415" s="1">
         <v>4</v>
@@ -14635,7 +14021,7 @@
         <v>38828</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H416" s="1">
         <v>2</v>
@@ -14667,7 +14053,7 @@
         <v>38828</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H417" s="1">
         <v>1</v>
@@ -14699,7 +14085,7 @@
         <v>38828</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H418" s="1">
         <v>1</v>
@@ -14731,7 +14117,7 @@
         <v>38828</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H419" s="1">
         <v>2</v>
@@ -14763,7 +14149,7 @@
         <v>38828</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H420" s="1">
         <v>2</v>
@@ -14795,7 +14181,7 @@
         <v>38828</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H421" s="1">
         <v>2</v>
@@ -14827,7 +14213,7 @@
         <v>38828</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H422" s="1">
         <v>4</v>
@@ -14859,7 +14245,7 @@
         <v>38828</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H423" s="1">
         <v>2</v>
@@ -14891,7 +14277,7 @@
         <v>38828</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H424" s="1">
         <v>2</v>
@@ -14923,7 +14309,7 @@
         <v>38828</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H425" s="1">
         <v>2</v>
@@ -14955,7 +14341,7 @@
         <v>38828</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H426" s="1">
         <v>0</v>
@@ -14987,7 +14373,7 @@
         <v>38828</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H427" s="1">
         <v>2</v>
@@ -15019,7 +14405,7 @@
         <v>38828</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H428" s="1">
         <v>2</v>
@@ -15051,7 +14437,7 @@
         <v>38828</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H429" s="1">
         <v>2</v>
@@ -15083,7 +14469,7 @@
         <v>38828</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H430" s="1">
         <v>2</v>
@@ -15115,7 +14501,7 @@
         <v>38828</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H431" s="1">
         <v>1</v>
@@ -15147,7 +14533,7 @@
         <v>38828</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H432" s="1">
         <v>3</v>
@@ -15179,7 +14565,7 @@
         <v>38828</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H433" s="1">
         <v>3</v>
@@ -15211,7 +14597,7 @@
         <v>38828</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H434" s="1">
         <v>3</v>
@@ -15243,7 +14629,7 @@
         <v>38828</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H435" s="1">
         <v>9</v>
@@ -15275,7 +14661,7 @@
         <v>38828</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H436" s="1">
         <v>3</v>
@@ -15307,7 +14693,7 @@
         <v>38828</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H437" s="1">
         <v>3</v>
@@ -15339,7 +14725,7 @@
         <v>38828</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H438" s="1">
         <v>2</v>
@@ -15371,7 +14757,7 @@
         <v>38828</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H439" s="1">
         <v>1</v>
@@ -15403,7 +14789,7 @@
         <v>38828</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H440" s="1">
         <v>3</v>
@@ -15435,7 +14821,7 @@
         <v>38828</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H441" s="1">
         <v>0</v>
@@ -15467,7 +14853,7 @@
         <v>38837</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H442" s="1">
         <v>4</v>
@@ -15499,7 +14885,7 @@
         <v>38837</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H443" s="1">
         <v>0</v>
@@ -15531,7 +14917,7 @@
         <v>38837</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H444" s="1">
         <v>2</v>
@@ -15563,7 +14949,7 @@
         <v>38837</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H445" s="1">
         <v>0</v>
@@ -15595,7 +14981,7 @@
         <v>38837</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H446" s="1">
         <v>5</v>
@@ -15627,7 +15013,7 @@
         <v>38837</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H447" s="1">
         <v>3</v>
@@ -15659,7 +15045,7 @@
         <v>38837</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H448" s="1">
         <v>1</v>
@@ -15691,7 +15077,7 @@
         <v>38837</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H449" s="1">
         <v>4</v>
@@ -15723,7 +15109,7 @@
         <v>38837</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H450" s="1">
         <v>2</v>
@@ -15755,7 +15141,7 @@
         <v>38837</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H451" s="1">
         <v>0</v>
@@ -15787,7 +15173,7 @@
         <v>38837</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H452" s="1">
         <v>1</v>
@@ -15819,7 +15205,7 @@
         <v>38837</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H453" s="1">
         <v>3</v>
@@ -15851,7 +15237,7 @@
         <v>38837</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H454" s="1">
         <v>2</v>
@@ -15883,7 +15269,7 @@
         <v>38837</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H455" s="1">
         <v>2</v>
@@ -15915,7 +15301,7 @@
         <v>38837</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H456" s="1">
         <v>2</v>
@@ -15947,7 +15333,7 @@
         <v>38837</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H457" s="1">
         <v>1</v>
@@ -15979,7 +15365,7 @@
         <v>38837</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H458" s="1">
         <v>6</v>
@@ -16011,7 +15397,7 @@
         <v>38837</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H459" s="1">
         <v>0</v>
@@ -16043,7 +15429,7 @@
         <v>38837</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H460" s="1">
         <v>2</v>
@@ -16075,7 +15461,7 @@
         <v>38837</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H461" s="1">
         <v>0</v>
@@ -16107,7 +15493,7 @@
         <v>38837</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H462" s="1">
         <v>4</v>
@@ -16139,7 +15525,7 @@
         <v>38837</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H463" s="1">
         <v>4</v>
@@ -16171,7 +15557,7 @@
         <v>38837</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H464" s="1">
         <v>1</v>
@@ -16203,7 +15589,7 @@
         <v>38837</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H465" s="1">
         <v>6</v>
@@ -16235,7 +15621,7 @@
         <v>38837</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H466" s="1">
         <v>0</v>
@@ -16267,7 +15653,7 @@
         <v>38837</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H467" s="1">
         <v>0</v>
@@ -16299,7 +15685,7 @@
         <v>38837</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H468" s="1">
         <v>3</v>
@@ -16331,7 +15717,7 @@
         <v>38837</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H469" s="1">
         <v>2</v>
@@ -16363,7 +15749,7 @@
         <v>38837</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H470" s="1">
         <v>1</v>
@@ -16395,7 +15781,7 @@
         <v>38779</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H471" s="1">
         <v>1</v>
@@ -16427,7 +15813,7 @@
         <v>38779</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H472" s="1">
         <v>3</v>
@@ -16459,7 +15845,7 @@
         <v>38779</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H473" s="1">
         <v>2</v>
@@ -16491,7 +15877,7 @@
         <v>38779</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H474" s="1">
         <v>3</v>
@@ -16523,7 +15909,7 @@
         <v>38779</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H475" s="1">
         <v>4</v>
@@ -16555,7 +15941,7 @@
         <v>38779</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H476" s="1">
         <v>3</v>
@@ -16587,7 +15973,7 @@
         <v>38779</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H477" s="1">
         <v>12</v>
@@ -16619,7 +16005,7 @@
         <v>38779</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H478" s="1">
         <v>2</v>
@@ -16651,7 +16037,7 @@
         <v>38779</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H479" s="1">
         <v>0</v>
@@ -16683,7 +16069,7 @@
         <v>38779</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -16715,7 +16101,7 @@
         <v>38779</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -16747,7 +16133,7 @@
         <v>38779</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H482" s="1">
         <v>3</v>
@@ -16779,7 +16165,7 @@
         <v>38779</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H483" s="1">
         <v>1</v>
@@ -16811,7 +16197,7 @@
         <v>38779</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H484" s="1">
         <v>1</v>
@@ -16843,7 +16229,7 @@
         <v>38779</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H485" s="1">
         <v>4</v>
@@ -16875,7 +16261,7 @@
         <v>38779</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H486" s="1">
         <v>2</v>
@@ -16907,7 +16293,7 @@
         <v>38779</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H487" s="1">
         <v>11</v>
@@ -16939,7 +16325,7 @@
         <v>38779</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H488" s="1">
         <v>8</v>
@@ -16971,7 +16357,7 @@
         <v>38779</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H489" s="1">
         <v>3</v>
@@ -17003,7 +16389,7 @@
         <v>38779</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H490" s="1">
         <v>0</v>
@@ -17035,7 +16421,7 @@
         <v>38779</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H491" s="1">
         <v>0</v>
@@ -17067,7 +16453,7 @@
         <v>38779</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H492" s="1">
         <v>0</v>
@@ -17099,7 +16485,7 @@
         <v>38779</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H493" s="1">
         <v>2</v>
@@ -17131,7 +16517,7 @@
         <v>38779</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H494" s="1">
         <v>0</v>
@@ -17163,7 +16549,7 @@
         <v>38779</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H495" s="1">
         <v>4</v>
@@ -17195,7 +16581,7 @@
         <v>38779</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H496" s="1">
         <v>0</v>
@@ -17227,7 +16613,7 @@
         <v>38779</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H497" s="1">
         <v>0</v>
@@ -17259,7 +16645,7 @@
         <v>38798</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H498" s="1">
         <v>3</v>
@@ -17291,7 +16677,7 @@
         <v>38798</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H499" s="1">
         <v>7</v>
@@ -17323,7 +16709,7 @@
         <v>38798</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H500" s="1">
         <v>7</v>
@@ -17355,7 +16741,7 @@
         <v>38798</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H501" s="1">
         <v>0</v>
@@ -17387,7 +16773,7 @@
         <v>38798</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H502" s="1">
         <v>2</v>
@@ -17419,7 +16805,7 @@
         <v>38798</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H503" s="1">
         <v>10</v>
@@ -17451,7 +16837,7 @@
         <v>38798</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H504" s="1">
         <v>7</v>
@@ -17483,7 +16869,7 @@
         <v>38798</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H505" s="1">
         <v>21</v>
@@ -17515,7 +16901,7 @@
         <v>38798</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H506" s="1">
         <v>6</v>
@@ -17547,7 +16933,7 @@
         <v>38798</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H507" s="1">
         <v>0</v>
@@ -17579,7 +16965,7 @@
         <v>38798</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H508" s="1">
         <v>0</v>
@@ -17611,7 +16997,7 @@
         <v>38798</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H509" s="1">
         <v>2</v>
@@ -17643,7 +17029,7 @@
         <v>38798</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H510" s="1">
         <v>1</v>
@@ -17675,7 +17061,7 @@
         <v>38798</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H511" s="1">
         <v>3</v>
@@ -17707,7 +17093,7 @@
         <v>38798</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H512" s="1">
         <v>2</v>
@@ -17739,7 +17125,7 @@
         <v>38798</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H513" s="1">
         <v>0</v>
@@ -17771,7 +17157,7 @@
         <v>38798</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H514" s="1">
         <v>1</v>
@@ -17803,7 +17189,7 @@
         <v>38798</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H515" s="1">
         <v>0</v>
@@ -17835,7 +17221,7 @@
         <v>38798</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H516" s="1">
         <v>4</v>
@@ -17867,7 +17253,7 @@
         <v>38798</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H517" s="1">
         <v>2</v>
@@ -17899,7 +17285,7 @@
         <v>38798</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H518" s="1">
         <v>2</v>
@@ -17931,7 +17317,7 @@
         <v>38798</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H519" s="1">
         <v>3</v>
@@ -17963,7 +17349,7 @@
         <v>38798</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H520" s="1">
         <v>8</v>
@@ -17995,7 +17381,7 @@
         <v>38798</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H521" s="1">
         <v>9</v>
@@ -18027,7 +17413,7 @@
         <v>38798</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H522" s="1">
         <v>4</v>
@@ -18059,7 +17445,7 @@
         <v>38798</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H523" s="1">
         <v>0</v>
@@ -18091,7 +17477,7 @@
         <v>38798</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H524" s="1">
         <v>0</v>
@@ -18123,7 +17509,7 @@
         <v>38798</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H525" s="1">
         <v>0</v>
@@ -18155,7 +17541,7 @@
         <v>38798</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H526" s="1">
         <v>0</v>
@@ -18187,7 +17573,7 @@
         <v>38798</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H527" s="1">
         <v>3</v>
@@ -18219,7 +17605,7 @@
         <v>38798</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H528" s="1">
         <v>0</v>
@@ -18251,7 +17637,7 @@
         <v>38798</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H529" s="1">
         <v>4</v>
@@ -18283,7 +17669,7 @@
         <v>38798</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H530" s="1">
         <v>0</v>
@@ -18315,7 +17701,7 @@
         <v>38821</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H531" s="1">
         <v>2</v>
@@ -18347,7 +17733,7 @@
         <v>38821</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H532" s="1">
         <v>4</v>
@@ -18379,7 +17765,7 @@
         <v>38821</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H533" s="1">
         <v>0</v>
@@ -18411,7 +17797,7 @@
         <v>38821</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H534" s="1">
         <v>1</v>
@@ -18443,7 +17829,7 @@
         <v>38821</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H535" s="1">
         <v>21</v>
@@ -18475,7 +17861,7 @@
         <v>38821</v>
       </c>
       <c r="G536" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H536" s="1">
         <v>5</v>
@@ -18507,7 +17893,7 @@
         <v>38821</v>
       </c>
       <c r="G537" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H537" s="1">
         <v>7</v>
@@ -18539,7 +17925,7 @@
         <v>38821</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H538" s="1">
         <v>2</v>
@@ -18571,7 +17957,7 @@
         <v>38821</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H539" s="1">
         <v>0</v>
@@ -18603,7 +17989,7 @@
         <v>38821</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H540" s="1">
         <v>8</v>
@@ -18635,7 +18021,7 @@
         <v>38821</v>
       </c>
       <c r="G541" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H541" s="1">
         <v>5</v>
@@ -18667,7 +18053,7 @@
         <v>38821</v>
       </c>
       <c r="G542" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H542" s="1">
         <v>3</v>
@@ -18699,7 +18085,7 @@
         <v>38821</v>
       </c>
       <c r="G543" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H543" s="1">
         <v>2</v>
@@ -18731,7 +18117,7 @@
         <v>38821</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H544" s="1">
         <v>4</v>
@@ -18763,7 +18149,7 @@
         <v>38821</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H545" s="1">
         <v>2</v>
@@ -18795,7 +18181,7 @@
         <v>38821</v>
       </c>
       <c r="G546" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H546" s="1">
         <v>6</v>
@@ -18827,7 +18213,7 @@
         <v>38821</v>
       </c>
       <c r="G547" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H547" s="1">
         <v>3</v>
@@ -18859,7 +18245,7 @@
         <v>38821</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H548" s="1">
         <v>0</v>
@@ -18891,7 +18277,7 @@
         <v>38821</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H549" s="1">
         <v>4</v>
@@ -18923,7 +18309,7 @@
         <v>38821</v>
       </c>
       <c r="G550" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H550" s="1">
         <v>5</v>
@@ -18955,7 +18341,7 @@
         <v>38821</v>
       </c>
       <c r="G551" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H551" s="1">
         <v>7</v>
@@ -18987,7 +18373,7 @@
         <v>38821</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H552" s="1">
         <v>4</v>
@@ -19019,7 +18405,7 @@
         <v>38821</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H553" s="1">
         <v>0</v>
@@ -19051,7 +18437,7 @@
         <v>38821</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H554" s="1">
         <v>0</v>
@@ -19083,7 +18469,7 @@
         <v>38821</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H555" s="1">
         <v>0</v>
@@ -19115,7 +18501,7 @@
         <v>38821</v>
       </c>
       <c r="G556" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H556" s="1">
         <v>2</v>
@@ -19147,7 +18533,7 @@
         <v>38821</v>
       </c>
       <c r="G557" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H557" s="1">
         <v>2</v>
@@ -19179,7 +18565,7 @@
         <v>38821</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H558" s="1">
         <v>0</v>
@@ -19211,7 +18597,7 @@
         <v>38821</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H559" s="1">
         <v>3</v>
@@ -19243,7 +18629,7 @@
         <v>38771</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H560" s="1">
         <v>8</v>
@@ -19275,7 +18661,7 @@
         <v>38771</v>
       </c>
       <c r="G561" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H561" s="1">
         <v>4</v>
@@ -19307,7 +18693,7 @@
         <v>38771</v>
       </c>
       <c r="G562" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H562" s="1">
         <v>8</v>
@@ -19339,7 +18725,7 @@
         <v>38771</v>
       </c>
       <c r="G563" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H563" s="1">
         <v>2</v>
@@ -19371,7 +18757,7 @@
         <v>38771</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H564" s="1">
         <v>9</v>
@@ -19403,7 +18789,7 @@
         <v>38771</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H565" s="1">
         <v>11</v>
@@ -19435,7 +18821,7 @@
         <v>38771</v>
       </c>
       <c r="G566" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H566" s="1">
         <v>5</v>
@@ -19467,7 +18853,7 @@
         <v>38771</v>
       </c>
       <c r="G567" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H567" s="1">
         <v>29</v>
@@ -19499,7 +18885,7 @@
         <v>38771</v>
       </c>
       <c r="G568" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H568" s="1">
         <v>3</v>
@@ -19531,7 +18917,7 @@
         <v>38771</v>
       </c>
       <c r="G569" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H569" s="1">
         <v>4</v>
@@ -19563,7 +18949,7 @@
         <v>38771</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H570" s="1">
         <v>5</v>
@@ -19595,7 +18981,7 @@
         <v>38771</v>
       </c>
       <c r="G571" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H571" s="1">
         <v>34</v>
@@ -19627,7 +19013,7 @@
         <v>38771</v>
       </c>
       <c r="G572" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H572" s="1">
         <v>5</v>
@@ -19659,7 +19045,7 @@
         <v>38771</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H573" s="1">
         <v>7</v>
@@ -19691,7 +19077,7 @@
         <v>38771</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H574" s="1">
         <v>4</v>
@@ -19723,7 +19109,7 @@
         <v>38771</v>
       </c>
       <c r="G575" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H575" s="1">
         <v>4</v>
@@ -19755,7 +19141,7 @@
         <v>38771</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H576" s="1">
         <v>5</v>
@@ -19787,7 +19173,7 @@
         <v>38771</v>
       </c>
       <c r="G577" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H577" s="1">
         <v>11</v>
@@ -19819,7 +19205,7 @@
         <v>38771</v>
       </c>
       <c r="G578" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H578" s="1">
         <v>8</v>
@@ -19851,7 +19237,7 @@
         <v>38771</v>
       </c>
       <c r="G579" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H579" s="1">
         <v>4</v>
@@ -19883,7 +19269,7 @@
         <v>38829</v>
       </c>
       <c r="G580" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H580" s="1">
         <v>4</v>
@@ -19915,7 +19301,7 @@
         <v>38771</v>
       </c>
       <c r="G581" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H581" s="1">
         <v>11</v>
@@ -19947,7 +19333,7 @@
         <v>38771</v>
       </c>
       <c r="G582" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H582" s="1">
         <v>44</v>
@@ -19979,7 +19365,7 @@
         <v>38771</v>
       </c>
       <c r="G583" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H583" s="1">
         <v>8</v>
@@ -20011,7 +19397,7 @@
         <v>38771</v>
       </c>
       <c r="G584" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H584" s="1">
         <v>6</v>
@@ -20043,7 +19429,7 @@
         <v>38771</v>
       </c>
       <c r="G585" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H585" s="1">
         <v>0</v>
@@ -20075,7 +19461,7 @@
         <v>38771</v>
       </c>
       <c r="G586" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H586" s="1">
         <v>0</v>
@@ -20107,7 +19493,7 @@
         <v>38771</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H587" s="1">
         <v>4</v>
@@ -20139,7 +19525,7 @@
         <v>38771</v>
       </c>
       <c r="G588" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H588" s="1">
         <v>8</v>
@@ -20171,7 +19557,7 @@
         <v>38771</v>
       </c>
       <c r="G589" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H589" s="1">
         <v>4</v>
@@ -20203,7 +19589,7 @@
         <v>38771</v>
       </c>
       <c r="G590" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H590" s="1">
         <v>5</v>
@@ -20235,7 +19621,7 @@
         <v>38771</v>
       </c>
       <c r="G591" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H591" s="1">
         <v>0</v>
@@ -20267,7 +19653,7 @@
         <v>38813</v>
       </c>
       <c r="G592" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H592" s="1">
         <v>0</v>
@@ -20299,7 +19685,7 @@
         <v>38813</v>
       </c>
       <c r="G593" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H593" s="1">
         <v>3</v>
@@ -20331,7 +19717,7 @@
         <v>38813</v>
       </c>
       <c r="G594" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H594" s="1">
         <v>2</v>
@@ -20363,7 +19749,7 @@
         <v>38813</v>
       </c>
       <c r="G595" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H595" s="1">
         <v>4</v>
@@ -20395,7 +19781,7 @@
         <v>38813</v>
       </c>
       <c r="G596" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H596" s="1">
         <v>0</v>
@@ -20427,7 +19813,7 @@
         <v>38813</v>
       </c>
       <c r="G597" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H597" s="1">
         <v>5</v>
@@ -20459,7 +19845,7 @@
         <v>38813</v>
       </c>
       <c r="G598" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H598" s="1">
         <v>8</v>
@@ -20491,7 +19877,7 @@
         <v>38813</v>
       </c>
       <c r="G599" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H599" s="1">
         <v>7</v>
@@ -20523,7 +19909,7 @@
         <v>38813</v>
       </c>
       <c r="G600" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H600" s="1">
         <v>3</v>
@@ -20555,7 +19941,7 @@
         <v>38813</v>
       </c>
       <c r="G601" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H601" s="1">
         <v>26</v>
@@ -20587,7 +19973,7 @@
         <v>38813</v>
       </c>
       <c r="G602" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H602" s="1">
         <v>5</v>
@@ -20619,7 +20005,7 @@
         <v>38813</v>
       </c>
       <c r="G603" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H603" s="1">
         <v>4</v>
@@ -20651,7 +20037,7 @@
         <v>38813</v>
       </c>
       <c r="G604" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H604" s="1">
         <v>3</v>
@@ -20683,7 +20069,7 @@
         <v>38813</v>
       </c>
       <c r="G605" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H605" s="1">
         <v>0</v>
@@ -20715,7 +20101,7 @@
         <v>38813</v>
       </c>
       <c r="G606" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H606" s="1">
         <v>0</v>
@@ -20747,7 +20133,7 @@
         <v>38813</v>
       </c>
       <c r="G607" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H607" s="1">
         <v>0</v>
@@ -20779,7 +20165,7 @@
         <v>38813</v>
       </c>
       <c r="G608" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H608" s="1">
         <v>1</v>
@@ -20811,7 +20197,7 @@
         <v>38813</v>
       </c>
       <c r="G609" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H609" s="1">
         <v>6</v>
@@ -20843,7 +20229,7 @@
         <v>38813</v>
       </c>
       <c r="G610" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H610" s="1">
         <v>12</v>
@@ -20875,7 +20261,7 @@
         <v>38813</v>
       </c>
       <c r="G611" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H611" s="1">
         <v>4</v>
@@ -20907,7 +20293,7 @@
         <v>38813</v>
       </c>
       <c r="G612" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H612" s="1">
         <v>4</v>
@@ -20939,7 +20325,7 @@
         <v>38813</v>
       </c>
       <c r="G613" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H613" s="1">
         <v>8</v>
@@ -20971,7 +20357,7 @@
         <v>38813</v>
       </c>
       <c r="G614" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H614" s="1">
         <v>2</v>
@@ -21003,7 +20389,7 @@
         <v>38813</v>
       </c>
       <c r="G615" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H615" s="1">
         <v>3</v>
@@ -21035,7 +20421,7 @@
         <v>38813</v>
       </c>
       <c r="G616" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H616" s="1">
         <v>6</v>
@@ -21067,7 +20453,7 @@
         <v>38813</v>
       </c>
       <c r="G617" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H617" s="1">
         <v>2</v>
@@ -21099,7 +20485,7 @@
         <v>38813</v>
       </c>
       <c r="G618" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H618" s="1">
         <v>6</v>
@@ -21131,7 +20517,7 @@
         <v>38813</v>
       </c>
       <c r="G619" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H619" s="1">
         <v>5</v>
@@ -21163,7 +20549,7 @@
         <v>38813</v>
       </c>
       <c r="G620" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H620" s="1">
         <v>5</v>
@@ -21195,7 +20581,7 @@
         <v>38813</v>
       </c>
       <c r="G621" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H621" s="1">
         <v>2</v>
@@ -21227,7 +20613,7 @@
         <v>38813</v>
       </c>
       <c r="G622" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H622" s="1">
         <v>0</v>
@@ -21259,7 +20645,7 @@
         <v>38813</v>
       </c>
       <c r="G623" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H623" s="1">
         <v>4</v>
@@ -21291,7 +20677,7 @@
         <v>38813</v>
       </c>
       <c r="G624" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H624" s="1">
         <v>4</v>
@@ -21323,7 +20709,7 @@
         <v>38813</v>
       </c>
       <c r="G625" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H625" s="1">
         <v>5</v>
@@ -21355,7 +20741,7 @@
         <v>38813</v>
       </c>
       <c r="G626" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H626" s="1">
         <v>3</v>
@@ -21387,7 +20773,7 @@
         <v>38813</v>
       </c>
       <c r="G627" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H627" s="1">
         <v>0</v>
@@ -21419,7 +20805,7 @@
         <v>38813</v>
       </c>
       <c r="G628" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H628" s="1">
         <v>0</v>
@@ -21451,7 +20837,7 @@
         <v>38813</v>
       </c>
       <c r="G629" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H629" s="1">
         <v>0</v>
@@ -21483,7 +20869,7 @@
         <v>38813</v>
       </c>
       <c r="G630" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H630" s="1">
         <v>3</v>
@@ -21515,7 +20901,7 @@
         <v>38813</v>
       </c>
       <c r="G631" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H631" s="1">
         <v>0</v>
@@ -21547,7 +20933,7 @@
         <v>38813</v>
       </c>
       <c r="G632" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H632" s="1">
         <v>2</v>
@@ -21579,7 +20965,7 @@
         <v>38813</v>
       </c>
       <c r="G633" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H633" s="1">
         <v>0</v>
@@ -21611,7 +20997,7 @@
         <v>38829</v>
       </c>
       <c r="G634" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H634" s="1">
         <v>2</v>
@@ -21643,7 +21029,7 @@
         <v>38829</v>
       </c>
       <c r="G635" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H635" s="1">
         <v>0</v>
@@ -21675,7 +21061,7 @@
         <v>38829</v>
       </c>
       <c r="G636" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H636" s="1">
         <v>0</v>
@@ -21707,7 +21093,7 @@
         <v>38829</v>
       </c>
       <c r="G637" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H637" s="1">
         <v>0</v>
@@ -21739,7 +21125,7 @@
         <v>38829</v>
       </c>
       <c r="G638" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H638" s="1">
         <v>6</v>
@@ -21771,7 +21157,7 @@
         <v>38829</v>
       </c>
       <c r="G639" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H639" s="1">
         <v>2</v>
@@ -21803,7 +21189,7 @@
         <v>38829</v>
       </c>
       <c r="G640" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H640" s="1">
         <v>6</v>
@@ -21835,7 +21221,7 @@
         <v>38829</v>
       </c>
       <c r="G641" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H641" s="1">
         <v>32</v>
@@ -21867,7 +21253,7 @@
         <v>38829</v>
       </c>
       <c r="G642" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H642" s="1">
         <v>14</v>
@@ -21899,7 +21285,7 @@
         <v>38829</v>
       </c>
       <c r="G643" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H643" s="1">
         <v>8</v>
@@ -21931,7 +21317,7 @@
         <v>38829</v>
       </c>
       <c r="G644" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H644" s="1">
         <v>0</v>
@@ -21963,7 +21349,7 @@
         <v>38829</v>
       </c>
       <c r="G645" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H645" s="1">
         <v>0</v>
@@ -21995,7 +21381,7 @@
         <v>38829</v>
       </c>
       <c r="G646" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H646" s="1">
         <v>12</v>
@@ -22027,7 +21413,7 @@
         <v>38829</v>
       </c>
       <c r="G647" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H647" s="1">
         <v>0</v>
@@ -22059,7 +21445,7 @@
         <v>38829</v>
       </c>
       <c r="G648" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H648" s="1">
         <v>8</v>
@@ -22091,7 +21477,7 @@
         <v>38829</v>
       </c>
       <c r="G649" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H649" s="1">
         <v>0</v>
@@ -22123,7 +21509,7 @@
         <v>38829</v>
       </c>
       <c r="G650" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H650" s="1">
         <v>12</v>
@@ -22155,7 +21541,7 @@
         <v>38829</v>
       </c>
       <c r="G651" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H651" s="1">
         <v>4</v>
@@ -22187,7 +21573,7 @@
         <v>38829</v>
       </c>
       <c r="G652" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H652" s="1">
         <v>0</v>
@@ -22219,7 +21605,7 @@
         <v>38829</v>
       </c>
       <c r="G653" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H653" s="1">
         <v>0</v>
@@ -22251,7 +21637,7 @@
         <v>38829</v>
       </c>
       <c r="G654" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H654" s="1">
         <v>5</v>
@@ -22283,7 +21669,7 @@
         <v>38829</v>
       </c>
       <c r="G655" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H655" s="1">
         <v>6</v>
@@ -22315,7 +21701,7 @@
         <v>38829</v>
       </c>
       <c r="G656" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H656" s="1">
         <v>3</v>
@@ -22347,7 +21733,7 @@
         <v>38829</v>
       </c>
       <c r="G657" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H657" s="1">
         <v>0</v>
@@ -22379,7 +21765,7 @@
         <v>38829</v>
       </c>
       <c r="G658" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H658" s="1">
         <v>0</v>
@@ -22411,7 +21797,7 @@
         <v>38829</v>
       </c>
       <c r="G659" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H659" s="1">
         <v>0</v>
@@ -22443,7 +21829,7 @@
         <v>38829</v>
       </c>
       <c r="G660" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H660" s="1">
         <v>0</v>
@@ -22475,7 +21861,7 @@
         <v>38829</v>
       </c>
       <c r="G661" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H661" s="1">
         <v>0</v>
@@ -22507,7 +21893,7 @@
         <v>38829</v>
       </c>
       <c r="G662" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H662" s="1">
         <v>0</v>
@@ -22539,7 +21925,7 @@
         <v>38829</v>
       </c>
       <c r="G663" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H663" s="1">
         <v>0</v>
@@ -22571,7 +21957,7 @@
         <v>38829</v>
       </c>
       <c r="G664" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H664" s="1">
         <v>4</v>
@@ -22603,7 +21989,7 @@
         <v>38829</v>
       </c>
       <c r="G665" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H665" s="1">
         <v>0</v>
@@ -22635,7 +22021,7 @@
         <v>38829</v>
       </c>
       <c r="G666" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H666" s="1">
         <v>2</v>
@@ -22647,22 +22033,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="6:6">
+    <row r="667" spans="1:10">
       <c r="F667" s="4"/>
     </row>
-    <row r="668" spans="6:6">
+    <row r="668" spans="1:10">
       <c r="F668" s="4"/>
     </row>
-    <row r="669" spans="6:6">
+    <row r="669" spans="1:10">
       <c r="F669" s="4"/>
     </row>
-    <row r="670" spans="6:6">
+    <row r="670" spans="1:10">
       <c r="F670" s="4"/>
     </row>
-    <row r="671" spans="6:6">
+    <row r="671" spans="1:10">
       <c r="F671" s="4"/>
     </row>
-    <row r="672" spans="6:6">
+    <row r="672" spans="1:10">
       <c r="F672" s="4"/>
     </row>
     <row r="673" spans="6:6">
@@ -22698,24 +22084,20 @@
     <row r="1048558" customFormat="1"/>
     <row r="1048559" customFormat="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:J666" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <sortState ref="A2:J666">
+  <autoFilter ref="B1:J666" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J666">
     <sortCondition ref="A666"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K94"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="40.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -22726,7 +22108,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -22744,13 +22126,13 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -22758,7 +22140,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1">
         <v>8</v>
@@ -22773,7 +22155,7 @@
         <v>38815</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" s="1">
         <v>6</v>
@@ -22790,7 +22172,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -22805,7 +22187,7 @@
         <v>38815</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1">
         <v>6</v>
@@ -22822,7 +22204,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -22837,7 +22219,7 @@
         <v>38820</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1">
         <v>6</v>
@@ -22854,7 +22236,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -22869,7 +22251,7 @@
         <v>38820</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1">
         <v>5</v>
@@ -22886,7 +22268,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -22901,7 +22283,7 @@
         <v>38820</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -22918,7 +22300,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -22933,7 +22315,7 @@
         <v>38820</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -22950,7 +22332,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -22965,7 +22347,7 @@
         <v>38820</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -22982,7 +22364,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -22997,7 +22379,7 @@
         <v>38820</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -23014,7 +22396,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -23029,7 +22411,7 @@
         <v>38820</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -23046,7 +22428,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1">
         <v>6</v>
@@ -23061,7 +22443,7 @@
         <v>38789</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -23078,7 +22460,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1">
         <v>7</v>
@@ -23093,7 +22475,7 @@
         <v>38789</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I12" s="1">
         <v>12</v>
@@ -23110,7 +22492,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -23125,7 +22507,7 @@
         <v>38789</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
@@ -23142,7 +22524,7 @@
         <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
@@ -23157,7 +22539,7 @@
         <v>38789</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I14" s="1">
         <v>4</v>
@@ -23174,7 +22556,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -23189,7 +22571,7 @@
         <v>38789</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I15" s="1">
         <v>5</v>
@@ -23206,7 +22588,7 @@
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -23221,7 +22603,7 @@
         <v>38789</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -23238,7 +22620,7 @@
         <v>169</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1">
         <v>6</v>
@@ -23253,7 +22635,7 @@
         <v>38804</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I17" s="1">
         <v>2</v>
@@ -23270,7 +22652,7 @@
         <v>170</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1">
         <v>6</v>
@@ -23285,7 +22667,7 @@
         <v>38804</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1">
         <v>4</v>
@@ -23302,7 +22684,7 @@
         <v>171</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -23317,7 +22699,7 @@
         <v>38804</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1">
         <v>5</v>
@@ -23334,7 +22716,7 @@
         <v>172</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -23349,7 +22731,7 @@
         <v>38804</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I20" s="1">
         <v>2</v>
@@ -23366,7 +22748,7 @@
         <v>173</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -23381,7 +22763,7 @@
         <v>38804</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1">
         <v>3</v>
@@ -23398,7 +22780,7 @@
         <v>175</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1">
         <v>6</v>
@@ -23413,7 +22795,7 @@
         <v>38804</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I22" s="1">
         <v>16</v>
@@ -23430,7 +22812,7 @@
         <v>176</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1">
         <v>6</v>
@@ -23445,7 +22827,7 @@
         <v>38804</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I23" s="1">
         <v>4</v>
@@ -23462,7 +22844,7 @@
         <v>177</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -23477,7 +22859,7 @@
         <v>38804</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I24" s="1">
         <v>2</v>
@@ -23494,7 +22876,7 @@
         <v>178</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
@@ -23509,7 +22891,7 @@
         <v>38804</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I25" s="1">
         <v>4</v>
@@ -23526,7 +22908,7 @@
         <v>179</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -23541,7 +22923,7 @@
         <v>38804</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I26" s="1">
         <v>6</v>
@@ -23558,7 +22940,7 @@
         <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -23573,7 +22955,7 @@
         <v>38804</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1">
         <v>1</v>
@@ -23590,7 +22972,7 @@
         <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -23605,7 +22987,7 @@
         <v>38804</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1">
         <v>3</v>
@@ -23622,7 +23004,7 @@
         <v>237</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1">
         <v>6</v>
@@ -23637,7 +23019,7 @@
         <v>38813</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
@@ -23654,7 +23036,7 @@
         <v>238</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1">
         <v>7</v>
@@ -23669,7 +23051,7 @@
         <v>38813</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I30" s="1">
         <v>5</v>
@@ -23686,7 +23068,7 @@
         <v>239</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D31" s="1">
         <v>4</v>
@@ -23701,7 +23083,7 @@
         <v>38813</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -23718,7 +23100,7 @@
         <v>240</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D32" s="1">
         <v>4</v>
@@ -23733,7 +23115,7 @@
         <v>38813</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I32" s="1">
         <v>4</v>
@@ -23750,7 +23132,7 @@
         <v>241</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -23765,7 +23147,7 @@
         <v>38813</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -23782,7 +23164,7 @@
         <v>242</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
@@ -23797,7 +23179,7 @@
         <v>38813</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
@@ -23814,7 +23196,7 @@
         <v>243</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
         <v>6</v>
@@ -23829,7 +23211,7 @@
         <v>38813</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I35" s="1">
         <v>2</v>
@@ -23846,7 +23228,7 @@
         <v>244</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
@@ -23861,7 +23243,7 @@
         <v>38813</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -23878,7 +23260,7 @@
         <v>245</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
@@ -23893,7 +23275,7 @@
         <v>38813</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -23910,7 +23292,7 @@
         <v>246</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -23925,7 +23307,7 @@
         <v>38813</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I38" s="1">
         <v>3</v>
@@ -23942,7 +23324,7 @@
         <v>247</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -23957,7 +23339,7 @@
         <v>38813</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I39" s="1">
         <v>2</v>
@@ -23974,7 +23356,7 @@
         <v>248</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D40" s="1">
         <v>10</v>
@@ -23989,7 +23371,7 @@
         <v>38813</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I40" s="1">
         <v>2</v>
@@ -24006,7 +23388,7 @@
         <v>249</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
@@ -24021,7 +23403,7 @@
         <v>38813</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -24038,7 +23420,7 @@
         <v>250</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D42" s="1">
         <v>7</v>
@@ -24053,7 +23435,7 @@
         <v>38813</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I42" s="1">
         <v>2</v>
@@ -24070,7 +23452,7 @@
         <v>252</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D43" s="1">
         <v>6</v>
@@ -24085,7 +23467,7 @@
         <v>38819</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I43" s="1">
         <v>4</v>
@@ -24102,7 +23484,7 @@
         <v>253</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D44" s="1">
         <v>6</v>
@@ -24117,7 +23499,7 @@
         <v>38819</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
@@ -24134,7 +23516,7 @@
         <v>254</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -24149,7 +23531,7 @@
         <v>38819</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I45" s="1">
         <v>2</v>
@@ -24166,7 +23548,7 @@
         <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D46" s="1">
         <v>7</v>
@@ -24181,7 +23563,7 @@
         <v>38819</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I46" s="1">
         <v>12</v>
@@ -24198,7 +23580,7 @@
         <v>256</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -24213,7 +23595,7 @@
         <v>38819</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1">
         <v>8</v>
@@ -24230,7 +23612,7 @@
         <v>257</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D48" s="1">
         <v>1</v>
@@ -24245,7 +23627,7 @@
         <v>38819</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I48" s="1">
         <v>1</v>
@@ -24262,7 +23644,7 @@
         <v>258</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
@@ -24277,7 +23659,7 @@
         <v>38819</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I49" s="1">
         <v>4</v>
@@ -24294,7 +23676,7 @@
         <v>259</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1">
         <v>7</v>
@@ -24309,7 +23691,7 @@
         <v>38819</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I50" s="1">
         <v>7</v>
@@ -24326,7 +23708,7 @@
         <v>260</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D51" s="1">
         <v>6</v>
@@ -24341,7 +23723,7 @@
         <v>38819</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I51" s="1">
         <v>2</v>
@@ -24358,7 +23740,7 @@
         <v>261</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
@@ -24373,7 +23755,7 @@
         <v>38819</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I52" s="1">
         <v>1</v>
@@ -24390,7 +23772,7 @@
         <v>262</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
@@ -24405,7 +23787,7 @@
         <v>38819</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I53" s="1">
         <v>3</v>
@@ -24422,7 +23804,7 @@
         <v>263</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
@@ -24437,7 +23819,7 @@
         <v>38819</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I54" s="1">
         <v>3</v>
@@ -24454,7 +23836,7 @@
         <v>264</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D55" s="1">
         <v>7</v>
@@ -24469,7 +23851,7 @@
         <v>38819</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
@@ -24486,7 +23868,7 @@
         <v>265</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D56" s="1">
         <v>2</v>
@@ -24501,7 +23883,7 @@
         <v>38819</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
@@ -24518,7 +23900,7 @@
         <v>266</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D57" s="1">
         <v>6</v>
@@ -24533,7 +23915,7 @@
         <v>38819</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I57" s="1">
         <v>3</v>
@@ -24550,7 +23932,7 @@
         <v>267</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D58" s="1">
         <v>7</v>
@@ -24565,7 +23947,7 @@
         <v>38819</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I58" s="1">
         <v>2</v>
@@ -24582,7 +23964,7 @@
         <v>296</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -24597,7 +23979,7 @@
         <v>38821</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
@@ -24614,7 +23996,7 @@
         <v>297</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -24629,7 +24011,7 @@
         <v>38821</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I60" s="1">
         <v>5</v>
@@ -24646,7 +24028,7 @@
         <v>298</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -24661,7 +24043,7 @@
         <v>38821</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I61" s="1">
         <v>6</v>
@@ -24678,7 +24060,7 @@
         <v>299</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -24693,7 +24075,7 @@
         <v>38821</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I62" s="1">
         <v>3</v>
@@ -24710,7 +24092,7 @@
         <v>300</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D63" s="1">
         <v>6</v>
@@ -24725,7 +24107,7 @@
         <v>38821</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I63" s="1">
         <v>4</v>
@@ -24742,7 +24124,7 @@
         <v>301</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -24757,7 +24139,7 @@
         <v>38821</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I64" s="1">
         <v>1</v>
@@ -24774,7 +24156,7 @@
         <v>302</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D65" s="1">
         <v>2</v>
@@ -24789,7 +24171,7 @@
         <v>38821</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I65" s="1">
         <v>3</v>
@@ -24806,7 +24188,7 @@
         <v>303</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D66" s="1">
         <v>3</v>
@@ -24821,7 +24203,7 @@
         <v>38821</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I66" s="1">
         <v>1</v>
@@ -24838,7 +24220,7 @@
         <v>304</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D67" s="1">
         <v>1</v>
@@ -24853,7 +24235,7 @@
         <v>38821</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I67" s="1">
         <v>4</v>
@@ -24870,7 +24252,7 @@
         <v>305</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D68" s="1">
         <v>7</v>
@@ -24885,7 +24267,7 @@
         <v>38821</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I68" s="1">
         <v>12</v>
@@ -24902,7 +24284,7 @@
         <v>307</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -24917,7 +24299,7 @@
         <v>38832</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I69" s="1">
         <v>3</v>
@@ -24934,7 +24316,7 @@
         <v>308</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D70" s="1">
         <v>2</v>
@@ -24949,7 +24331,7 @@
         <v>38832</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I70" s="1">
         <v>2</v>
@@ -24966,7 +24348,7 @@
         <v>309</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -24981,7 +24363,7 @@
         <v>38832</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I71" s="1">
         <v>2</v>
@@ -24998,7 +24380,7 @@
         <v>310</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -25013,7 +24395,7 @@
         <v>38832</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I72" s="1">
         <v>5</v>
@@ -25030,7 +24412,7 @@
         <v>311</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
@@ -25045,7 +24427,7 @@
         <v>38832</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1">
         <v>2</v>
@@ -25062,7 +24444,7 @@
         <v>312</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D74" s="1">
         <v>2</v>
@@ -25077,7 +24459,7 @@
         <v>38832</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
@@ -25094,7 +24476,7 @@
         <v>313</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D75" s="1">
         <v>2</v>
@@ -25109,7 +24491,7 @@
         <v>38832</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I75" s="1">
         <v>3</v>
@@ -25126,7 +24508,7 @@
         <v>314</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -25141,7 +24523,7 @@
         <v>38832</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I76" s="1">
         <v>5</v>
@@ -25158,7 +24540,7 @@
         <v>315</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -25173,7 +24555,7 @@
         <v>38832</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I77" s="1">
         <v>1</v>
@@ -25190,7 +24572,7 @@
         <v>316</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D78" s="1">
         <v>2</v>
@@ -25205,7 +24587,7 @@
         <v>38832</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I78" s="1">
         <v>4</v>
@@ -25222,7 +24604,7 @@
         <v>317</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D79" s="1">
         <v>3</v>
@@ -25237,7 +24619,7 @@
         <v>38832</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I79" s="1">
         <v>2</v>
@@ -25254,7 +24636,7 @@
         <v>353</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -25269,7 +24651,7 @@
         <v>38821</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I80" s="1">
         <v>2</v>
@@ -25286,7 +24668,7 @@
         <v>354</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D81" s="1">
         <v>6</v>
@@ -25301,7 +24683,7 @@
         <v>38821</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I81" s="1">
         <v>2</v>
@@ -25318,7 +24700,7 @@
         <v>355</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D82" s="1">
         <v>6</v>
@@ -25333,7 +24715,7 @@
         <v>38821</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I82" s="1">
         <v>6</v>
@@ -25350,7 +24732,7 @@
         <v>357</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
@@ -25365,7 +24747,7 @@
         <v>38821</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I83" s="1">
         <v>2</v>
@@ -25382,7 +24764,7 @@
         <v>358</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -25397,7 +24779,7 @@
         <v>38821</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I84" s="1">
         <v>1</v>
@@ -25414,7 +24796,7 @@
         <v>359</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D85" s="1">
         <v>7</v>
@@ -25429,7 +24811,7 @@
         <v>38821</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I85" s="1">
         <v>2</v>
@@ -25446,7 +24828,7 @@
         <v>360</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D86" s="1">
         <v>6</v>
@@ -25461,7 +24843,7 @@
         <v>38821</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I86" s="1">
         <v>2</v>
@@ -25478,7 +24860,7 @@
         <v>361</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D87" s="1">
         <v>6</v>
@@ -25493,7 +24875,7 @@
         <v>38821</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I87" s="1">
         <v>5</v>
@@ -25510,7 +24892,7 @@
         <v>363</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -25525,7 +24907,7 @@
         <v>38821</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
@@ -25542,7 +24924,7 @@
         <v>364</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D89" s="1">
         <v>7</v>
@@ -25557,7 +24939,7 @@
         <v>38821</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I89" s="1">
         <v>5</v>
@@ -25574,7 +24956,7 @@
         <v>426</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D90" s="1">
         <v>6</v>
@@ -25589,7 +24971,7 @@
         <v>38814</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I90" s="1">
         <v>2</v>
@@ -25606,7 +24988,7 @@
         <v>429</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D91" s="1">
         <v>6</v>
@@ -25621,7 +25003,7 @@
         <v>38814</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I91" s="1">
         <v>2</v>
@@ -25638,7 +25020,7 @@
         <v>433</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D92" s="1">
         <v>6</v>
@@ -25653,7 +25035,7 @@
         <v>38814</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I92" s="1">
         <v>2</v>
@@ -25670,7 +25052,7 @@
         <v>434</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -25685,7 +25067,7 @@
         <v>38814</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I93" s="1">
         <v>1</v>
@@ -25702,7 +25084,7 @@
         <v>436</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D94" s="1">
         <v>7</v>
@@ -25717,7 +25099,7 @@
         <v>38814</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I94" s="1">
         <v>4</v>
@@ -25730,21 +25112,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K94" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:K94" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>